--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,7 +74,31 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -151,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,13 +207,27 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,7 +235,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -282,7 +320,7 @@
     <author>build_control_workbook.py</author>
   </authors>
   <commentList>
-    <comment ref="C20" authorId="0" shapeId="0">
+    <comment ref="C21" authorId="0" shapeId="0">
       <text>
         <t>DRY RUN is the safe default. It navigates and logs but exports nothing.</t>
       </text>
@@ -581,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D41"/>
+  <dimension ref="B2:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -774,232 +812,343 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>C:\Audit\PP2_FY26\Extracts</t>
+          <t>C:\Users\eslucres\Documents\Audit GBKM</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Created if missing. One subfolder per month tab, e.g. ...\Extracts\Sep 25.</t>
+          <t>Taken from recordings/Audit.vbs. Created if missing. One subfolder per month tab, e.g. ...\Audit GBKM\Sep 25.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Run mode</t>
+          <t>Confirming party name</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>DRY RUN</t>
+          <t>SANTANDER SCF</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>DRY RUN walks every screen and logs what it would export, without exporting. EXTRACT performs the exports. Always complete one clean DRY RUN first.</t>
+          <t>A cleared item whose supplier name matches this is treated as a confirming (supply-chain-finance) payment and routed down the Audit2 path, which needs extra steps. Matched case-insensitively, ignoring spaces.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Amount match tolerance</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>0.01</v>
+          <t>Run mode</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>DRY RUN</t>
+        </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Absolute currency tolerance when matching a sample amount to a statement line.</t>
+          <t>DRY RUN walks every screen and logs what it would export, without exporting. EXTRACT performs the exports. Always complete one clean DRY RUN first.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Stop on first error</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+          <t>Amount match tolerance</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>0.01</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>YES halts the run on the first unrecognised screen. NO logs and continues to the next sample.</t>
+          <t>Absolute currency tolerance when matching a sample amount to a statement line.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Max seconds to wait per screen</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>60</v>
+          <t>Stop on first error</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Guards against an indefinite hang when SAP is slow.</t>
+          <t>YES halts the run on the first unrecognised screen. NO logs and continues to the next sample.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>SAP date format</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>DMY</t>
-        </is>
+          <t>Max seconds to wait per screen</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>60</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>How your SAP user renders dates, from SU3 &gt; Defaults. DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
+          <t>Guards against an indefinite hang when SAP is slow.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="10" t="inlineStr">
         <is>
+          <t>SAP date format</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>DDMMYYYY</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>How dates are typed into SAP. DDMMYYYY = 01092025, which is what recordings/Audit.vbs used and therefore what is known to work here. Also supported: DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Cleared list amount column</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr"/>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Caption of the amount column in the exported cleared-items list, if the macro does not find it on its own. Open the first exported file and copy the heading exactly. Leave blank to let the macro try its built-in list of captions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Cleared list supplier column</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr"/>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Caption of the supplier-name column in that same file. Same rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Cleared list document column</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr"/>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Caption of the invoice document-number column in that same file. Optional -- without it the run still identifies the supplier and amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
           <t>Operator name</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr"/>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr"/>
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Samples in scope</t>
-        </is>
-      </c>
-      <c r="C29" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="C30" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Errored</t>
-        </is>
-      </c>
-      <c r="C31" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="C32" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
-        <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>Samples in scope</t>
         </is>
       </c>
       <c r="C33" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="14" t="inlineStr">
         <is>
+          <t>DONE -- invoice downloaded</t>
+        </is>
+      </c>
+      <c r="C34" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>BLOCKED_SCF -- Santander, needs the Audit2 steps</t>
+        </is>
+      </c>
+      <c r="C35" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL -- traced, no invoice file</t>
+        </is>
+      </c>
+      <c r="C36" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>NOT FOUND -- no matching statement line</t>
+        </is>
+      </c>
+      <c r="C37" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS -- more than one line matched</t>
+        </is>
+      </c>
+      <c r="C38" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C39" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C40" s="15">
+        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Files downloaded</t>
+        </is>
+      </c>
+      <c r="C41" s="15">
+        <f>SUM(Samples!N5:N1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="14" t="inlineStr">
+        <is>
           <t>Samples with no named beneficiary in the request</t>
         </is>
       </c>
-      <c r="C34" s="15">
+      <c r="C42" s="15">
         <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Samples the request already names as SANTANDER SCF</t>
+        </is>
+      </c>
+      <c r="C43" s="15">
+        <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="B38" s="14" t="inlineStr">
+    <row r="47" ht="28" customHeight="1">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="B39" s="14" t="inlineStr">
+    <row r="48" ht="28" customHeight="1">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="14" t="inlineStr">
+    <row r="49" ht="28" customHeight="1">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="B41" s="14" t="inlineStr">
+    <row r="50" ht="28" customHeight="1">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1007,16 +1156,16 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C50:D50"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"DRY RUN,EXTRACT"</formula1>
     </dataValidation>
-    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1032,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F41"/>
+  <dimension ref="A2:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1050,10 +1199,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
+    <row r="3" ht="56" customHeight="1">
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Record a session with Alt+F12 &gt; Script Recording and Playback, open the .vbs it writes, and copy each findById("...") string into column F. The example IDs in column D are typical but release-dependent -- verify every one against your own recording before switching Run mode to EXTRACT.</t>
+          <t>Column F is what the macro reads, and it is pre-filled from recordings/Audit.vbs. Rows marked 'recorded' in column D came straight out of that file and should be right for this system. Rows marked VERIFY were not covered by the recording -- check each one against a fresh Alt+F12 recording before switching Run mode to EXTRACT. Rows marked BLOCKED are unknown because Audit2.vbs captured no steps.</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1220,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>Example ID (illustrative)</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
@@ -1081,14 +1230,14 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Your recorded ID</t>
+          <t>Element ID (the macro reads this)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>FEBAN selection screen</t>
+          <t>FEBAN selection screen (a MODAL dialog on this system, wnd[1])</t>
         </is>
       </c>
       <c r="C6" s="19" t="n"/>
@@ -1099,17 +1248,17 @@
     <row r="7">
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.CompanyCode</t>
+          <t>FEBAN.SelectionWindow</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Company code input field</t>
+          <t>Window the selection fields sit in. wnd[1] here, because FEBAN opens its selection as a popup rather than a full screen</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtFEBA_SEL-BUKRS</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -1117,68 +1266,80 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.HouseBank</t>
+          <t>FEBAN.CompanyCode</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>House bank input field</t>
+          <t>Company code input field</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtFEBA_SEL-HBKID</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtSL_BUKRS-LOW</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.AccountId</t>
+          <t>FEBAN.StatementDateFrom</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Account ID input field</t>
+          <t>Statement date, low value</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtFEBA_SEL-HKTID</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtSL_AZDAT-LOW</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.StatementDateFrom</t>
+          <t>FEBAN.StatementDateTo</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Statement date, low value</t>
+          <t>Statement date, high value</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtFEBA_SEL-AZDAT</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -1186,53 +1347,65 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtSL_AZDAT-HIGH</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.StatementDateTo</t>
+          <t>FEBAN.ExecuteButton</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Statement date, high value</t>
+          <t>Execute, on the popup's own toolbar</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtFEBA_SEL-AZDAT_BIS</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[8]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.ExecuteButton</t>
+          <t>FEBAN.PostExecuteButton</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Execute. Prefer the button ID over sending F8</t>
+          <t>Toolbar button pressed straight after Execute in the recording. Leave blank to skip it -- check what it does before relying on it</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/tbar[1]/btn[8]</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/tbar[1]/btn[14]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="18" t="inlineStr">
@@ -1253,12 +1426,12 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>ALV grid shell holding the statement items</t>
+          <t>ALV grid holding the statement items</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/shellcont/shell/shellcont[1]/shell[1]</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -1266,30 +1439,38 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/shellcont/shell</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.ResultTree</t>
+          <t>FEBAN.Col.Amount</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Navigation tree, if this release shows one</t>
+          <t>Grid column holding the amount</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/shellcont/shell/shellcont[0]/shell</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>KWBTR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="20" t="inlineStr">
@@ -1299,58 +1480,66 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Grid column name holding the value date</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
+          <t>Grid column holding the value date. NOT in the recording -- run modFeban.DumpGridColumns and paste the real name here</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>VALUT</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.Col.Amount</t>
+          <t>FEBAN.Col.Status</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Grid column name holding the amount</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>KWBTR</t>
+          <t>Grid column holding the posting status. VERIFY</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>ESTAT</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.Col.Status</t>
+          <t>FEBAN.Col.DocNumber</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Grid column name holding the posting status</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>ESTAT</t>
+          <t>Grid column holding the FI document number. VERIFY</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -1358,22 +1547,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>BELNR</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.Col.DocNumber</t>
+          <t>FEBAN.Col.PartyName</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Grid column name holding the FI document number</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>BELNR</t>
+          <t>Grid column holding the beneficiary name, if the grid has one</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>optional</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -1381,79 +1574,71 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F19" s="11" t="n"/>
+      <c r="F19" s="23" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>FEBAN.Col.Reference</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Grid column name holding the bank reference or note-to-payee</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>SGTXT</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>ALV export</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>FEBAN item detail</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Feban.Detail.DocNumber</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>FI document field on the statement-item detail screen</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/subSUB_MAIN:SAPLNEW_FEBA:4000/subSUB_APPLICATION:SAPLNEW_FEBA:2200/subAREA1:SAPLNEW_FEBA:2201/txtD2201_BELNR</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Export.ToolbarButton</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Grid toolbar export button function code</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>&amp;MB_EXPORT</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n"/>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>FI document (reached with F2 from the detail screen)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Export.MenuItem</t>
+          <t>Doc.BsegGrid</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Context-menu entry for local file / spreadsheet</t>
+          <t>Line-item grid on the document overview</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>&amp;PC</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -1461,45 +1646,53 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F23" s="11" t="n"/>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/cntlCTRL_CONTAINERBSEG/shellcont/shell</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Export.FormatRadio</t>
+          <t>Doc.Col.Amount</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Radio button for the chosen file format in the format popup</t>
+          <t>Line-item grid column holding the local-currency amount</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/subSUBSCREEN_STEPLOOP:SAPLSPO5:0150/sub:SAPLSPO5:0150/radSPOPLI-SELFLAG[1,0]</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>DMBTR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Export.FormatOkButton</t>
+          <t>Doc.Col.Vendor</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Confirm the format popup</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>wnd[1]/tbar[0]/btn[0]</t>
+          <t>Line-item grid column holding the vendor account. VERIFY</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -1507,56 +1700,64 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F25" s="11" t="n"/>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>LIFNR</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>Save-as dialog</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Doc.ClearingDocField</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Clearing-document field on the line-item detail screen</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/txtBSEG-AUGBL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Save.Path</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Directory field</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>wnd[1]/usr/ctxtDY_PATH</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="n"/>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Cleared items with supplier names</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Save.FileName</t>
+          <t>Cleared.Menu</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>File name field</t>
+          <t>Menu path that produces the cleared-items list from the clearing document. menu[5]/menu[3] in the recording</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -1564,22 +1765,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F28" s="11" t="n"/>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/mbar/menu[5]/menu[3]</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Save.Encoding</t>
+          <t>Cleared.ListAnchor</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Encoding field, where present</t>
+          <t>A label that exists on the cleared-items list, used to confirm the list actually came up</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -1587,148 +1792,156 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F29" s="11" t="n"/>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/lbl[28,7]</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Save.GenerateButton</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Generate / Replace button</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>wnd[1]/tbar[0]/btn[11]</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Classic list export (List &gt; Save/Send &gt; File)</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Export.ListMenu</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Menu path that opens the save-list dialog</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F30" s="11" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>Document drill-down (FB03)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/mbar/menu[0]/menu[3]/menu[1]</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>FB03.DocNumber</t>
+          <t>Export.FormatOkButton</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Document number field</t>
+          <t>Confirm the file-format popup</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/txtRF05L-BELNR</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[0]</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>FB03.CompanyCode</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Company code field</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>wnd[0]/usr/ctxtRF05L-BUKRS</t>
-        </is>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="n"/>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Save-as dialog</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>FB03.FiscalYear</t>
+          <t>Save.Path</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Fiscal year field</t>
+          <t>Directory field</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/txtRF05L-GJAHR</t>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtDY_PATH</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>FB03.ItemGrid</t>
+          <t>Save.FileName</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Line-item ALV grid shell</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>wnd[0]/usr/cntlGRID1/shellcont/shell</t>
+          <t>File name field. The recording left the default in place, so this ID is standard-but-unconfirmed. VERIFY</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>FB03.GosToolbox</t>
+          <t>Save.Encoding</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Services-for-object toolbox on the title bar</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>wnd[0]/titl/shellcont/shell</t>
+          <t>Encoding field, where present. VERIFY</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -1736,76 +1949,247 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F36" s="11" t="n"/>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>Attachment list (OAOR / GOS)</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Save.GenerateButton</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the save. btn[0], not btn[11], on this dialog</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[0]</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Attach.ListGrid</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Attachment list grid shell</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>wnd[1]/usr/cntlCONTAINER/shellcont/shell</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="n"/>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Invoice PDF: regular supplier route</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Attach.SaveButton</t>
+          <t>Invoice.GosToolbox</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Save / export attachment button</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
+          <t>Services-for-object toolbox on the title bar. NOT in the recording -- Audit2.vbs captured no steps. VERIFY</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/titl/shellcont/shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.AttachListGrid</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Attachment-list grid. VERIFY</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/cntlCONTAINER/shellcont/shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.SaveButton</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Save/export button on the attachment list. VERIFY</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>wnd[1]/tbar[0]/btn[5]</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Invoice PDF: Santander SCF confirming route</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>Scf.Step1</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>First step of the confirming-payment route. BLOCKED: Audit2.vbs recorded nothing, so these steps are unknown. Re-record and fill in</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F39" s="11" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="16" t="inlineStr">
+      <c r="F43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>Scf.Step2</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Second step of the confirming-payment route. BLOCKED</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Scf.Step3</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Third step of the confirming-payment route. BLOCKED</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>The recording entered dates as 8 digits with no separators (01092025). The Control sheet's 'SAP date format' is set to DDMMYYYY to match. Do not change it to DMY unless you have checked that this system accepts 01.09.2025 as well.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B41:F41"/>
+  <mergeCells count="13">
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1938,18 +2322,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="27">
         <f>IF($E5="","",DATE(YEAR($E5),MONTH($E5),1))</f>
         <v/>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="27">
         <f>IF($E5="","",EOMONTH($E5,0))</f>
         <v/>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="27" t="n">
         <v>45903</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="28" t="n">
         <v>8072447.42</v>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
@@ -1958,7 +2342,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -1967,7 +2351,7 @@
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
-      <c r="N5" s="26" t="n"/>
+      <c r="N5" s="30" t="n"/>
       <c r="O5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -1979,18 +2363,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="27">
         <f>IF($E6="","",DATE(YEAR($E6),MONTH($E6),1))</f>
         <v/>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="27">
         <f>IF($E6="","",EOMONTH($E6,0))</f>
         <v/>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="27" t="n">
         <v>45912</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="28" t="n">
         <v>2161788.23</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -2003,7 +2387,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -2012,7 +2396,7 @@
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
-      <c r="N6" s="26" t="n"/>
+      <c r="N6" s="30" t="n"/>
       <c r="O6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -2024,18 +2408,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="27">
         <f>IF($E7="","",DATE(YEAR($E7),MONTH($E7),1))</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="27">
         <f>IF($E7="","",EOMONTH($E7,0))</f>
         <v/>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="27" t="n">
         <v>45915</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="28" t="n">
         <v>5988033.6</v>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -2044,7 +2428,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2053,7 +2437,7 @@
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15" t="n"/>
-      <c r="N7" s="26" t="n"/>
+      <c r="N7" s="30" t="n"/>
       <c r="O7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -2065,18 +2449,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="27">
         <f>IF($E8="","",DATE(YEAR($E8),MONTH($E8),1))</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="27">
         <f>IF($E8="","",EOMONTH($E8,0))</f>
         <v/>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="27" t="n">
         <v>45922</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="28" t="n">
         <v>2942842.52</v>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
@@ -2085,7 +2469,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2094,7 +2478,7 @@
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
-      <c r="N8" s="26" t="n"/>
+      <c r="N8" s="30" t="n"/>
       <c r="O8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -2106,18 +2490,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="27">
         <f>IF($E9="","",DATE(YEAR($E9),MONTH($E9),1))</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="27">
         <f>IF($E9="","",EOMONTH($E9,0))</f>
         <v/>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="27" t="n">
         <v>45924</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="28" t="n">
         <v>8617262.93</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -2130,7 +2514,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2139,7 +2523,7 @@
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
-      <c r="N9" s="26" t="n"/>
+      <c r="N9" s="30" t="n"/>
       <c r="O9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -2151,18 +2535,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="27">
         <f>IF($E10="","",DATE(YEAR($E10),MONTH($E10),1))</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="27">
         <f>IF($E10="","",EOMONTH($E10,0))</f>
         <v/>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="27" t="n">
         <v>45925</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="28" t="n">
         <v>2968313.21</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -2175,7 +2559,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2184,7 +2568,7 @@
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
-      <c r="N10" s="26" t="n"/>
+      <c r="N10" s="30" t="n"/>
       <c r="O10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -2196,18 +2580,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="27">
         <f>IF($E11="","",DATE(YEAR($E11),MONTH($E11),1))</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="27">
         <f>IF($E11="","",EOMONTH($E11,0))</f>
         <v/>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="27" t="n">
         <v>45930</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2220,7 +2604,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2229,7 +2613,7 @@
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="15" t="n"/>
       <c r="M11" s="15" t="n"/>
-      <c r="N11" s="26" t="n"/>
+      <c r="N11" s="30" t="n"/>
       <c r="O11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -2241,18 +2625,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="27">
         <f>IF($E12="","",DATE(YEAR($E12),MONTH($E12),1))</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="27">
         <f>IF($E12="","",EOMONTH($E12,0))</f>
         <v/>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="27" t="n">
         <v>45931</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="28" t="n">
         <v>4483676.08</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -2265,7 +2649,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2274,7 +2658,7 @@
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
-      <c r="N12" s="26" t="n"/>
+      <c r="N12" s="30" t="n"/>
       <c r="O12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -2286,18 +2670,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="27">
         <f>IF($E13="","",DATE(YEAR($E13),MONTH($E13),1))</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="27">
         <f>IF($E13="","",EOMONTH($E13,0))</f>
         <v/>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="27" t="n">
         <v>45933</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="28" t="n">
         <v>3412038.97</v>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -2306,7 +2690,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2315,7 +2699,7 @@
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
-      <c r="N13" s="26" t="n"/>
+      <c r="N13" s="30" t="n"/>
       <c r="O13" s="15" t="n"/>
     </row>
     <row r="14">
@@ -2327,18 +2711,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="27">
         <f>IF($E14="","",DATE(YEAR($E14),MONTH($E14),1))</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="27">
         <f>IF($E14="","",EOMONTH($E14,0))</f>
         <v/>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="27" t="n">
         <v>45943</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="28" t="n">
         <v>3385329.45</v>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
@@ -2347,7 +2731,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2356,7 +2740,7 @@
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
-      <c r="N14" s="26" t="n"/>
+      <c r="N14" s="30" t="n"/>
       <c r="O14" s="15" t="n"/>
     </row>
     <row r="15">
@@ -2368,18 +2752,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="27">
         <f>IF($E15="","",DATE(YEAR($E15),MONTH($E15),1))</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="27">
         <f>IF($E15="","",EOMONTH($E15,0))</f>
         <v/>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="27" t="n">
         <v>45950</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="28" t="n">
         <v>4898587.92</v>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
@@ -2388,7 +2772,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2397,7 +2781,7 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="15" t="n"/>
-      <c r="N15" s="26" t="n"/>
+      <c r="N15" s="30" t="n"/>
       <c r="O15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -2409,18 +2793,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="27">
         <f>IF($E16="","",DATE(YEAR($E16),MONTH($E16),1))</f>
         <v/>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="27">
         <f>IF($E16="","",EOMONTH($E16,0))</f>
         <v/>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="27" t="n">
         <v>45954</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="28" t="n">
         <v>3480924.53</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -2433,7 +2817,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>date_stored_as_text; party_whitespace_cleaned</t>
         </is>
@@ -2442,7 +2826,7 @@
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
-      <c r="N16" s="26" t="n"/>
+      <c r="N16" s="30" t="n"/>
       <c r="O16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -2454,18 +2838,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="27">
         <f>IF($E17="","",DATE(YEAR($E17),MONTH($E17),1))</f>
         <v/>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="27">
         <f>IF($E17="","",EOMONTH($E17,0))</f>
         <v/>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="27" t="n">
         <v>45957</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="28" t="n">
         <v>2614260.03</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -2478,7 +2862,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2487,7 +2871,7 @@
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
-      <c r="N17" s="26" t="n"/>
+      <c r="N17" s="30" t="n"/>
       <c r="O17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -2499,18 +2883,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="27">
         <f>IF($E18="","",DATE(YEAR($E18),MONTH($E18),1))</f>
         <v/>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="27">
         <f>IF($E18="","",EOMONTH($E18,0))</f>
         <v/>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="27" t="n">
         <v>45961</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -2523,7 +2907,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2532,7 +2916,7 @@
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
-      <c r="N18" s="26" t="n"/>
+      <c r="N18" s="30" t="n"/>
       <c r="O18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -2544,18 +2928,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="27">
         <f>IF($E19="","",DATE(YEAR($E19),MONTH($E19),1))</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="27">
         <f>IF($E19="","",EOMONTH($E19,0))</f>
         <v/>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="27" t="n">
         <v>45961</v>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="28" t="n">
         <v>3317511.83</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -2568,7 +2952,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2577,7 +2961,7 @@
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
-      <c r="N19" s="26" t="n"/>
+      <c r="N19" s="30" t="n"/>
       <c r="O19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -2589,18 +2973,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="27">
         <f>IF($E20="","",DATE(YEAR($E20),MONTH($E20),1))</f>
         <v/>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="27">
         <f>IF($E20="","",EOMONTH($E20,0))</f>
         <v/>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="27" t="n">
         <v>45964</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="28" t="n">
         <v>3724798.28</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -2613,12 +2997,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr"/>
+      <c r="I20" s="29" t="inlineStr"/>
       <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
-      <c r="N20" s="26" t="n"/>
+      <c r="N20" s="30" t="n"/>
       <c r="O20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -2630,18 +3014,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="27">
         <f>IF($E21="","",DATE(YEAR($E21),MONTH($E21),1))</f>
         <v/>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="27">
         <f>IF($E21="","",EOMONTH($E21,0))</f>
         <v/>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="27" t="n">
         <v>45966</v>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="F21" s="28" t="n">
         <v>5044035.13</v>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
@@ -2650,7 +3034,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2659,7 +3043,7 @@
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15" t="n"/>
-      <c r="N21" s="26" t="n"/>
+      <c r="N21" s="30" t="n"/>
       <c r="O21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -2671,18 +3055,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="27">
         <f>IF($E22="","",DATE(YEAR($E22),MONTH($E22),1))</f>
         <v/>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="27">
         <f>IF($E22="","",EOMONTH($E22,0))</f>
         <v/>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="27" t="n">
         <v>45978</v>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="28" t="n">
         <v>5245536.51</v>
       </c>
       <c r="G22" s="10" t="inlineStr"/>
@@ -2691,7 +3075,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I22" s="25" t="inlineStr">
+      <c r="I22" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2700,7 +3084,7 @@
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
-      <c r="N22" s="26" t="n"/>
+      <c r="N22" s="30" t="n"/>
       <c r="O22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -2712,18 +3096,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="27">
         <f>IF($E23="","",DATE(YEAR($E23),MONTH($E23),1))</f>
         <v/>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="27">
         <f>IF($E23="","",EOMONTH($E23,0))</f>
         <v/>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="27" t="n">
         <v>45989</v>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="28" t="n">
         <v>4173936.71</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -2736,7 +3120,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2745,7 +3129,7 @@
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
-      <c r="N23" s="26" t="n"/>
+      <c r="N23" s="30" t="n"/>
       <c r="O23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -2757,18 +3141,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="27">
         <f>IF($E24="","",DATE(YEAR($E24),MONTH($E24),1))</f>
         <v/>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="27">
         <f>IF($E24="","",EOMONTH($E24,0))</f>
         <v/>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="27" t="n">
         <v>45989</v>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -2781,7 +3165,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="29" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2790,7 +3174,7 @@
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
-      <c r="N24" s="26" t="n"/>
+      <c r="N24" s="30" t="n"/>
       <c r="O24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -2802,18 +3186,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="27">
         <f>IF($E25="","",DATE(YEAR($E25),MONTH($E25),1))</f>
         <v/>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="27">
         <f>IF($E25="","",EOMONTH($E25,0))</f>
         <v/>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="27" t="n">
         <v>46020</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="28" t="n">
         <v>2828677.68</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -2826,7 +3210,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I25" s="25" t="inlineStr">
+      <c r="I25" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2835,7 +3219,7 @@
       <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n"/>
       <c r="M25" s="15" t="n"/>
-      <c r="N25" s="26" t="n"/>
+      <c r="N25" s="30" t="n"/>
       <c r="O25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -2847,18 +3231,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="27">
         <f>IF($E26="","",DATE(YEAR($E26),MONTH($E26),1))</f>
         <v/>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="27">
         <f>IF($E26="","",EOMONTH($E26,0))</f>
         <v/>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="27" t="n">
         <v>46022</v>
       </c>
-      <c r="F26" s="24" t="n">
+      <c r="F26" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2871,7 +3255,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I26" s="25" t="inlineStr">
+      <c r="I26" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2880,7 +3264,7 @@
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
-      <c r="N26" s="26" t="n"/>
+      <c r="N26" s="30" t="n"/>
       <c r="O26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -2892,18 +3276,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="27">
         <f>IF($E27="","",DATE(YEAR($E27),MONTH($E27),1))</f>
         <v/>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="27">
         <f>IF($E27="","",EOMONTH($E27,0))</f>
         <v/>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E27" s="27" t="n">
         <v>46022</v>
       </c>
-      <c r="F27" s="24" t="n">
+      <c r="F27" s="28" t="n">
         <v>2233241.99</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -2916,7 +3300,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I27" s="25" t="inlineStr">
+      <c r="I27" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2925,7 +3309,7 @@
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15" t="n"/>
-      <c r="N27" s="26" t="n"/>
+      <c r="N27" s="30" t="n"/>
       <c r="O27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -2937,18 +3321,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="27">
         <f>IF($E28="","",DATE(YEAR($E28),MONTH($E28),1))</f>
         <v/>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="27">
         <f>IF($E28="","",EOMONTH($E28,0))</f>
         <v/>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="27" t="n">
         <v>46024</v>
       </c>
-      <c r="F28" s="24" t="n">
+      <c r="F28" s="28" t="n">
         <v>3489077.98</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -2961,7 +3345,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I28" s="25" t="inlineStr">
+      <c r="I28" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -2970,7 +3354,7 @@
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
-      <c r="N28" s="26" t="n"/>
+      <c r="N28" s="30" t="n"/>
       <c r="O28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -2982,18 +3366,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="27">
         <f>IF($E29="","",DATE(YEAR($E29),MONTH($E29),1))</f>
         <v/>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="27">
         <f>IF($E29="","",EOMONTH($E29,0))</f>
         <v/>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E29" s="27" t="n">
         <v>46028</v>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="28" t="n">
         <v>4395299.21</v>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -3002,7 +3386,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I29" s="25" t="inlineStr">
+      <c r="I29" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3011,7 +3395,7 @@
       <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
-      <c r="N29" s="26" t="n"/>
+      <c r="N29" s="30" t="n"/>
       <c r="O29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -3023,18 +3407,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="27">
         <f>IF($E30="","",DATE(YEAR($E30),MONTH($E30),1))</f>
         <v/>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="27">
         <f>IF($E30="","",EOMONTH($E30,0))</f>
         <v/>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="27" t="n">
         <v>46031</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="28" t="n">
         <v>8800991.4</v>
       </c>
       <c r="G30" s="10" t="inlineStr"/>
@@ -3043,7 +3427,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I30" s="25" t="inlineStr">
+      <c r="I30" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3052,7 +3436,7 @@
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
       <c r="M30" s="15" t="n"/>
-      <c r="N30" s="26" t="n"/>
+      <c r="N30" s="30" t="n"/>
       <c r="O30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -3064,18 +3448,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="27">
         <f>IF($E31="","",DATE(YEAR($E31),MONTH($E31),1))</f>
         <v/>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="27">
         <f>IF($E31="","",EOMONTH($E31,0))</f>
         <v/>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="27" t="n">
         <v>46038</v>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="28" t="n">
         <v>6502110.67</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3088,7 +3472,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I31" s="25" t="inlineStr">
+      <c r="I31" s="29" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3097,7 +3481,7 @@
       <c r="K31" s="15" t="n"/>
       <c r="L31" s="15" t="n"/>
       <c r="M31" s="15" t="n"/>
-      <c r="N31" s="26" t="n"/>
+      <c r="N31" s="30" t="n"/>
       <c r="O31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -3109,18 +3493,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="27">
         <f>IF($E32="","",DATE(YEAR($E32),MONTH($E32),1))</f>
         <v/>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="27">
         <f>IF($E32="","",EOMONTH($E32,0))</f>
         <v/>
       </c>
-      <c r="E32" s="23" t="n">
+      <c r="E32" s="27" t="n">
         <v>46051</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="28" t="n">
         <v>3463573.21</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -3133,7 +3517,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I32" s="25" t="inlineStr">
+      <c r="I32" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3142,7 +3526,7 @@
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
-      <c r="N32" s="26" t="n"/>
+      <c r="N32" s="30" t="n"/>
       <c r="O32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -3154,18 +3538,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C33" s="23">
+      <c r="C33" s="27">
         <f>IF($E33="","",DATE(YEAR($E33),MONTH($E33),1))</f>
         <v/>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="27">
         <f>IF($E33="","",EOMONTH($E33,0))</f>
         <v/>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="27" t="n">
         <v>46052</v>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -3178,7 +3562,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I33" s="25" t="inlineStr">
+      <c r="I33" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3187,7 +3571,7 @@
       <c r="K33" s="15" t="n"/>
       <c r="L33" s="15" t="n"/>
       <c r="M33" s="15" t="n"/>
-      <c r="N33" s="26" t="n"/>
+      <c r="N33" s="30" t="n"/>
       <c r="O33" s="15" t="n"/>
     </row>
     <row r="34">
@@ -3199,18 +3583,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="27">
         <f>IF($E34="","",DATE(YEAR($E34),MONTH($E34),1))</f>
         <v/>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="27">
         <f>IF($E34="","",EOMONTH($E34,0))</f>
         <v/>
       </c>
-      <c r="E34" s="23" t="n">
+      <c r="E34" s="27" t="n">
         <v>46055</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="28" t="n">
         <v>3679179.76</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -3223,7 +3607,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I34" s="25" t="inlineStr">
+      <c r="I34" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -3232,7 +3616,7 @@
       <c r="K34" s="15" t="n"/>
       <c r="L34" s="15" t="n"/>
       <c r="M34" s="15" t="n"/>
-      <c r="N34" s="26" t="n"/>
+      <c r="N34" s="30" t="n"/>
       <c r="O34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -3244,18 +3628,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="27">
         <f>IF($E35="","",DATE(YEAR($E35),MONTH($E35),1))</f>
         <v/>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="27">
         <f>IF($E35="","",EOMONTH($E35,0))</f>
         <v/>
       </c>
-      <c r="E35" s="23" t="n">
+      <c r="E35" s="27" t="n">
         <v>46057</v>
       </c>
-      <c r="F35" s="24" t="n">
+      <c r="F35" s="28" t="n">
         <v>3674499.52</v>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
@@ -3264,7 +3648,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I35" s="25" t="inlineStr">
+      <c r="I35" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3273,7 +3657,7 @@
       <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="15" t="n"/>
-      <c r="N35" s="26" t="n"/>
+      <c r="N35" s="30" t="n"/>
       <c r="O35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -3285,18 +3669,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="27">
         <f>IF($E36="","",DATE(YEAR($E36),MONTH($E36),1))</f>
         <v/>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="27">
         <f>IF($E36="","",EOMONTH($E36,0))</f>
         <v/>
       </c>
-      <c r="E36" s="23" t="n">
+      <c r="E36" s="27" t="n">
         <v>46080</v>
       </c>
-      <c r="F36" s="24" t="n">
+      <c r="F36" s="28" t="n">
         <v>6558159.12</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -3309,7 +3693,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I36" s="25" t="inlineStr">
+      <c r="I36" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3318,7 +3702,7 @@
       <c r="K36" s="15" t="n"/>
       <c r="L36" s="15" t="n"/>
       <c r="M36" s="15" t="n"/>
-      <c r="N36" s="26" t="n"/>
+      <c r="N36" s="30" t="n"/>
       <c r="O36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -3330,18 +3714,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C37" s="23">
+      <c r="C37" s="27">
         <f>IF($E37="","",DATE(YEAR($E37),MONTH($E37),1))</f>
         <v/>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="27">
         <f>IF($E37="","",EOMONTH($E37,0))</f>
         <v/>
       </c>
-      <c r="E37" s="23" t="n">
+      <c r="E37" s="27" t="n">
         <v>46080</v>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -3354,7 +3738,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I37" s="25" t="inlineStr">
+      <c r="I37" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3363,7 +3747,7 @@
       <c r="K37" s="15" t="n"/>
       <c r="L37" s="15" t="n"/>
       <c r="M37" s="15" t="n"/>
-      <c r="N37" s="26" t="n"/>
+      <c r="N37" s="30" t="n"/>
       <c r="O37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -3375,18 +3759,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="27">
         <f>IF($E38="","",DATE(YEAR($E38),MONTH($E38),1))</f>
         <v/>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="27">
         <f>IF($E38="","",EOMONTH($E38,0))</f>
         <v/>
       </c>
-      <c r="E38" s="23" t="n">
+      <c r="E38" s="27" t="n">
         <v>46083</v>
       </c>
-      <c r="F38" s="24" t="n">
+      <c r="F38" s="28" t="n">
         <v>3562528.89</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3399,7 +3783,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I38" s="25" t="inlineStr">
+      <c r="I38" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3408,7 +3792,7 @@
       <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n"/>
       <c r="M38" s="15" t="n"/>
-      <c r="N38" s="26" t="n"/>
+      <c r="N38" s="30" t="n"/>
       <c r="O38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -3420,18 +3804,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="27">
         <f>IF($E39="","",DATE(YEAR($E39),MONTH($E39),1))</f>
         <v/>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="27">
         <f>IF($E39="","",EOMONTH($E39,0))</f>
         <v/>
       </c>
-      <c r="E39" s="23" t="n">
+      <c r="E39" s="27" t="n">
         <v>46085</v>
       </c>
-      <c r="F39" s="24" t="n">
+      <c r="F39" s="28" t="n">
         <v>8557737.25</v>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
@@ -3440,7 +3824,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I39" s="25" t="inlineStr">
+      <c r="I39" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -3449,7 +3833,7 @@
       <c r="K39" s="15" t="n"/>
       <c r="L39" s="15" t="n"/>
       <c r="M39" s="15" t="n"/>
-      <c r="N39" s="26" t="n"/>
+      <c r="N39" s="30" t="n"/>
       <c r="O39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -3461,18 +3845,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C40" s="23">
+      <c r="C40" s="27">
         <f>IF($E40="","",DATE(YEAR($E40),MONTH($E40),1))</f>
         <v/>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="27">
         <f>IF($E40="","",EOMONTH($E40,0))</f>
         <v/>
       </c>
-      <c r="E40" s="23" t="n">
+      <c r="E40" s="27" t="n">
         <v>46093</v>
       </c>
-      <c r="F40" s="24" t="n">
+      <c r="F40" s="28" t="n">
         <v>2301959.84</v>
       </c>
       <c r="G40" s="10" t="inlineStr"/>
@@ -3481,7 +3865,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I40" s="25" t="inlineStr">
+      <c r="I40" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -3490,7 +3874,7 @@
       <c r="K40" s="15" t="n"/>
       <c r="L40" s="15" t="n"/>
       <c r="M40" s="15" t="n"/>
-      <c r="N40" s="26" t="n"/>
+      <c r="N40" s="30" t="n"/>
       <c r="O40" s="15" t="n"/>
     </row>
     <row r="41">
@@ -3502,18 +3886,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C41" s="23">
+      <c r="C41" s="27">
         <f>IF($E41="","",DATE(YEAR($E41),MONTH($E41),1))</f>
         <v/>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="27">
         <f>IF($E41="","",EOMONTH($E41,0))</f>
         <v/>
       </c>
-      <c r="E41" s="23" t="n">
+      <c r="E41" s="27" t="n">
         <v>46108</v>
       </c>
-      <c r="F41" s="24" t="n">
+      <c r="F41" s="28" t="n">
         <v>5989486.48</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -3526,7 +3910,7 @@
           <t>DS Smith Paper Limited</t>
         </is>
       </c>
-      <c r="I41" s="25" t="inlineStr">
+      <c r="I41" s="29" t="inlineStr">
         <is>
           <t>ref_holds_a_party_name_not_a_transaction_description; party_whitespace_cleaned</t>
         </is>
@@ -3535,7 +3919,7 @@
       <c r="K41" s="15" t="n"/>
       <c r="L41" s="15" t="n"/>
       <c r="M41" s="15" t="n"/>
-      <c r="N41" s="26" t="n"/>
+      <c r="N41" s="30" t="n"/>
       <c r="O41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -3547,18 +3931,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="27">
         <f>IF($E42="","",DATE(YEAR($E42),MONTH($E42),1))</f>
         <v/>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="27">
         <f>IF($E42="","",EOMONTH($E42,0))</f>
         <v/>
       </c>
-      <c r="E42" s="23" t="n">
+      <c r="E42" s="27" t="n">
         <v>46112</v>
       </c>
-      <c r="F42" s="24" t="n">
+      <c r="F42" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -3571,12 +3955,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I42" s="25" t="inlineStr"/>
+      <c r="I42" s="29" t="inlineStr"/>
       <c r="J42" s="15" t="n"/>
       <c r="K42" s="15" t="n"/>
       <c r="L42" s="15" t="n"/>
       <c r="M42" s="15" t="n"/>
-      <c r="N42" s="26" t="n"/>
+      <c r="N42" s="30" t="n"/>
       <c r="O42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -3588,18 +3972,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="27">
         <f>IF($E43="","",DATE(YEAR($E43),MONTH($E43),1))</f>
         <v/>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="27">
         <f>IF($E43="","",EOMONTH($E43,0))</f>
         <v/>
       </c>
-      <c r="E43" s="23" t="n">
+      <c r="E43" s="27" t="n">
         <v>46113</v>
       </c>
-      <c r="F43" s="24" t="n">
+      <c r="F43" s="28" t="n">
         <v>3316944.84</v>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -3612,12 +3996,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I43" s="25" t="inlineStr"/>
+      <c r="I43" s="29" t="inlineStr"/>
       <c r="J43" s="15" t="n"/>
       <c r="K43" s="15" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15" t="n"/>
-      <c r="N43" s="26" t="n"/>
+      <c r="N43" s="30" t="n"/>
       <c r="O43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -3629,18 +4013,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="27">
         <f>IF($E44="","",DATE(YEAR($E44),MONTH($E44),1))</f>
         <v/>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="27">
         <f>IF($E44="","",EOMONTH($E44,0))</f>
         <v/>
       </c>
-      <c r="E44" s="23" t="n">
+      <c r="E44" s="27" t="n">
         <v>46128</v>
       </c>
-      <c r="F44" s="24" t="n">
+      <c r="F44" s="28" t="n">
         <v>2611670.69</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -3653,12 +4037,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I44" s="25" t="inlineStr"/>
+      <c r="I44" s="29" t="inlineStr"/>
       <c r="J44" s="15" t="n"/>
       <c r="K44" s="15" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15" t="n"/>
-      <c r="N44" s="26" t="n"/>
+      <c r="N44" s="30" t="n"/>
       <c r="O44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -3670,18 +4054,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C45" s="23">
+      <c r="C45" s="27">
         <f>IF($E45="","",DATE(YEAR($E45),MONTH($E45),1))</f>
         <v/>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="27">
         <f>IF($E45="","",EOMONTH($E45,0))</f>
         <v/>
       </c>
-      <c r="E45" s="23" t="n">
+      <c r="E45" s="27" t="n">
         <v>46129</v>
       </c>
-      <c r="F45" s="24" t="n">
+      <c r="F45" s="28" t="n">
         <v>4996002.96</v>
       </c>
       <c r="G45" s="10" t="inlineStr"/>
@@ -3690,7 +4074,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I45" s="25" t="inlineStr">
+      <c r="I45" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -3699,7 +4083,7 @@
       <c r="K45" s="15" t="n"/>
       <c r="L45" s="15" t="n"/>
       <c r="M45" s="15" t="n"/>
-      <c r="N45" s="26" t="n"/>
+      <c r="N45" s="30" t="n"/>
       <c r="O45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -3711,18 +4095,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C46" s="23">
+      <c r="C46" s="27">
         <f>IF($E46="","",DATE(YEAR($E46),MONTH($E46),1))</f>
         <v/>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="27">
         <f>IF($E46="","",EOMONTH($E46,0))</f>
         <v/>
       </c>
-      <c r="E46" s="23" t="n">
+      <c r="E46" s="27" t="n">
         <v>46135</v>
       </c>
-      <c r="F46" s="24" t="n">
+      <c r="F46" s="28" t="n">
         <v>2334786.77</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -3735,7 +4119,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I46" s="25" t="inlineStr">
+      <c r="I46" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3744,7 +4128,7 @@
       <c r="K46" s="15" t="n"/>
       <c r="L46" s="15" t="n"/>
       <c r="M46" s="15" t="n"/>
-      <c r="N46" s="26" t="n"/>
+      <c r="N46" s="30" t="n"/>
       <c r="O46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -3756,18 +4140,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="27">
         <f>IF($E47="","",DATE(YEAR($E47),MONTH($E47),1))</f>
         <v/>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="27">
         <f>IF($E47="","",EOMONTH($E47,0))</f>
         <v/>
       </c>
-      <c r="E47" s="23" t="n">
+      <c r="E47" s="27" t="n">
         <v>46139</v>
       </c>
-      <c r="F47" s="24" t="n">
+      <c r="F47" s="28" t="n">
         <v>2598639.67</v>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -3780,7 +4164,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I47" s="25" t="inlineStr">
+      <c r="I47" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3789,7 +4173,7 @@
       <c r="K47" s="15" t="n"/>
       <c r="L47" s="15" t="n"/>
       <c r="M47" s="15" t="n"/>
-      <c r="N47" s="26" t="n"/>
+      <c r="N47" s="30" t="n"/>
       <c r="O47" s="15" t="n"/>
     </row>
     <row r="48">
@@ -3801,18 +4185,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C48" s="23">
+      <c r="C48" s="27">
         <f>IF($E48="","",DATE(YEAR($E48),MONTH($E48),1))</f>
         <v/>
       </c>
-      <c r="D48" s="23">
+      <c r="D48" s="27">
         <f>IF($E48="","",EOMONTH($E48,0))</f>
         <v/>
       </c>
-      <c r="E48" s="23" t="n">
+      <c r="E48" s="27" t="n">
         <v>46142</v>
       </c>
-      <c r="F48" s="24" t="n">
+      <c r="F48" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -3825,12 +4209,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I48" s="25" t="inlineStr"/>
+      <c r="I48" s="29" t="inlineStr"/>
       <c r="J48" s="15" t="n"/>
       <c r="K48" s="15" t="n"/>
       <c r="L48" s="15" t="n"/>
       <c r="M48" s="15" t="n"/>
-      <c r="N48" s="26" t="n"/>
+      <c r="N48" s="30" t="n"/>
       <c r="O48" s="15" t="n"/>
     </row>
     <row r="49">
@@ -3842,18 +4226,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C49" s="23">
+      <c r="C49" s="27">
         <f>IF($E49="","",DATE(YEAR($E49),MONTH($E49),1))</f>
         <v/>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="27">
         <f>IF($E49="","",EOMONTH($E49,0))</f>
         <v/>
       </c>
-      <c r="E49" s="23" t="n">
+      <c r="E49" s="27" t="n">
         <v>46142</v>
       </c>
-      <c r="F49" s="24" t="n">
+      <c r="F49" s="28" t="n">
         <v>3232025.51</v>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -3866,7 +4250,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I49" s="25" t="inlineStr">
+      <c r="I49" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3875,7 +4259,7 @@
       <c r="K49" s="15" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15" t="n"/>
-      <c r="N49" s="26" t="n"/>
+      <c r="N49" s="30" t="n"/>
       <c r="O49" s="15" t="n"/>
     </row>
     <row r="50">
@@ -3887,18 +4271,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C50" s="23">
+      <c r="C50" s="27">
         <f>IF($E50="","",DATE(YEAR($E50),MONTH($E50),1))</f>
         <v/>
       </c>
-      <c r="D50" s="23">
+      <c r="D50" s="27">
         <f>IF($E50="","",EOMONTH($E50,0))</f>
         <v/>
       </c>
-      <c r="E50" s="23" t="n">
+      <c r="E50" s="27" t="n">
         <v>46147</v>
       </c>
-      <c r="F50" s="24" t="n">
+      <c r="F50" s="28" t="n">
         <v>3723586.74</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -3911,12 +4295,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I50" s="25" t="inlineStr"/>
+      <c r="I50" s="29" t="inlineStr"/>
       <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="n"/>
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15" t="n"/>
-      <c r="N50" s="26" t="n"/>
+      <c r="N50" s="30" t="n"/>
       <c r="O50" s="15" t="n"/>
     </row>
     <row r="51">
@@ -3928,18 +4312,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C51" s="23">
+      <c r="C51" s="27">
         <f>IF($E51="","",DATE(YEAR($E51),MONTH($E51),1))</f>
         <v/>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="27">
         <f>IF($E51="","",EOMONTH($E51,0))</f>
         <v/>
       </c>
-      <c r="E51" s="23" t="n">
+      <c r="E51" s="27" t="n">
         <v>46150</v>
       </c>
-      <c r="F51" s="24" t="n">
+      <c r="F51" s="28" t="n">
         <v>5009315.83</v>
       </c>
       <c r="G51" s="10" t="inlineStr"/>
@@ -3948,7 +4332,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I51" s="25" t="inlineStr">
+      <c r="I51" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3957,7 +4341,7 @@
       <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15" t="n"/>
-      <c r="N51" s="26" t="n"/>
+      <c r="N51" s="30" t="n"/>
       <c r="O51" s="15" t="n"/>
     </row>
     <row r="52">
@@ -3969,18 +4353,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C52" s="23">
+      <c r="C52" s="27">
         <f>IF($E52="","",DATE(YEAR($E52),MONTH($E52),1))</f>
         <v/>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="27">
         <f>IF($E52="","",EOMONTH($E52,0))</f>
         <v/>
       </c>
-      <c r="E52" s="23" t="n">
+      <c r="E52" s="27" t="n">
         <v>46157</v>
       </c>
-      <c r="F52" s="24" t="n">
+      <c r="F52" s="28" t="n">
         <v>4340970.4</v>
       </c>
       <c r="G52" s="10" t="inlineStr"/>
@@ -3989,7 +4373,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I52" s="25" t="inlineStr">
+      <c r="I52" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3998,7 +4382,7 @@
       <c r="K52" s="15" t="n"/>
       <c r="L52" s="15" t="n"/>
       <c r="M52" s="15" t="n"/>
-      <c r="N52" s="26" t="n"/>
+      <c r="N52" s="30" t="n"/>
       <c r="O52" s="15" t="n"/>
     </row>
     <row r="53">
@@ -4010,18 +4394,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C53" s="23">
+      <c r="C53" s="27">
         <f>IF($E53="","",DATE(YEAR($E53),MONTH($E53),1))</f>
         <v/>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="27">
         <f>IF($E53="","",EOMONTH($E53,0))</f>
         <v/>
       </c>
-      <c r="E53" s="23" t="n">
+      <c r="E53" s="27" t="n">
         <v>46170</v>
       </c>
-      <c r="F53" s="24" t="n">
+      <c r="F53" s="28" t="n">
         <v>2400509.91</v>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -4034,7 +4418,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I53" s="25" t="inlineStr">
+      <c r="I53" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4043,7 +4427,7 @@
       <c r="K53" s="15" t="n"/>
       <c r="L53" s="15" t="n"/>
       <c r="M53" s="15" t="n"/>
-      <c r="N53" s="26" t="n"/>
+      <c r="N53" s="30" t="n"/>
       <c r="O53" s="15" t="n"/>
     </row>
     <row r="54">
@@ -4055,18 +4439,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="27">
         <f>IF($E54="","",DATE(YEAR($E54),MONTH($E54),1))</f>
         <v/>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="27">
         <f>IF($E54="","",EOMONTH($E54,0))</f>
         <v/>
       </c>
-      <c r="E54" s="23" t="n">
+      <c r="E54" s="27" t="n">
         <v>46171</v>
       </c>
-      <c r="F54" s="24" t="n">
+      <c r="F54" s="28" t="n">
         <v>3444449.93</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -4079,7 +4463,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I54" s="25" t="inlineStr">
+      <c r="I54" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4088,7 +4472,7 @@
       <c r="K54" s="15" t="n"/>
       <c r="L54" s="15" t="n"/>
       <c r="M54" s="15" t="n"/>
-      <c r="N54" s="26" t="n"/>
+      <c r="N54" s="30" t="n"/>
       <c r="O54" s="15" t="n"/>
     </row>
     <row r="55">
@@ -4100,18 +4484,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C55" s="23">
+      <c r="C55" s="27">
         <f>IF($E55="","",DATE(YEAR($E55),MONTH($E55),1))</f>
         <v/>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="27">
         <f>IF($E55="","",EOMONTH($E55,0))</f>
         <v/>
       </c>
-      <c r="E55" s="23" t="n">
+      <c r="E55" s="27" t="n">
         <v>46171</v>
       </c>
-      <c r="F55" s="24" t="n">
+      <c r="F55" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -4124,12 +4508,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I55" s="25" t="inlineStr"/>
+      <c r="I55" s="29" t="inlineStr"/>
       <c r="J55" s="15" t="n"/>
       <c r="K55" s="15" t="n"/>
       <c r="L55" s="15" t="n"/>
       <c r="M55" s="15" t="n"/>
-      <c r="N55" s="26" t="n"/>
+      <c r="N55" s="30" t="n"/>
       <c r="O55" s="15" t="n"/>
     </row>
     <row r="56">
@@ -4141,18 +4525,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C56" s="23">
+      <c r="C56" s="27">
         <f>IF($E56="","",DATE(YEAR($E56),MONTH($E56),1))</f>
         <v/>
       </c>
-      <c r="D56" s="23">
+      <c r="D56" s="27">
         <f>IF($E56="","",EOMONTH($E56,0))</f>
         <v/>
       </c>
-      <c r="E56" s="23" t="n">
+      <c r="E56" s="27" t="n">
         <v>46176</v>
       </c>
-      <c r="F56" s="24" t="n">
+      <c r="F56" s="28" t="n">
         <v>5210470.59</v>
       </c>
       <c r="G56" s="10" t="inlineStr"/>
@@ -4161,7 +4545,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I56" s="25" t="inlineStr">
+      <c r="I56" s="29" t="inlineStr">
         <is>
           <t>ref_typo_corrected_from:ACH PYMTS - LCL BULK FNG; no_named_beneficiary</t>
         </is>
@@ -4170,7 +4554,7 @@
       <c r="K56" s="15" t="n"/>
       <c r="L56" s="15" t="n"/>
       <c r="M56" s="15" t="n"/>
-      <c r="N56" s="26" t="n"/>
+      <c r="N56" s="30" t="n"/>
       <c r="O56" s="15" t="n"/>
     </row>
     <row r="57">
@@ -4182,18 +4566,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C57" s="23">
+      <c r="C57" s="27">
         <f>IF($E57="","",DATE(YEAR($E57),MONTH($E57),1))</f>
         <v/>
       </c>
-      <c r="D57" s="23">
+      <c r="D57" s="27">
         <f>IF($E57="","",EOMONTH($E57,0))</f>
         <v/>
       </c>
-      <c r="E57" s="23" t="n">
+      <c r="E57" s="27" t="n">
         <v>46177</v>
       </c>
-      <c r="F57" s="24" t="n">
+      <c r="F57" s="28" t="n">
         <v>4006482.03</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -4206,12 +4590,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I57" s="25" t="inlineStr"/>
+      <c r="I57" s="29" t="inlineStr"/>
       <c r="J57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
       <c r="L57" s="15" t="n"/>
       <c r="M57" s="15" t="n"/>
-      <c r="N57" s="26" t="n"/>
+      <c r="N57" s="30" t="n"/>
       <c r="O57" s="15" t="n"/>
     </row>
     <row r="58">
@@ -4223,18 +4607,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C58" s="23">
+      <c r="C58" s="27">
         <f>IF($E58="","",DATE(YEAR($E58),MONTH($E58),1))</f>
         <v/>
       </c>
-      <c r="D58" s="23">
+      <c r="D58" s="27">
         <f>IF($E58="","",EOMONTH($E58,0))</f>
         <v/>
       </c>
-      <c r="E58" s="23" t="n">
+      <c r="E58" s="27" t="n">
         <v>46184</v>
       </c>
-      <c r="F58" s="24" t="n">
+      <c r="F58" s="28" t="n">
         <v>6226088.99</v>
       </c>
       <c r="G58" s="10" t="inlineStr"/>
@@ -4243,7 +4627,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I58" s="25" t="inlineStr">
+      <c r="I58" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4252,7 +4636,7 @@
       <c r="K58" s="15" t="n"/>
       <c r="L58" s="15" t="n"/>
       <c r="M58" s="15" t="n"/>
-      <c r="N58" s="26" t="n"/>
+      <c r="N58" s="30" t="n"/>
       <c r="O58" s="15" t="n"/>
     </row>
     <row r="59">
@@ -4264,18 +4648,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C59" s="23">
+      <c r="C59" s="27">
         <f>IF($E59="","",DATE(YEAR($E59),MONTH($E59),1))</f>
         <v/>
       </c>
-      <c r="D59" s="23">
+      <c r="D59" s="27">
         <f>IF($E59="","",EOMONTH($E59,0))</f>
         <v/>
       </c>
-      <c r="E59" s="23" t="n">
+      <c r="E59" s="27" t="n">
         <v>46185</v>
       </c>
-      <c r="F59" s="24" t="n">
+      <c r="F59" s="28" t="n">
         <v>2292348.71</v>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -4288,7 +4672,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I59" s="25" t="inlineStr">
+      <c r="I59" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4297,7 +4681,7 @@
       <c r="K59" s="15" t="n"/>
       <c r="L59" s="15" t="n"/>
       <c r="M59" s="15" t="n"/>
-      <c r="N59" s="26" t="n"/>
+      <c r="N59" s="30" t="n"/>
       <c r="O59" s="15" t="n"/>
     </row>
     <row r="60">
@@ -4309,18 +4693,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C60" s="23">
+      <c r="C60" s="27">
         <f>IF($E60="","",DATE(YEAR($E60),MONTH($E60),1))</f>
         <v/>
       </c>
-      <c r="D60" s="23">
+      <c r="D60" s="27">
         <f>IF($E60="","",EOMONTH($E60,0))</f>
         <v/>
       </c>
-      <c r="E60" s="23" t="n">
+      <c r="E60" s="27" t="n">
         <v>46202</v>
       </c>
-      <c r="F60" s="24" t="n">
+      <c r="F60" s="28" t="n">
         <v>2782960.69</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -4333,7 +4717,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I60" s="25" t="inlineStr">
+      <c r="I60" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4342,16 +4726,16 @@
       <c r="K60" s="15" t="n"/>
       <c r="L60" s="15" t="n"/>
       <c r="M60" s="15" t="n"/>
-      <c r="N60" s="26" t="n"/>
+      <c r="N60" s="30" t="n"/>
       <c r="O60" s="15" t="n"/>
     </row>
     <row r="61">
-      <c r="E61" s="27" t="inlineStr">
+      <c r="E61" s="31" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F61" s="28">
+      <c r="F61" s="32">
         <f>SUM(F5:F60)</f>
         <v/>
       </c>
@@ -4530,7 +4914,7 @@
       <c r="C6" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>5, 6, 7, 8, 12, 13, 14, 15, 19, 20, 21, 22, ... (+15 more)</t>
         </is>
@@ -4550,7 +4934,7 @@
       <c r="C7" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 17, 18, ... (+14 more)</t>
         </is>
@@ -4570,7 +4954,7 @@
       <c r="C8" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>1, 3, 4, 9, 10, 11, 17, 18, 25, 26, 31, 35, ... (+6 more)</t>
         </is>
@@ -4590,7 +4974,7 @@
       <c r="C9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>12, 20, 27</t>
         </is>
@@ -4610,7 +4994,7 @@
       <c r="C10" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -4630,7 +5014,7 @@
       <c r="C11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -4649,7 +5033,7 @@
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -4661,7 +5045,7 @@
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -4673,7 +5057,7 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -4685,7 +5069,7 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>*</t>
         </is>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,12 +87,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00BF8F00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00595959"/>
       <sz val="9"/>
     </font>
     <font>
@@ -175,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -222,12 +216,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -235,7 +226,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -619,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D50"/>
+  <dimension ref="B2:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -961,194 +952,233 @@
     <row r="29">
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>SCF invoice list amount column</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr"/>
       <c r="D29" s="12" t="inlineStr">
         <is>
+          <t>Level 2 only. Caption of the amount column in the exported list of invoices behind a Santander SCF payment. Leave blank to fall back to the 'Cleared list ...' captions and then the built-in list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>SCF invoice list supplier column</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr"/>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Level 2 only. Caption of the supplier column in that same file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>SCF invoice list document column</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Level 2 only. Caption of the invoice-number column in that same file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr"/>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>Samples in scope</t>
-        </is>
-      </c>
-      <c r="C33" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>DONE -- invoice downloaded</t>
-        </is>
-      </c>
-      <c r="C34" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>BLOCKED_SCF -- Santander, needs the Audit2 steps</t>
-        </is>
-      </c>
-      <c r="C35" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
-        <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>PARTIAL -- traced, no invoice file</t>
+          <t>Samples in scope</t>
         </is>
       </c>
       <c r="C36" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C37" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>BLOCKED_SCF -- Santander, needs the Audit2 steps</t>
         </is>
       </c>
       <c r="C38" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>PARTIAL -- traced, no invoice file</t>
         </is>
       </c>
       <c r="C39" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C40" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C41" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C42" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="14" t="inlineStr">
         <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C43" s="15">
+        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Files downloaded</t>
+        </is>
+      </c>
+      <c r="C44" s="15">
+        <f>SUM(Samples!N5:N1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Samples with no named beneficiary in the request</t>
+        </is>
+      </c>
+      <c r="C45" s="15">
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C43" s="15">
+      <c r="C46" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="3" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="B50" s="14" t="inlineStr">
         <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="B53" s="14" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1156,10 +1186,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C53:D53"/>
     <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1181,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F49"/>
+  <dimension ref="A2:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1302,66 +1332,66 @@
     <row r="9">
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.StatementDateFrom</t>
+          <t>FEBAN.HouseBank</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Statement date, low value</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>House bank filter. Not in the recording, which left it blank. Worth setting if the EUR account turns out to be out of scope. VERIFY</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtSL_AZDAT-LOW</t>
+          <t>wnd[1]/usr/ctxtSL_HBKID-LOW</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.StatementDateTo</t>
+          <t>FEBAN.AccountId</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Statement date, high value</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Account ID filter. Same. VERIFY</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtSL_AZDAT-HIGH</t>
+          <t>wnd[1]/usr/ctxtSL_HKTID-LOW</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.ExecuteButton</t>
+          <t>FEBAN.StatementDateFrom</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Execute, on the popup's own toolbar</t>
+          <t>Statement date, low value</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -1376,19 +1406,19 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[8]</t>
+          <t>wnd[1]/usr/ctxtSL_AZDAT-LOW</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.PostExecuteButton</t>
+          <t>FEBAN.StatementDateTo</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Toolbar button pressed straight after Execute in the recording. Leave blank to skip it -- check what it does before relying on it</t>
+          <t>Statement date, high value</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -1398,35 +1428,51 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/tbar[1]/btn[14]</t>
+          <t>wnd[1]/usr/ctxtSL_AZDAT-HIGH</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>FEBAN result list</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>FEBAN.ExecuteButton</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Execute, on the popup's own toolbar</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[8]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.ResultGrid</t>
+          <t>FEBAN.PostExecuteButton</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>ALV grid holding the statement items</t>
+          <t>Toolbar button pressed straight after Execute in the recording. Leave blank to skip it -- check what it does before relying on it</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -1436,56 +1482,40 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/shellcont/shell</t>
+          <t>wnd[0]/tbar[1]/btn[14]</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>FEBAN.Col.Amount</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Grid column holding the amount</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>KWBTR</t>
-        </is>
-      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>FEBAN result list</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.Col.ValueDate</t>
+          <t>FEBAN.ResultGrid</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the value date. NOT in the recording -- run modFeban.DumpGridColumns and paste the real name here</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>ALV grid holding the statement items</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -1495,46 +1525,46 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>VALUT</t>
+          <t>wnd[0]/shellcont/shell</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.Col.Status</t>
+          <t>FEBAN.Col.Amount</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the posting status. VERIFY</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Grid column holding the amount</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>ESTAT</t>
+          <t>KWBTR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.Col.DocNumber</t>
+          <t>FEBAN.Col.ValueDate</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the FI document number. VERIFY</t>
+          <t>Grid column holding the value date. NOT in the recording -- run modFeban.DumpGridColumns and paste the real name here</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -1544,29 +1574,29 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>BELNR</t>
+          <t>VALUT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.Col.PartyName</t>
+          <t>FEBAN.Col.Status</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the beneficiary name, if the grid has one</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>optional</t>
+          <t>Grid column holding the posting status. VERIFY</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -1574,50 +1604,70 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F19" s="23" t="n"/>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>ESTAT</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>FEBAN item detail</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>FEBAN.Col.DocNumber</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Grid column holding the FI document number. VERIFY</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>BELNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Feban.Detail.DocNumber</t>
+          <t>FEBAN.Col.Reference</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>FI document field on the statement-item detail screen</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Grid column holding the bank reference or note-to-payee, logged alongside each match as context. VERIFY</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/subSUB_MAIN:SAPLNEW_FEBA:4000/subSUB_APPLICATION:SAPLNEW_FEBA:2200/subAREA1:SAPLNEW_FEBA:2201/txtD2201_BELNR</t>
+          <t>SGTXT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>FI document (reached with F2 from the detail screen)</t>
+          <t>FEBAN item detail</t>
         </is>
       </c>
       <c r="C22" s="19" t="n"/>
@@ -1625,15 +1675,15 @@
       <c r="E22" s="19" t="n"/>
       <c r="F22" s="19" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Doc.BsegGrid</t>
+          <t>Feban.Detail.DocNumber</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Line-item grid on the document overview</t>
+          <t>FI document field on the statement-item detail screen</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -1648,322 +1698,302 @@
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/cntlCTRL_CONTAINERBSEG/shellcont/shell</t>
+          <t>wnd[0]/usr/subSUB_MAIN:SAPLNEW_FEBA:4000/subSUB_APPLICATION:SAPLNEW_FEBA:2200/subAREA1:SAPLNEW_FEBA:2201/txtD2201_BELNR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Doc.Col.Amount</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Line-item grid column holding the local-currency amount</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>DMBTR</t>
-        </is>
-      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>FI document (reached with F2 from the detail screen)</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Doc.Col.Vendor</t>
+          <t>Doc.BsegGrid</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Line-item grid column holding the vendor account. VERIFY</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Line-item grid on the document overview</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>LIFNR</t>
+          <t>wnd[0]/usr/cntlCTRL_CONTAINERBSEG/shellcont/shell</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="20" t="inlineStr">
         <is>
+          <t>Doc.Col.Amount</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Line-item grid column holding the local-currency amount</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>DMBTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
           <t>Doc.ClearingDocField</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Clearing-document field on the line-item detail screen</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/txtBSEG-AUGBL</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="18" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Cleared items with supplier names</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Cleared.Menu</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Menu path that produces the cleared-items list from the clearing document. menu[5]/menu[3] in the recording</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/mbar/menu[5]/menu[3]</t>
-        </is>
-      </c>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="20" t="inlineStr">
         <is>
+          <t>Cleared.Menu</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Menu path that produces the cleared-items list from the clearing document. menu[5]/menu[3] in the recording</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/mbar/menu[5]/menu[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="20" t="inlineStr">
+        <is>
           <t>Cleared.ListAnchor</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>A label that exists on the cleared-items list, used to confirm the list actually came up</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/lbl[28,7]</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Classic list export (List &gt; Save/Send &gt; File)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-    </row>
     <row r="31">
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>Export.ListMenu</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Menu path that opens the save-list dialog</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/mbar/menu[0]/menu[3]/menu[1]</t>
-        </is>
-      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>FEBAN statement-list export (optional period context)</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Export.FormatOkButton</t>
+          <t>Export.AlvToolbarButton</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Confirm the file-format popup</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Function code of the export button on the FEBAN grid's own toolbar. The recording never exported this grid, so this is unrecorded and the whole step is optional -- leave both blank to skip it. VERIFY</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[0]</t>
+          <t>&amp;MB_EXPORT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>Save-as dialog</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Export.AlvMenuItem</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Context-menu entry for local file / spreadsheet. VERIFY</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>&amp;PC</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Save.Path</t>
+          <t>Export.AlvFormatRadio</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Directory field</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Radio button for the file format, if that popup appears. VERIFY</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>wnd[1]/usr/ctxtDY_PATH</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>Save.FileName</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>File name field. The recording left the default in place, so this ID is standard-but-unconfirmed. VERIFY</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
-        </is>
-      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Classic list export (List &gt; Save/Send &gt; File)</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Save.Encoding</t>
+          <t>Export.ListMenu</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Encoding field, where present. VERIFY</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Menu path that opens the save-list dialog</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
+          <t>wnd[0]/mbar/menu[0]/menu[3]/menu[1]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Save.GenerateButton</t>
+          <t>Export.FormatOkButton</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Confirm the save. btn[0], not btn[11], on this dialog</t>
+          <t>Confirm the file-format popup</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -1985,7 +2015,7 @@
     <row r="38">
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Invoice PDF: regular supplier route</t>
+          <t>Save-as dialog</t>
         </is>
       </c>
       <c r="C38" s="19" t="n"/>
@@ -1996,39 +2026,39 @@
     <row r="39">
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Invoice.GosToolbox</t>
+          <t>Save.Path</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Services-for-object toolbox on the title bar. NOT in the recording -- Audit2.vbs captured no steps. VERIFY</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Directory field</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/titl/shellcont/shell</t>
+          <t>wnd[1]/usr/ctxtDY_PATH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListGrid</t>
+          <t>Save.FileName</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Attachment-list grid. VERIFY</t>
+          <t>File name field. The recording left the default in place, so this ID is standard-but-unconfirmed. VERIFY</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
@@ -2038,24 +2068,24 @@
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/cntlCONTAINER/shellcont/shell</t>
+          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Invoice.SaveButton</t>
+          <t>Save.Encoding</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Save/export button on the attachment list. VERIFY</t>
+          <t>Encoding field, where present. VERIFY</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
@@ -2070,58 +2100,62 @@
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[5]</t>
+          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>Invoice PDF: Santander SCF confirming route</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>Save.GenerateButton</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the save. btn[0], not btn[11], on this dialog</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[0]</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>Scf.Step1</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>First step of the confirming-payment route. BLOCKED: Audit2.vbs recorded nothing, so these steps are unknown. Re-record and fill in</t>
-        </is>
-      </c>
-      <c r="D43" s="26" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="E43" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="n"/>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Invoice PDF: regular supplier route</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Scf.Step2</t>
+          <t>Invoice.GosToolbox</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Second step of the confirming-payment route. BLOCKED</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>Services-for-object toolbox on the title bar. NOT in the recording -- Audit2.vbs captured no steps. VERIFY</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E44" s="22" t="inlineStr">
@@ -2129,67 +2163,183 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F44" s="23" t="n"/>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/titl/shellcont/shell</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>Scf.Step3</t>
+          <t>Invoice.AttachListGrid</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Third step of the confirming-payment route. BLOCKED</t>
-        </is>
-      </c>
-      <c r="D45" s="26" t="inlineStr">
+          <t>Attachment-list grid. VERIFY</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/cntlCONTAINER/shellcont/shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.SaveButton</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Save/export button on the attachment list. VERIFY</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Level 2: Santander SCF confirming route</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="19" t="n"/>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="19" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>Scf.OpenPayment</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>How you get from the cleared-items list into the Santander SCF payment. A menu entry, a button, or a field to put the cursor on and press F2 -- the macro works out which from the control type. BLOCKED: Audit2.vbs recorded nothing, so this is unknown</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E45" s="22" t="inlineStr">
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F45" s="23" t="n"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="16" t="inlineStr">
+      <c r="F48" s="23" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Scf.InvoiceListMenu</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Menu path that lists the supplier invoices that SCF payment settled. BLOCKED</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>Scf.InvoiceListAnchor</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Optional. An element that exists on that invoice list, used only to confirm the previous step landed where expected. BLOCKED</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="16" t="inlineStr">
+    <row r="53" ht="30" customHeight="1">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="B49" s="16" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>The recording entered dates as 8 digits with no separators (01092025). The Control sheet's 'SAP date format' is set to DDMMYYYY to match. Do not change it to DMY unless you have checked that this system accepts 01.09.2025 as well.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B30:F30"/>
+  <mergeCells count="14">
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2322,18 +2472,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <f>IF($E5="","",DATE(YEAR($E5),MONTH($E5),1))</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="26">
         <f>IF($E5="","",EOMONTH($E5,0))</f>
         <v/>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="26" t="n">
         <v>45903</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="27" t="n">
         <v>8072447.42</v>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
@@ -2342,7 +2492,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2351,7 +2501,7 @@
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
-      <c r="N5" s="30" t="n"/>
+      <c r="N5" s="29" t="n"/>
       <c r="O5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -2363,18 +2513,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <f>IF($E6="","",DATE(YEAR($E6),MONTH($E6),1))</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <f>IF($E6="","",EOMONTH($E6,0))</f>
         <v/>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="26" t="n">
         <v>45912</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="27" t="n">
         <v>2161788.23</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -2387,7 +2537,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -2396,7 +2546,7 @@
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
-      <c r="N6" s="30" t="n"/>
+      <c r="N6" s="29" t="n"/>
       <c r="O6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -2408,18 +2558,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <f>IF($E7="","",DATE(YEAR($E7),MONTH($E7),1))</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="26">
         <f>IF($E7="","",EOMONTH($E7,0))</f>
         <v/>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="26" t="n">
         <v>45915</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="27" t="n">
         <v>5988033.6</v>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -2428,7 +2578,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2437,7 +2587,7 @@
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15" t="n"/>
-      <c r="N7" s="30" t="n"/>
+      <c r="N7" s="29" t="n"/>
       <c r="O7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -2449,18 +2599,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <f>IF($E8="","",DATE(YEAR($E8),MONTH($E8),1))</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <f>IF($E8="","",EOMONTH($E8,0))</f>
         <v/>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="26" t="n">
         <v>45922</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="27" t="n">
         <v>2942842.52</v>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
@@ -2469,7 +2619,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2478,7 +2628,7 @@
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
-      <c r="N8" s="30" t="n"/>
+      <c r="N8" s="29" t="n"/>
       <c r="O8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -2490,18 +2640,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <f>IF($E9="","",DATE(YEAR($E9),MONTH($E9),1))</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <f>IF($E9="","",EOMONTH($E9,0))</f>
         <v/>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="26" t="n">
         <v>45924</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="27" t="n">
         <v>8617262.93</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -2514,7 +2664,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2523,7 +2673,7 @@
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
-      <c r="N9" s="30" t="n"/>
+      <c r="N9" s="29" t="n"/>
       <c r="O9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -2535,18 +2685,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <f>IF($E10="","",DATE(YEAR($E10),MONTH($E10),1))</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <f>IF($E10="","",EOMONTH($E10,0))</f>
         <v/>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="26" t="n">
         <v>45925</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="27" t="n">
         <v>2968313.21</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -2559,7 +2709,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2568,7 +2718,7 @@
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
-      <c r="N10" s="30" t="n"/>
+      <c r="N10" s="29" t="n"/>
       <c r="O10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -2580,18 +2730,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <f>IF($E11="","",DATE(YEAR($E11),MONTH($E11),1))</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <f>IF($E11="","",EOMONTH($E11,0))</f>
         <v/>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="26" t="n">
         <v>45930</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2604,7 +2754,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2613,7 +2763,7 @@
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="15" t="n"/>
       <c r="M11" s="15" t="n"/>
-      <c r="N11" s="30" t="n"/>
+      <c r="N11" s="29" t="n"/>
       <c r="O11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -2625,18 +2775,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <f>IF($E12="","",DATE(YEAR($E12),MONTH($E12),1))</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="26">
         <f>IF($E12="","",EOMONTH($E12,0))</f>
         <v/>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="26" t="n">
         <v>45931</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="27" t="n">
         <v>4483676.08</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -2649,7 +2799,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2658,7 +2808,7 @@
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
-      <c r="N12" s="30" t="n"/>
+      <c r="N12" s="29" t="n"/>
       <c r="O12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -2670,18 +2820,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <f>IF($E13="","",DATE(YEAR($E13),MONTH($E13),1))</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="26">
         <f>IF($E13="","",EOMONTH($E13,0))</f>
         <v/>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="26" t="n">
         <v>45933</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="27" t="n">
         <v>3412038.97</v>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -2690,7 +2840,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2699,7 +2849,7 @@
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
-      <c r="N13" s="30" t="n"/>
+      <c r="N13" s="29" t="n"/>
       <c r="O13" s="15" t="n"/>
     </row>
     <row r="14">
@@ -2711,18 +2861,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <f>IF($E14="","",DATE(YEAR($E14),MONTH($E14),1))</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="26">
         <f>IF($E14="","",EOMONTH($E14,0))</f>
         <v/>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="26" t="n">
         <v>45943</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="27" t="n">
         <v>3385329.45</v>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
@@ -2731,7 +2881,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2740,7 +2890,7 @@
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
-      <c r="N14" s="30" t="n"/>
+      <c r="N14" s="29" t="n"/>
       <c r="O14" s="15" t="n"/>
     </row>
     <row r="15">
@@ -2752,18 +2902,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <f>IF($E15="","",DATE(YEAR($E15),MONTH($E15),1))</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="26">
         <f>IF($E15="","",EOMONTH($E15,0))</f>
         <v/>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="26" t="n">
         <v>45950</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="27" t="n">
         <v>4898587.92</v>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
@@ -2772,7 +2922,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2781,7 +2931,7 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="15" t="n"/>
-      <c r="N15" s="30" t="n"/>
+      <c r="N15" s="29" t="n"/>
       <c r="O15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -2793,18 +2943,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <f>IF($E16="","",DATE(YEAR($E16),MONTH($E16),1))</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <f>IF($E16="","",EOMONTH($E16,0))</f>
         <v/>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="26" t="n">
         <v>45954</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="27" t="n">
         <v>3480924.53</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -2817,7 +2967,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I16" s="29" t="inlineStr">
+      <c r="I16" s="28" t="inlineStr">
         <is>
           <t>date_stored_as_text; party_whitespace_cleaned</t>
         </is>
@@ -2826,7 +2976,7 @@
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
-      <c r="N16" s="30" t="n"/>
+      <c r="N16" s="29" t="n"/>
       <c r="O16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -2838,18 +2988,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <f>IF($E17="","",DATE(YEAR($E17),MONTH($E17),1))</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="26">
         <f>IF($E17="","",EOMONTH($E17,0))</f>
         <v/>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="26" t="n">
         <v>45957</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="27" t="n">
         <v>2614260.03</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -2862,7 +3012,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I17" s="29" t="inlineStr">
+      <c r="I17" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2871,7 +3021,7 @@
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
-      <c r="N17" s="30" t="n"/>
+      <c r="N17" s="29" t="n"/>
       <c r="O17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -2883,18 +3033,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <f>IF($E18="","",DATE(YEAR($E18),MONTH($E18),1))</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <f>IF($E18="","",EOMONTH($E18,0))</f>
         <v/>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="26" t="n">
         <v>45961</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -2907,7 +3057,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I18" s="29" t="inlineStr">
+      <c r="I18" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2916,7 +3066,7 @@
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
-      <c r="N18" s="30" t="n"/>
+      <c r="N18" s="29" t="n"/>
       <c r="O18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -2928,18 +3078,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <f>IF($E19="","",DATE(YEAR($E19),MONTH($E19),1))</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="26">
         <f>IF($E19="","",EOMONTH($E19,0))</f>
         <v/>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="26" t="n">
         <v>45961</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="27" t="n">
         <v>3317511.83</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -2952,7 +3102,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I19" s="29" t="inlineStr">
+      <c r="I19" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2961,7 +3111,7 @@
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
-      <c r="N19" s="30" t="n"/>
+      <c r="N19" s="29" t="n"/>
       <c r="O19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -2973,18 +3123,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <f>IF($E20="","",DATE(YEAR($E20),MONTH($E20),1))</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="26">
         <f>IF($E20="","",EOMONTH($E20,0))</f>
         <v/>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="26" t="n">
         <v>45964</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="27" t="n">
         <v>3724798.28</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -2997,12 +3147,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I20" s="29" t="inlineStr"/>
+      <c r="I20" s="28" t="inlineStr"/>
       <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
-      <c r="N20" s="30" t="n"/>
+      <c r="N20" s="29" t="n"/>
       <c r="O20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -3014,18 +3164,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <f>IF($E21="","",DATE(YEAR($E21),MONTH($E21),1))</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="26">
         <f>IF($E21="","",EOMONTH($E21,0))</f>
         <v/>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="26" t="n">
         <v>45966</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="27" t="n">
         <v>5044035.13</v>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
@@ -3034,7 +3184,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="I21" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3043,7 +3193,7 @@
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15" t="n"/>
-      <c r="N21" s="30" t="n"/>
+      <c r="N21" s="29" t="n"/>
       <c r="O21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -3055,18 +3205,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <f>IF($E22="","",DATE(YEAR($E22),MONTH($E22),1))</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="26">
         <f>IF($E22="","",EOMONTH($E22,0))</f>
         <v/>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="26" t="n">
         <v>45978</v>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="27" t="n">
         <v>5245536.51</v>
       </c>
       <c r="G22" s="10" t="inlineStr"/>
@@ -3075,7 +3225,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I22" s="29" t="inlineStr">
+      <c r="I22" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3084,7 +3234,7 @@
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
-      <c r="N22" s="30" t="n"/>
+      <c r="N22" s="29" t="n"/>
       <c r="O22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -3096,18 +3246,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <f>IF($E23="","",DATE(YEAR($E23),MONTH($E23),1))</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="26">
         <f>IF($E23="","",EOMONTH($E23,0))</f>
         <v/>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="26" t="n">
         <v>45989</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="27" t="n">
         <v>4173936.71</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -3120,7 +3270,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I23" s="29" t="inlineStr">
+      <c r="I23" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3129,7 +3279,7 @@
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
-      <c r="N23" s="30" t="n"/>
+      <c r="N23" s="29" t="n"/>
       <c r="O23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -3141,18 +3291,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <f>IF($E24="","",DATE(YEAR($E24),MONTH($E24),1))</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="26">
         <f>IF($E24="","",EOMONTH($E24,0))</f>
         <v/>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="26" t="n">
         <v>45989</v>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="F24" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -3165,7 +3315,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I24" s="29" t="inlineStr">
+      <c r="I24" s="28" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3174,7 +3324,7 @@
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
-      <c r="N24" s="30" t="n"/>
+      <c r="N24" s="29" t="n"/>
       <c r="O24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -3186,18 +3336,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <f>IF($E25="","",DATE(YEAR($E25),MONTH($E25),1))</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="26">
         <f>IF($E25="","",EOMONTH($E25,0))</f>
         <v/>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="26" t="n">
         <v>46020</v>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="27" t="n">
         <v>2828677.68</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -3210,7 +3360,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I25" s="29" t="inlineStr">
+      <c r="I25" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3219,7 +3369,7 @@
       <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n"/>
       <c r="M25" s="15" t="n"/>
-      <c r="N25" s="30" t="n"/>
+      <c r="N25" s="29" t="n"/>
       <c r="O25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -3231,18 +3381,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <f>IF($E26="","",DATE(YEAR($E26),MONTH($E26),1))</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="26">
         <f>IF($E26="","",EOMONTH($E26,0))</f>
         <v/>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="26" t="n">
         <v>46022</v>
       </c>
-      <c r="F26" s="28" t="n">
+      <c r="F26" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -3255,7 +3405,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I26" s="29" t="inlineStr">
+      <c r="I26" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3264,7 +3414,7 @@
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
-      <c r="N26" s="30" t="n"/>
+      <c r="N26" s="29" t="n"/>
       <c r="O26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -3276,18 +3426,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <f>IF($E27="","",DATE(YEAR($E27),MONTH($E27),1))</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="26">
         <f>IF($E27="","",EOMONTH($E27,0))</f>
         <v/>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="26" t="n">
         <v>46022</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F27" s="27" t="n">
         <v>2233241.99</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3300,7 +3450,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I27" s="29" t="inlineStr">
+      <c r="I27" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3309,7 +3459,7 @@
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15" t="n"/>
-      <c r="N27" s="30" t="n"/>
+      <c r="N27" s="29" t="n"/>
       <c r="O27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -3321,18 +3471,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <f>IF($E28="","",DATE(YEAR($E28),MONTH($E28),1))</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="26">
         <f>IF($E28="","",EOMONTH($E28,0))</f>
         <v/>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="26" t="n">
         <v>46024</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="27" t="n">
         <v>3489077.98</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -3345,7 +3495,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I28" s="29" t="inlineStr">
+      <c r="I28" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -3354,7 +3504,7 @@
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
-      <c r="N28" s="30" t="n"/>
+      <c r="N28" s="29" t="n"/>
       <c r="O28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -3366,18 +3516,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <f>IF($E29="","",DATE(YEAR($E29),MONTH($E29),1))</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="26">
         <f>IF($E29="","",EOMONTH($E29,0))</f>
         <v/>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="26" t="n">
         <v>46028</v>
       </c>
-      <c r="F29" s="28" t="n">
+      <c r="F29" s="27" t="n">
         <v>4395299.21</v>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -3386,7 +3536,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I29" s="29" t="inlineStr">
+      <c r="I29" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3395,7 +3545,7 @@
       <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
-      <c r="N29" s="30" t="n"/>
+      <c r="N29" s="29" t="n"/>
       <c r="O29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -3407,18 +3557,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="26">
         <f>IF($E30="","",DATE(YEAR($E30),MONTH($E30),1))</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="26">
         <f>IF($E30="","",EOMONTH($E30,0))</f>
         <v/>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="26" t="n">
         <v>46031</v>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="F30" s="27" t="n">
         <v>8800991.4</v>
       </c>
       <c r="G30" s="10" t="inlineStr"/>
@@ -3427,7 +3577,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I30" s="29" t="inlineStr">
+      <c r="I30" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3436,7 +3586,7 @@
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
       <c r="M30" s="15" t="n"/>
-      <c r="N30" s="30" t="n"/>
+      <c r="N30" s="29" t="n"/>
       <c r="O30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -3448,18 +3598,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="26">
         <f>IF($E31="","",DATE(YEAR($E31),MONTH($E31),1))</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="26">
         <f>IF($E31="","",EOMONTH($E31,0))</f>
         <v/>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E31" s="26" t="n">
         <v>46038</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F31" s="27" t="n">
         <v>6502110.67</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3472,7 +3622,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I31" s="29" t="inlineStr">
+      <c r="I31" s="28" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3481,7 +3631,7 @@
       <c r="K31" s="15" t="n"/>
       <c r="L31" s="15" t="n"/>
       <c r="M31" s="15" t="n"/>
-      <c r="N31" s="30" t="n"/>
+      <c r="N31" s="29" t="n"/>
       <c r="O31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -3493,18 +3643,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="26">
         <f>IF($E32="","",DATE(YEAR($E32),MONTH($E32),1))</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="26">
         <f>IF($E32="","",EOMONTH($E32,0))</f>
         <v/>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="26" t="n">
         <v>46051</v>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="F32" s="27" t="n">
         <v>3463573.21</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -3517,7 +3667,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I32" s="29" t="inlineStr">
+      <c r="I32" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3526,7 +3676,7 @@
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
-      <c r="N32" s="30" t="n"/>
+      <c r="N32" s="29" t="n"/>
       <c r="O32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -3538,18 +3688,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="26">
         <f>IF($E33="","",DATE(YEAR($E33),MONTH($E33),1))</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="26">
         <f>IF($E33="","",EOMONTH($E33,0))</f>
         <v/>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="26" t="n">
         <v>46052</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -3562,7 +3712,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I33" s="29" t="inlineStr">
+      <c r="I33" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3571,7 +3721,7 @@
       <c r="K33" s="15" t="n"/>
       <c r="L33" s="15" t="n"/>
       <c r="M33" s="15" t="n"/>
-      <c r="N33" s="30" t="n"/>
+      <c r="N33" s="29" t="n"/>
       <c r="O33" s="15" t="n"/>
     </row>
     <row r="34">
@@ -3583,18 +3733,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="26">
         <f>IF($E34="","",DATE(YEAR($E34),MONTH($E34),1))</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="26">
         <f>IF($E34="","",EOMONTH($E34,0))</f>
         <v/>
       </c>
-      <c r="E34" s="27" t="n">
+      <c r="E34" s="26" t="n">
         <v>46055</v>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="F34" s="27" t="n">
         <v>3679179.76</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -3607,7 +3757,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I34" s="29" t="inlineStr">
+      <c r="I34" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -3616,7 +3766,7 @@
       <c r="K34" s="15" t="n"/>
       <c r="L34" s="15" t="n"/>
       <c r="M34" s="15" t="n"/>
-      <c r="N34" s="30" t="n"/>
+      <c r="N34" s="29" t="n"/>
       <c r="O34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -3628,18 +3778,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="26">
         <f>IF($E35="","",DATE(YEAR($E35),MONTH($E35),1))</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="26">
         <f>IF($E35="","",EOMONTH($E35,0))</f>
         <v/>
       </c>
-      <c r="E35" s="27" t="n">
+      <c r="E35" s="26" t="n">
         <v>46057</v>
       </c>
-      <c r="F35" s="28" t="n">
+      <c r="F35" s="27" t="n">
         <v>3674499.52</v>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
@@ -3648,7 +3798,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I35" s="29" t="inlineStr">
+      <c r="I35" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3657,7 +3807,7 @@
       <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="15" t="n"/>
-      <c r="N35" s="30" t="n"/>
+      <c r="N35" s="29" t="n"/>
       <c r="O35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -3669,18 +3819,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="26">
         <f>IF($E36="","",DATE(YEAR($E36),MONTH($E36),1))</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="26">
         <f>IF($E36="","",EOMONTH($E36,0))</f>
         <v/>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="26" t="n">
         <v>46080</v>
       </c>
-      <c r="F36" s="28" t="n">
+      <c r="F36" s="27" t="n">
         <v>6558159.12</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -3693,7 +3843,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I36" s="29" t="inlineStr">
+      <c r="I36" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3702,7 +3852,7 @@
       <c r="K36" s="15" t="n"/>
       <c r="L36" s="15" t="n"/>
       <c r="M36" s="15" t="n"/>
-      <c r="N36" s="30" t="n"/>
+      <c r="N36" s="29" t="n"/>
       <c r="O36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -3714,18 +3864,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="26">
         <f>IF($E37="","",DATE(YEAR($E37),MONTH($E37),1))</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="26">
         <f>IF($E37="","",EOMONTH($E37,0))</f>
         <v/>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="26" t="n">
         <v>46080</v>
       </c>
-      <c r="F37" s="28" t="n">
+      <c r="F37" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -3738,7 +3888,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I37" s="29" t="inlineStr">
+      <c r="I37" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3747,7 +3897,7 @@
       <c r="K37" s="15" t="n"/>
       <c r="L37" s="15" t="n"/>
       <c r="M37" s="15" t="n"/>
-      <c r="N37" s="30" t="n"/>
+      <c r="N37" s="29" t="n"/>
       <c r="O37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -3759,18 +3909,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="26">
         <f>IF($E38="","",DATE(YEAR($E38),MONTH($E38),1))</f>
         <v/>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="26">
         <f>IF($E38="","",EOMONTH($E38,0))</f>
         <v/>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E38" s="26" t="n">
         <v>46083</v>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F38" s="27" t="n">
         <v>3562528.89</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3783,7 +3933,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I38" s="29" t="inlineStr">
+      <c r="I38" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3792,7 +3942,7 @@
       <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n"/>
       <c r="M38" s="15" t="n"/>
-      <c r="N38" s="30" t="n"/>
+      <c r="N38" s="29" t="n"/>
       <c r="O38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -3804,18 +3954,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="26">
         <f>IF($E39="","",DATE(YEAR($E39),MONTH($E39),1))</f>
         <v/>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="26">
         <f>IF($E39="","",EOMONTH($E39,0))</f>
         <v/>
       </c>
-      <c r="E39" s="27" t="n">
+      <c r="E39" s="26" t="n">
         <v>46085</v>
       </c>
-      <c r="F39" s="28" t="n">
+      <c r="F39" s="27" t="n">
         <v>8557737.25</v>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
@@ -3824,7 +3974,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I39" s="29" t="inlineStr">
+      <c r="I39" s="28" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -3833,7 +3983,7 @@
       <c r="K39" s="15" t="n"/>
       <c r="L39" s="15" t="n"/>
       <c r="M39" s="15" t="n"/>
-      <c r="N39" s="30" t="n"/>
+      <c r="N39" s="29" t="n"/>
       <c r="O39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -3845,18 +3995,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="26">
         <f>IF($E40="","",DATE(YEAR($E40),MONTH($E40),1))</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="26">
         <f>IF($E40="","",EOMONTH($E40,0))</f>
         <v/>
       </c>
-      <c r="E40" s="27" t="n">
+      <c r="E40" s="26" t="n">
         <v>46093</v>
       </c>
-      <c r="F40" s="28" t="n">
+      <c r="F40" s="27" t="n">
         <v>2301959.84</v>
       </c>
       <c r="G40" s="10" t="inlineStr"/>
@@ -3865,7 +4015,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I40" s="29" t="inlineStr">
+      <c r="I40" s="28" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -3874,7 +4024,7 @@
       <c r="K40" s="15" t="n"/>
       <c r="L40" s="15" t="n"/>
       <c r="M40" s="15" t="n"/>
-      <c r="N40" s="30" t="n"/>
+      <c r="N40" s="29" t="n"/>
       <c r="O40" s="15" t="n"/>
     </row>
     <row r="41">
@@ -3886,18 +4036,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="26">
         <f>IF($E41="","",DATE(YEAR($E41),MONTH($E41),1))</f>
         <v/>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="26">
         <f>IF($E41="","",EOMONTH($E41,0))</f>
         <v/>
       </c>
-      <c r="E41" s="27" t="n">
+      <c r="E41" s="26" t="n">
         <v>46108</v>
       </c>
-      <c r="F41" s="28" t="n">
+      <c r="F41" s="27" t="n">
         <v>5989486.48</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -3910,7 +4060,7 @@
           <t>DS Smith Paper Limited</t>
         </is>
       </c>
-      <c r="I41" s="29" t="inlineStr">
+      <c r="I41" s="28" t="inlineStr">
         <is>
           <t>ref_holds_a_party_name_not_a_transaction_description; party_whitespace_cleaned</t>
         </is>
@@ -3919,7 +4069,7 @@
       <c r="K41" s="15" t="n"/>
       <c r="L41" s="15" t="n"/>
       <c r="M41" s="15" t="n"/>
-      <c r="N41" s="30" t="n"/>
+      <c r="N41" s="29" t="n"/>
       <c r="O41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -3931,18 +4081,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="26">
         <f>IF($E42="","",DATE(YEAR($E42),MONTH($E42),1))</f>
         <v/>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="26">
         <f>IF($E42="","",EOMONTH($E42,0))</f>
         <v/>
       </c>
-      <c r="E42" s="27" t="n">
+      <c r="E42" s="26" t="n">
         <v>46112</v>
       </c>
-      <c r="F42" s="28" t="n">
+      <c r="F42" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -3955,12 +4105,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I42" s="29" t="inlineStr"/>
+      <c r="I42" s="28" t="inlineStr"/>
       <c r="J42" s="15" t="n"/>
       <c r="K42" s="15" t="n"/>
       <c r="L42" s="15" t="n"/>
       <c r="M42" s="15" t="n"/>
-      <c r="N42" s="30" t="n"/>
+      <c r="N42" s="29" t="n"/>
       <c r="O42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -3972,18 +4122,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="26">
         <f>IF($E43="","",DATE(YEAR($E43),MONTH($E43),1))</f>
         <v/>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="26">
         <f>IF($E43="","",EOMONTH($E43,0))</f>
         <v/>
       </c>
-      <c r="E43" s="27" t="n">
+      <c r="E43" s="26" t="n">
         <v>46113</v>
       </c>
-      <c r="F43" s="28" t="n">
+      <c r="F43" s="27" t="n">
         <v>3316944.84</v>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -3996,12 +4146,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I43" s="29" t="inlineStr"/>
+      <c r="I43" s="28" t="inlineStr"/>
       <c r="J43" s="15" t="n"/>
       <c r="K43" s="15" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15" t="n"/>
-      <c r="N43" s="30" t="n"/>
+      <c r="N43" s="29" t="n"/>
       <c r="O43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -4013,18 +4163,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="26">
         <f>IF($E44="","",DATE(YEAR($E44),MONTH($E44),1))</f>
         <v/>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="26">
         <f>IF($E44="","",EOMONTH($E44,0))</f>
         <v/>
       </c>
-      <c r="E44" s="27" t="n">
+      <c r="E44" s="26" t="n">
         <v>46128</v>
       </c>
-      <c r="F44" s="28" t="n">
+      <c r="F44" s="27" t="n">
         <v>2611670.69</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -4037,12 +4187,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I44" s="29" t="inlineStr"/>
+      <c r="I44" s="28" t="inlineStr"/>
       <c r="J44" s="15" t="n"/>
       <c r="K44" s="15" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15" t="n"/>
-      <c r="N44" s="30" t="n"/>
+      <c r="N44" s="29" t="n"/>
       <c r="O44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -4054,18 +4204,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="26">
         <f>IF($E45="","",DATE(YEAR($E45),MONTH($E45),1))</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="26">
         <f>IF($E45="","",EOMONTH($E45,0))</f>
         <v/>
       </c>
-      <c r="E45" s="27" t="n">
+      <c r="E45" s="26" t="n">
         <v>46129</v>
       </c>
-      <c r="F45" s="28" t="n">
+      <c r="F45" s="27" t="n">
         <v>4996002.96</v>
       </c>
       <c r="G45" s="10" t="inlineStr"/>
@@ -4074,7 +4224,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I45" s="29" t="inlineStr">
+      <c r="I45" s="28" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4083,7 +4233,7 @@
       <c r="K45" s="15" t="n"/>
       <c r="L45" s="15" t="n"/>
       <c r="M45" s="15" t="n"/>
-      <c r="N45" s="30" t="n"/>
+      <c r="N45" s="29" t="n"/>
       <c r="O45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -4095,18 +4245,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="26">
         <f>IF($E46="","",DATE(YEAR($E46),MONTH($E46),1))</f>
         <v/>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="26">
         <f>IF($E46="","",EOMONTH($E46,0))</f>
         <v/>
       </c>
-      <c r="E46" s="27" t="n">
+      <c r="E46" s="26" t="n">
         <v>46135</v>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="F46" s="27" t="n">
         <v>2334786.77</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -4119,7 +4269,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I46" s="29" t="inlineStr">
+      <c r="I46" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4128,7 +4278,7 @@
       <c r="K46" s="15" t="n"/>
       <c r="L46" s="15" t="n"/>
       <c r="M46" s="15" t="n"/>
-      <c r="N46" s="30" t="n"/>
+      <c r="N46" s="29" t="n"/>
       <c r="O46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -4140,18 +4290,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="26">
         <f>IF($E47="","",DATE(YEAR($E47),MONTH($E47),1))</f>
         <v/>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="26">
         <f>IF($E47="","",EOMONTH($E47,0))</f>
         <v/>
       </c>
-      <c r="E47" s="27" t="n">
+      <c r="E47" s="26" t="n">
         <v>46139</v>
       </c>
-      <c r="F47" s="28" t="n">
+      <c r="F47" s="27" t="n">
         <v>2598639.67</v>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -4164,7 +4314,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I47" s="29" t="inlineStr">
+      <c r="I47" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4173,7 +4323,7 @@
       <c r="K47" s="15" t="n"/>
       <c r="L47" s="15" t="n"/>
       <c r="M47" s="15" t="n"/>
-      <c r="N47" s="30" t="n"/>
+      <c r="N47" s="29" t="n"/>
       <c r="O47" s="15" t="n"/>
     </row>
     <row r="48">
@@ -4185,18 +4335,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="26">
         <f>IF($E48="","",DATE(YEAR($E48),MONTH($E48),1))</f>
         <v/>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="26">
         <f>IF($E48="","",EOMONTH($E48,0))</f>
         <v/>
       </c>
-      <c r="E48" s="27" t="n">
+      <c r="E48" s="26" t="n">
         <v>46142</v>
       </c>
-      <c r="F48" s="28" t="n">
+      <c r="F48" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -4209,12 +4359,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I48" s="29" t="inlineStr"/>
+      <c r="I48" s="28" t="inlineStr"/>
       <c r="J48" s="15" t="n"/>
       <c r="K48" s="15" t="n"/>
       <c r="L48" s="15" t="n"/>
       <c r="M48" s="15" t="n"/>
-      <c r="N48" s="30" t="n"/>
+      <c r="N48" s="29" t="n"/>
       <c r="O48" s="15" t="n"/>
     </row>
     <row r="49">
@@ -4226,18 +4376,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="26">
         <f>IF($E49="","",DATE(YEAR($E49),MONTH($E49),1))</f>
         <v/>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="26">
         <f>IF($E49="","",EOMONTH($E49,0))</f>
         <v/>
       </c>
-      <c r="E49" s="27" t="n">
+      <c r="E49" s="26" t="n">
         <v>46142</v>
       </c>
-      <c r="F49" s="28" t="n">
+      <c r="F49" s="27" t="n">
         <v>3232025.51</v>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -4250,7 +4400,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I49" s="29" t="inlineStr">
+      <c r="I49" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4259,7 +4409,7 @@
       <c r="K49" s="15" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15" t="n"/>
-      <c r="N49" s="30" t="n"/>
+      <c r="N49" s="29" t="n"/>
       <c r="O49" s="15" t="n"/>
     </row>
     <row r="50">
@@ -4271,18 +4421,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="26">
         <f>IF($E50="","",DATE(YEAR($E50),MONTH($E50),1))</f>
         <v/>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="26">
         <f>IF($E50="","",EOMONTH($E50,0))</f>
         <v/>
       </c>
-      <c r="E50" s="27" t="n">
+      <c r="E50" s="26" t="n">
         <v>46147</v>
       </c>
-      <c r="F50" s="28" t="n">
+      <c r="F50" s="27" t="n">
         <v>3723586.74</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -4295,12 +4445,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I50" s="29" t="inlineStr"/>
+      <c r="I50" s="28" t="inlineStr"/>
       <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="n"/>
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15" t="n"/>
-      <c r="N50" s="30" t="n"/>
+      <c r="N50" s="29" t="n"/>
       <c r="O50" s="15" t="n"/>
     </row>
     <row r="51">
@@ -4312,18 +4462,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="26">
         <f>IF($E51="","",DATE(YEAR($E51),MONTH($E51),1))</f>
         <v/>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="26">
         <f>IF($E51="","",EOMONTH($E51,0))</f>
         <v/>
       </c>
-      <c r="E51" s="27" t="n">
+      <c r="E51" s="26" t="n">
         <v>46150</v>
       </c>
-      <c r="F51" s="28" t="n">
+      <c r="F51" s="27" t="n">
         <v>5009315.83</v>
       </c>
       <c r="G51" s="10" t="inlineStr"/>
@@ -4332,7 +4482,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I51" s="29" t="inlineStr">
+      <c r="I51" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -4341,7 +4491,7 @@
       <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15" t="n"/>
-      <c r="N51" s="30" t="n"/>
+      <c r="N51" s="29" t="n"/>
       <c r="O51" s="15" t="n"/>
     </row>
     <row r="52">
@@ -4353,18 +4503,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="26">
         <f>IF($E52="","",DATE(YEAR($E52),MONTH($E52),1))</f>
         <v/>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="26">
         <f>IF($E52="","",EOMONTH($E52,0))</f>
         <v/>
       </c>
-      <c r="E52" s="27" t="n">
+      <c r="E52" s="26" t="n">
         <v>46157</v>
       </c>
-      <c r="F52" s="28" t="n">
+      <c r="F52" s="27" t="n">
         <v>4340970.4</v>
       </c>
       <c r="G52" s="10" t="inlineStr"/>
@@ -4373,7 +4523,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I52" s="29" t="inlineStr">
+      <c r="I52" s="28" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -4382,7 +4532,7 @@
       <c r="K52" s="15" t="n"/>
       <c r="L52" s="15" t="n"/>
       <c r="M52" s="15" t="n"/>
-      <c r="N52" s="30" t="n"/>
+      <c r="N52" s="29" t="n"/>
       <c r="O52" s="15" t="n"/>
     </row>
     <row r="53">
@@ -4394,18 +4544,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="26">
         <f>IF($E53="","",DATE(YEAR($E53),MONTH($E53),1))</f>
         <v/>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="26">
         <f>IF($E53="","",EOMONTH($E53,0))</f>
         <v/>
       </c>
-      <c r="E53" s="27" t="n">
+      <c r="E53" s="26" t="n">
         <v>46170</v>
       </c>
-      <c r="F53" s="28" t="n">
+      <c r="F53" s="27" t="n">
         <v>2400509.91</v>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -4418,7 +4568,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I53" s="29" t="inlineStr">
+      <c r="I53" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4427,7 +4577,7 @@
       <c r="K53" s="15" t="n"/>
       <c r="L53" s="15" t="n"/>
       <c r="M53" s="15" t="n"/>
-      <c r="N53" s="30" t="n"/>
+      <c r="N53" s="29" t="n"/>
       <c r="O53" s="15" t="n"/>
     </row>
     <row r="54">
@@ -4439,18 +4589,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="26">
         <f>IF($E54="","",DATE(YEAR($E54),MONTH($E54),1))</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="26">
         <f>IF($E54="","",EOMONTH($E54,0))</f>
         <v/>
       </c>
-      <c r="E54" s="27" t="n">
+      <c r="E54" s="26" t="n">
         <v>46171</v>
       </c>
-      <c r="F54" s="28" t="n">
+      <c r="F54" s="27" t="n">
         <v>3444449.93</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -4463,7 +4613,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I54" s="29" t="inlineStr">
+      <c r="I54" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4472,7 +4622,7 @@
       <c r="K54" s="15" t="n"/>
       <c r="L54" s="15" t="n"/>
       <c r="M54" s="15" t="n"/>
-      <c r="N54" s="30" t="n"/>
+      <c r="N54" s="29" t="n"/>
       <c r="O54" s="15" t="n"/>
     </row>
     <row r="55">
@@ -4484,18 +4634,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="26">
         <f>IF($E55="","",DATE(YEAR($E55),MONTH($E55),1))</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="26">
         <f>IF($E55="","",EOMONTH($E55,0))</f>
         <v/>
       </c>
-      <c r="E55" s="27" t="n">
+      <c r="E55" s="26" t="n">
         <v>46171</v>
       </c>
-      <c r="F55" s="28" t="n">
+      <c r="F55" s="27" t="n">
         <v>2450000</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -4508,12 +4658,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I55" s="29" t="inlineStr"/>
+      <c r="I55" s="28" t="inlineStr"/>
       <c r="J55" s="15" t="n"/>
       <c r="K55" s="15" t="n"/>
       <c r="L55" s="15" t="n"/>
       <c r="M55" s="15" t="n"/>
-      <c r="N55" s="30" t="n"/>
+      <c r="N55" s="29" t="n"/>
       <c r="O55" s="15" t="n"/>
     </row>
     <row r="56">
@@ -4525,18 +4675,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="26">
         <f>IF($E56="","",DATE(YEAR($E56),MONTH($E56),1))</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="26">
         <f>IF($E56="","",EOMONTH($E56,0))</f>
         <v/>
       </c>
-      <c r="E56" s="27" t="n">
+      <c r="E56" s="26" t="n">
         <v>46176</v>
       </c>
-      <c r="F56" s="28" t="n">
+      <c r="F56" s="27" t="n">
         <v>5210470.59</v>
       </c>
       <c r="G56" s="10" t="inlineStr"/>
@@ -4545,7 +4695,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I56" s="29" t="inlineStr">
+      <c r="I56" s="28" t="inlineStr">
         <is>
           <t>ref_typo_corrected_from:ACH PYMTS - LCL BULK FNG; no_named_beneficiary</t>
         </is>
@@ -4554,7 +4704,7 @@
       <c r="K56" s="15" t="n"/>
       <c r="L56" s="15" t="n"/>
       <c r="M56" s="15" t="n"/>
-      <c r="N56" s="30" t="n"/>
+      <c r="N56" s="29" t="n"/>
       <c r="O56" s="15" t="n"/>
     </row>
     <row r="57">
@@ -4566,18 +4716,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="26">
         <f>IF($E57="","",DATE(YEAR($E57),MONTH($E57),1))</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="26">
         <f>IF($E57="","",EOMONTH($E57,0))</f>
         <v/>
       </c>
-      <c r="E57" s="27" t="n">
+      <c r="E57" s="26" t="n">
         <v>46177</v>
       </c>
-      <c r="F57" s="28" t="n">
+      <c r="F57" s="27" t="n">
         <v>4006482.03</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -4590,12 +4740,12 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I57" s="29" t="inlineStr"/>
+      <c r="I57" s="28" t="inlineStr"/>
       <c r="J57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
       <c r="L57" s="15" t="n"/>
       <c r="M57" s="15" t="n"/>
-      <c r="N57" s="30" t="n"/>
+      <c r="N57" s="29" t="n"/>
       <c r="O57" s="15" t="n"/>
     </row>
     <row r="58">
@@ -4607,18 +4757,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="26">
         <f>IF($E58="","",DATE(YEAR($E58),MONTH($E58),1))</f>
         <v/>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="26">
         <f>IF($E58="","",EOMONTH($E58,0))</f>
         <v/>
       </c>
-      <c r="E58" s="27" t="n">
+      <c r="E58" s="26" t="n">
         <v>46184</v>
       </c>
-      <c r="F58" s="28" t="n">
+      <c r="F58" s="27" t="n">
         <v>6226088.99</v>
       </c>
       <c r="G58" s="10" t="inlineStr"/>
@@ -4627,7 +4777,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I58" s="29" t="inlineStr">
+      <c r="I58" s="28" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4636,7 +4786,7 @@
       <c r="K58" s="15" t="n"/>
       <c r="L58" s="15" t="n"/>
       <c r="M58" s="15" t="n"/>
-      <c r="N58" s="30" t="n"/>
+      <c r="N58" s="29" t="n"/>
       <c r="O58" s="15" t="n"/>
     </row>
     <row r="59">
@@ -4648,18 +4798,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="26">
         <f>IF($E59="","",DATE(YEAR($E59),MONTH($E59),1))</f>
         <v/>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="26">
         <f>IF($E59="","",EOMONTH($E59,0))</f>
         <v/>
       </c>
-      <c r="E59" s="27" t="n">
+      <c r="E59" s="26" t="n">
         <v>46185</v>
       </c>
-      <c r="F59" s="28" t="n">
+      <c r="F59" s="27" t="n">
         <v>2292348.71</v>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -4672,7 +4822,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I59" s="29" t="inlineStr">
+      <c r="I59" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4681,7 +4831,7 @@
       <c r="K59" s="15" t="n"/>
       <c r="L59" s="15" t="n"/>
       <c r="M59" s="15" t="n"/>
-      <c r="N59" s="30" t="n"/>
+      <c r="N59" s="29" t="n"/>
       <c r="O59" s="15" t="n"/>
     </row>
     <row r="60">
@@ -4693,18 +4843,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="26">
         <f>IF($E60="","",DATE(YEAR($E60),MONTH($E60),1))</f>
         <v/>
       </c>
-      <c r="D60" s="27">
+      <c r="D60" s="26">
         <f>IF($E60="","",EOMONTH($E60,0))</f>
         <v/>
       </c>
-      <c r="E60" s="27" t="n">
+      <c r="E60" s="26" t="n">
         <v>46202</v>
       </c>
-      <c r="F60" s="28" t="n">
+      <c r="F60" s="27" t="n">
         <v>2782960.69</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -4717,7 +4867,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I60" s="29" t="inlineStr">
+      <c r="I60" s="28" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4726,16 +4876,16 @@
       <c r="K60" s="15" t="n"/>
       <c r="L60" s="15" t="n"/>
       <c r="M60" s="15" t="n"/>
-      <c r="N60" s="30" t="n"/>
+      <c r="N60" s="29" t="n"/>
       <c r="O60" s="15" t="n"/>
     </row>
     <row r="61">
-      <c r="E61" s="31" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="31">
         <f>SUM(F5:F60)</f>
         <v/>
       </c>
@@ -4914,7 +5064,7 @@
       <c r="C6" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>5, 6, 7, 8, 12, 13, 14, 15, 19, 20, 21, 22, ... (+15 more)</t>
         </is>
@@ -4934,7 +5084,7 @@
       <c r="C7" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 17, 18, ... (+14 more)</t>
         </is>
@@ -4954,7 +5104,7 @@
       <c r="C8" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>1, 3, 4, 9, 10, 11, 17, 18, 25, 26, 31, 35, ... (+6 more)</t>
         </is>
@@ -4974,7 +5124,7 @@
       <c r="C9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>12, 20, 27</t>
         </is>
@@ -4994,7 +5144,7 @@
       <c r="C10" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -5014,7 +5164,7 @@
       <c r="C11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -5033,7 +5183,7 @@
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5045,7 +5195,7 @@
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5057,7 +5207,7 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5069,7 +5219,7 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Data Issues" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Samples'!$A$4:$O$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Samples'!$A$4:$P$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +87,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00BF8F00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
       <sz val="9"/>
     </font>
     <font>
@@ -169,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -216,17 +222,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -314,6 +326,21 @@
     <comment ref="C21" authorId="0" shapeId="0">
       <text>
         <t>DRY RUN is the safe default. It navigates and logs but exports nothing.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>build_control_workbook.py</author>
+  </authors>
+  <commentList>
+    <comment ref="P4" authorId="0" shapeId="0">
+      <text>
+        <t>Set to No to leave a row out of the run. Blank counts as Yes. Use the autofilter on this column, or modSelect.IncludeOnlyMonth, to pick a subset.</t>
       </text>
     </comment>
   </commentList>
@@ -610,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D53"/>
+  <dimension ref="B2:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -825,7 +852,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>A cleared item whose supplier name matches this is treated as a confirming (supply-chain-finance) payment and routed down the Audit2 path, which needs extra steps. Matched case-insensitively, ignoring spaces.</t>
+          <t>If the largest ZP payment of the batch is to this party, it is a confirming (supply-chain-finance) payment and needs the extra hop to reach the supplier invoices. Matched on letters and digits, so 'SCF Santander' also matches, but 'SANTANDER UK PLC' does not.</t>
         </is>
       </c>
     </row>
@@ -913,272 +940,337 @@
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Cleared list amount column</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr"/>
+          <t>Payment document type</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Caption of the amount column in the exported cleared-items list, if the macro does not find it on its own. Open the first exported file and copy the heading exactly. Leave blank to let the macro try its built-in list of captions.</t>
+          <t>Only documents of this type are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Cleared list supplier column</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr"/>
+          <t>Clearing line posting key</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Caption of the supplier-name column in that same file. Same rules.</t>
+          <t>Step 4 opens the first line-item row with this posting key that also carries a clearing document. Blank means 'any row with a clearing document'.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Cleared list document column</t>
+          <t>Payment usage document column</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr"/>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Caption of the invoice document-number column in that same file. Optional -- without it the run still identifies the supplier and amount.</t>
+          <t>Caption of the document-number column in the exported Payment Usage list, if the macro cannot find it. Open the first exported file and copy the heading exactly.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>SCF invoice list amount column</t>
+          <t>Payment usage type column</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr"/>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Level 2 only. Caption of the amount column in the exported list of invoices behind a Santander SCF payment. Leave blank to fall back to the 'Cleared list ...' captions and then the built-in list.</t>
+          <t>Caption of the document-type column in that same file. Without it every document is taken rather than only the ZP ones, and the Log says so.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>SCF invoice list supplier column</t>
+          <t>Invoice list amount column</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr"/>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Level 2 only. Caption of the supplier column in that same file.</t>
+          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>SCF invoice list document column</t>
+          <t>Invoice list supplier column</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr"/>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Level 2 only. Caption of the invoice-number column in that same file.</t>
+          <t>Caption of the supplier column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>Invoice list document column</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr"/>
       <c r="D32" s="12" t="inlineStr">
         <is>
+          <t>Caption of the invoice-number column in that same file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr"/>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Samples in scope</t>
-        </is>
-      </c>
-      <c r="C36" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>DONE -- invoice downloaded</t>
+          <t>Samples in the sheet</t>
         </is>
       </c>
       <c r="C37" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_SCF -- Santander, needs the Audit2 steps</t>
+          <t>Included in the next run</t>
         </is>
       </c>
       <c r="C38" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
+        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>PARTIAL -- traced, no invoice file</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C39" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <f>COUNTIF(Samples!P5:P1000,"No")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C40" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
         </is>
       </c>
       <c r="C41" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>BLOCKED_SCF -- Santander, needs the extra hop</t>
         </is>
       </c>
       <c r="C42" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
         </is>
       </c>
       <c r="C43" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>PARTIAL -- traced, no invoice file</t>
         </is>
       </c>
       <c r="C44" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C45" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="14" t="inlineStr">
         <is>
+          <t>AMBIGUOUS -- more than one line matched</t>
+        </is>
+      </c>
+      <c r="C46" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C47" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C48" s="15">
+        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Files downloaded</t>
+        </is>
+      </c>
+      <c r="C49" s="15">
+        <f>SUM(Samples!N5:N1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Samples with no named beneficiary in the request</t>
+        </is>
+      </c>
+      <c r="C50" s="15">
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C46" s="15">
+      <c r="C51" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="B50" s="14" t="inlineStr">
+    <row r="55" ht="28" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="B51" s="14" t="inlineStr">
+    <row r="56" ht="28" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="B52" s="14" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="B53" s="14" t="inlineStr">
+    <row r="58" ht="28" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1186,10 +1278,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1211,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F54"/>
+  <dimension ref="A2:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1232,7 +1324,7 @@
     <row r="3" ht="56" customHeight="1">
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Column F is what the macro reads, and it is pre-filled from recordings/Audit.vbs. Rows marked 'recorded' in column D came straight out of that file and should be right for this system. Rows marked VERIFY were not covered by the recording -- check each one against a fresh Alt+F12 recording before switching Run mode to EXTRACT. Rows marked BLOCKED are unknown because Audit2.vbs captured no steps.</t>
+          <t>Column F is what the macro reads. Column D says how much to trust it. recorded = came straight out of a recording in recordings/, so it should be right for this system. VERIFY = standard SAP, but no recording touched it. PREDICTED = written from standard SAP for steps 8-10, which no recording reaches at all -- put SAP on the screen in question and run modProbe.ProbeCurrentScreen to find out which of these hold, then correct them here. BLOCKED = genuinely unknown, and the run stops short of that stage and says so.</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1359,7 @@
     <row r="6">
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>FEBAN selection screen (a MODAL dialog on this system, wnd[1])</t>
+          <t>Step 1: FEBAN selection (a MODAL popup on this system, wnd[1])</t>
         </is>
       </c>
       <c r="C6" s="19" t="n"/>
@@ -1310,7 +1402,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Company code input field</t>
+          <t>Company code</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -1332,66 +1424,66 @@
     <row r="9">
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.HouseBank</t>
+          <t>FEBAN.StatementDateFrom</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>House bank filter. Not in the recording, which left it blank. Worth setting if the EUR account turns out to be out of scope. VERIFY</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Statement date, low</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtSL_HBKID-LOW</t>
+          <t>wnd[1]/usr/ctxtSL_AZDAT-LOW</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.AccountId</t>
+          <t>FEBAN.StatementDateTo</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Account ID filter. Same. VERIFY</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Statement date, high</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtSL_HKTID-LOW</t>
+          <t>wnd[1]/usr/ctxtSL_AZDAT-HIGH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.StatementDateFrom</t>
+          <t>FEBAN.ExecuteButton</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Statement date, low value</t>
+          <t>Execute, on the popup's own toolbar</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -1406,19 +1498,19 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtSL_AZDAT-LOW</t>
+          <t>wnd[1]/tbar[0]/btn[8]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.StatementDateTo</t>
+          <t>FEBAN.PostExecuteButton</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Statement date, high value</t>
+          <t>Toolbar button pressed straight after Execute in all four recordings. Clear it to skip</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -1428,56 +1520,56 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtSL_AZDAT-HIGH</t>
+          <t>wnd[0]/tbar[1]/btn[14]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.ExecuteButton</t>
+          <t>FEBAN.HouseBank</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Execute, on the popup's own toolbar</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>House bank filter. Not recorded; worth setting if the EUR account is out of scope. VERIFY</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[8]</t>
+          <t>wnd[1]/usr/ctxtSL_HBKID-LOW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>FEBAN.PostExecuteButton</t>
+          <t>FEBAN.AccountId</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Toolbar button pressed straight after Execute in the recording. Leave blank to skip it -- check what it does before relying on it</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Account ID filter. VERIFY</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -1487,14 +1579,14 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/tbar[1]/btn[14]</t>
+          <t>wnd[1]/usr/ctxtSL_HKTID-LOW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>FEBAN result list</t>
+          <t>Step 2: FEBAN result list</t>
         </is>
       </c>
       <c r="C15" s="19" t="n"/>
@@ -1510,7 +1602,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>ALV grid holding the statement items</t>
+          <t>ALV grid of statement items</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -1537,7 +1629,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the amount</t>
+          <t>Amount column</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -1564,12 +1656,12 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the value date. NOT in the recording -- run modFeban.DumpGridColumns and paste the real name here</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Statement date column. Audit2.vbs double-clicked this by name, so it is a captured value</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -1579,7 +1671,7 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>VALUT</t>
+          <t>AZDAT</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1683,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the posting status. VERIFY</t>
+          <t>Posting status column. VERIFY</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -1618,7 +1710,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the FI document number. VERIFY</t>
+          <t>FI document column. VERIFY</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -1645,7 +1737,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Grid column holding the bank reference or note-to-payee, logged alongside each match as context. VERIFY</t>
+          <t>Bank reference / note-to-payee, logged as context. VERIFY</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
@@ -1667,7 +1759,7 @@
     <row r="22">
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>FEBAN item detail</t>
+          <t>ALV export (confirmed in Audit2.vbs)</t>
         </is>
       </c>
       <c r="C22" s="19" t="n"/>
@@ -1675,15 +1767,15 @@
       <c r="E22" s="19" t="n"/>
       <c r="F22" s="19" t="n"/>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Feban.Detail.DocNumber</t>
+          <t>Export.AlvToolbarButton</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>FI document field on the statement-item detail screen</t>
+          <t>Grid toolbar export function code</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -1693,96 +1785,92 @@
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/subSUB_MAIN:SAPLNEW_FEBA:4000/subSUB_APPLICATION:SAPLNEW_FEBA:2200/subAREA1:SAPLNEW_FEBA:2201/txtD2201_BELNR</t>
+          <t>&amp;MB_EXPORT</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>FI document (reached with F2 from the detail screen)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Export.AlvMenuItem</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Context-menu entry. &amp;XXL, not &amp;PC</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>&amp;XXL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Doc.BsegGrid</t>
+          <t>Export.AlvFormatRadio</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Line-item grid on the document overview</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
+          <t>Radio for the format, if that popup appears. VERIFY</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Step 3: statement item detail</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Feban.Detail.DocNumber</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Posting Area 1 Doc. number field. F2 from here opens the FI document</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/usr/cntlCTRL_CONTAINERBSEG/shellcont/shell</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Doc.Col.Amount</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Line-item grid column holding the local-currency amount</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>DMBTR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Doc.ClearingDocField</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Clearing-document field on the line-item detail screen</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1790,14 +1878,14 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/txtBSEG-AUGBL</t>
+          <t>wnd[0]/usr/subSUB_MAIN:SAPLNEW_FEBA:4000/subSUB_APPLICATION:SAPLNEW_FEBA:2200/subAREA1:SAPLNEW_FEBA:2201/txtD2201_BELNR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Cleared items with supplier names</t>
+          <t>Step 4: FI document line items</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
@@ -1808,12 +1896,12 @@
     <row r="29">
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Cleared.Menu</t>
+          <t>Doc.BsegGrid</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Menu path that produces the cleared-items list from the clearing document. menu[5]/menu[3] in the recording</t>
+          <t>Line-item grid on the document overview</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -1828,19 +1916,19 @@
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/mbar/menu[5]/menu[3]</t>
+          <t>wnd[0]/usr/cntlCTRL_CONTAINERBSEG/shellcont/shell</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Cleared.ListAnchor</t>
+          <t>Doc.Col.ClearingDoc</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>A label that exists on the cleared-items list, used to confirm the list actually came up</t>
+          <t>Clearing-document column. Audit3 and Audit5 both double-clicked AUGBL; Audit.vbs used DMBTR and Audit2 PRCTR, which were just where the cursor sat</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -1850,188 +1938,192 @@
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>AUGBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Doc.Col.PostingKey</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Posting-key column, so the macro can pick the key-40 line rather than whichever row the cursor lands on. VERIFY</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/usr/lbl[28,7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>FEBAN statement-list export (optional period context)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>BSCHL</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Export.AlvToolbarButton</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Function code of the export button on the FEBAN grid's own toolbar. The recording never exported this grid, so this is unrecorded and the whole step is optional -- leave both blank to skip it. VERIFY</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>&amp;MB_EXPORT</t>
-        </is>
-      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Step 5: line-item detail</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Export.AlvMenuItem</t>
+          <t>Doc.ClearingDocField</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Context-menu entry for local file / spreadsheet. VERIFY</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Clearing-document field. F2 from here opens the clearing document</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>&amp;PC</t>
+          <t>wnd[0]/usr/txtBSEG-AUGBL</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Export.AlvFormatRadio</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Radio button for the file format, if that popup appears. VERIFY</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="n"/>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Step 6: Environment &gt; Payment Usage</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>Classic list export (List &gt; Save/Send &gt; File)</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>PaymentUsage.Menu</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Menu path to the batch's payment documents. Confirmed in all four recordings</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/mbar/menu[5]/menu[3]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="20" t="inlineStr">
         <is>
+          <t>PaymentUsage.ListAnchor</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>An element that exists on that list, used only to confirm the menu landed. Clear it to skip the check</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/chk[1,6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Step 7: classic list export (List &gt; Save/Send &gt; File)</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="20" t="inlineStr">
+        <is>
           <t>Export.ListMenu</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Menu path that opens the save-list dialog</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/mbar/menu[0]/menu[3]/menu[1]</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>Export.FormatOkButton</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the file-format popup</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>wnd[1]/tbar[0]/btn[0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>Save-as dialog</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="19" t="n"/>
-      <c r="F38" s="19" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Save.Path</t>
+          <t>Export.FormatOkButton</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Directory field</t>
+          <t>Confirm the file-format popup</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -2046,24 +2138,24 @@
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_PATH</t>
+          <t>wnd[1]/tbar[0]/btn[0]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Save.FileName</t>
+          <t>Save.Path</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>File name field. The recording left the default in place, so this ID is standard-but-unconfirmed. VERIFY</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Directory field</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
@@ -2073,116 +2165,116 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
+          <t>wnd[1]/usr/ctxtDY_PATH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Save.Encoding</t>
+          <t>Save.FileName</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Encoding field, where present. VERIFY</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>File name field. Confirmed in Audit2.vbs and Audit5.vbs</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
+          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="20" t="inlineStr">
         <is>
+          <t>Save.Encoding</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Encoding field, where present. VERIFY</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="20" t="inlineStr">
+        <is>
           <t>Save.GenerateButton</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the save. btn[0], not btn[11], on this dialog</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the save. btn[0], not btn[11]</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>wnd[1]/tbar[0]/btn[0]</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>Invoice PDF: regular supplier route</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-    </row>
     <row r="44">
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>Invoice.GosToolbox</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>Services-for-object toolbox on the title bar. NOT in the recording -- Audit2.vbs captured no steps. VERIFY</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E44" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/titl/shellcont/shell</t>
-        </is>
-      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Steps 8-9: FBL1N, the ZP payments of the batch (PREDICTED)</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListGrid</t>
+          <t>Fbl1n.CompanyCode</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Attachment-list grid. VERIFY</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Company code. PREDICTED from standard RFITEMAP -- no recording reaches FBL1N. Run modProbe.ProbeCurrentScreen on the FBL1N selection screen to check every Fbl1n.* row at once</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
         </is>
       </c>
       <c r="E45" s="22" t="inlineStr">
@@ -2192,24 +2284,24 @@
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/cntlCONTAINER/shellcont/shell</t>
+          <t>wnd[0]/usr/ctxtDD_BUKRS-LOW</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Invoice.SaveButton</t>
+          <t>Fbl1n.AllItemsRadio</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Save/export button on the attachment list. VERIFY</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>'All items' radio. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
         </is>
       </c>
       <c r="E46" s="22" t="inlineStr">
@@ -2219,35 +2311,51 @@
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[5]</t>
+          <t>wnd[0]/usr/radX_AISEL</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>Level 2: Santander SCF confirming route</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="n"/>
-      <c r="D47" s="19" t="n"/>
-      <c r="E47" s="19" t="n"/>
-      <c r="F47" s="19" t="n"/>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>Fbl1n.PostingDateFrom</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Posting date, low. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/ctxtSO_BUDAT-LOW</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Scf.OpenPayment</t>
+          <t>Fbl1n.PostingDateTo</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>How you get from the cleared-items list into the Santander SCF payment. A menu entry, a button, or a field to put the cursor on and press F2 -- the macro works out which from the control type. BLOCKED: Audit2.vbs recorded nothing, so this is unknown</t>
+          <t>Posting date, high. PREDICTED</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>PREDICTED</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
@@ -2255,22 +2363,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F48" s="23" t="n"/>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/ctxtSO_BUDAT-HIGH</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Scf.InvoiceListMenu</t>
+          <t>Fbl1n.DocNumberFrom</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Menu path that lists the supplier invoices that SCF payment settled. BLOCKED</t>
+          <t>Document number, single value. NOTE: on standard FBL1N the document number lives in dynamic selections, not the main screen -- if the probe cannot find this, leave the whole Fbl1n block blank and use the fallback described in the README. PREDICTED</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>PREDICTED</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
@@ -2278,68 +2390,442 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F49" s="23" t="n"/>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/ctxtSO_BELNR-LOW</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Scf.InvoiceListAnchor</t>
+          <t>Fbl1n.DocNumberMultiSelect</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Optional. An element that exists on that invoice list, used only to confirm the previous step landed where expected. BLOCKED</t>
+          <t>The arrow button beside it that opens multiple selection. PREDICTED</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/btn%_SO_BELNR_%_APP_%-VALU_PUSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>MultiSel.PasteFromClipboard</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>'Upload from clipboard' on the multiple-selection dialog. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>MultiSel.Confirm</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Copy/Execute on that dialog. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Fbl1n.ExecuteButton</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Execute. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/tbar[1]/btn[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>Fbl1n.ResultGrid</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>ALV grid of vendor line items. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/cntlCONTAINER/shellcont/shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Fbl1n.Col.Amount</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>DC amount column. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>DMSHB</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>Fbl1n.Col.DocNumber</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Document number column. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>BELNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Fbl1n.Col.Vendor</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Vendor account column. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>LIFNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Fbl1n.Col.VendorName</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Vendor name column. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>NAME1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>Step 10: the invoice PDF (NOT RECORDED)</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="n"/>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="19" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.GosToolbox</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Services-for-object toolbox on the title bar. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/titl/shellcont/shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.AttachListGrid</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Attachment-list grid. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/cntlCONTAINER/shellcont/shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.SaveButton</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Save/export button on the attachment list. PREDICTED</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>PREDICTED</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/tbar[0]/btn[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>Step 10, Santander SCF only: the extra hop (NOT RECORDED)</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="19" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Scf.OpenInvoices</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>How you get from the SCF payment to the invoices it settled. A menu entry, a button, or a field to focus and F2 -- the macro reads the control type and does the right thing. BLOCKED: no recording covers it</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E64" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F50" s="23" t="n"/>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="B52" s="16" t="inlineStr">
+      <c r="F64" s="23" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>Scf.InvoiceListMenu</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Menu path that lists those invoices. BLOCKED</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="B53" s="16" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="B54" s="16" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>The recording entered dates as 8 digits with no separators (01092025). The Control sheet's 'SAP date format' is set to DDMMYYYY to match. Do not change it to DMY unless you have checked that this system accepts 01.09.2025 as well.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B43:F43"/>
+  <mergeCells count="15">
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B54:F54"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2352,7 +2838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:O61"/>
+  <dimension ref="A2:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2370,6 +2856,7 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2462,6 +2949,11 @@
           <t>Message</t>
         </is>
       </c>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <t>Include?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n">
@@ -2472,18 +2964,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>IF($E5="","",DATE(YEAR($E5),MONTH($E5),1))</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>IF($E5="","",EOMONTH($E5,0))</f>
         <v/>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="27" t="n">
         <v>45903</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="28" t="n">
         <v>8072447.42</v>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
@@ -2492,7 +2984,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2501,8 +2993,13 @@
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
-      <c r="N5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
       <c r="O5" s="15" t="n"/>
+      <c r="P5" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -2513,18 +3010,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>IF($E6="","",DATE(YEAR($E6),MONTH($E6),1))</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>IF($E6="","",EOMONTH($E6,0))</f>
         <v/>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="27" t="n">
         <v>45912</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="28" t="n">
         <v>2161788.23</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -2537,7 +3034,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -2546,8 +3043,13 @@
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
-      <c r="N6" s="29" t="n"/>
+      <c r="N6" s="30" t="n"/>
       <c r="O6" s="15" t="n"/>
+      <c r="P6" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -2558,18 +3060,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>IF($E7="","",DATE(YEAR($E7),MONTH($E7),1))</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>IF($E7="","",EOMONTH($E7,0))</f>
         <v/>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="27" t="n">
         <v>45915</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="28" t="n">
         <v>5988033.6</v>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -2578,7 +3080,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2587,8 +3089,13 @@
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15" t="n"/>
-      <c r="N7" s="29" t="n"/>
+      <c r="N7" s="30" t="n"/>
       <c r="O7" s="15" t="n"/>
+      <c r="P7" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -2599,18 +3106,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>IF($E8="","",DATE(YEAR($E8),MONTH($E8),1))</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>IF($E8="","",EOMONTH($E8,0))</f>
         <v/>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="27" t="n">
         <v>45922</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="28" t="n">
         <v>2942842.52</v>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
@@ -2619,7 +3126,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2628,8 +3135,13 @@
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
-      <c r="N8" s="29" t="n"/>
+      <c r="N8" s="30" t="n"/>
       <c r="O8" s="15" t="n"/>
+      <c r="P8" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -2640,18 +3152,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>IF($E9="","",DATE(YEAR($E9),MONTH($E9),1))</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>IF($E9="","",EOMONTH($E9,0))</f>
         <v/>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="27" t="n">
         <v>45924</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="28" t="n">
         <v>8617262.93</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -2664,7 +3176,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2673,8 +3185,13 @@
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
-      <c r="N9" s="29" t="n"/>
+      <c r="N9" s="30" t="n"/>
       <c r="O9" s="15" t="n"/>
+      <c r="P9" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -2685,18 +3202,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>IF($E10="","",DATE(YEAR($E10),MONTH($E10),1))</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>IF($E10="","",EOMONTH($E10,0))</f>
         <v/>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="27" t="n">
         <v>45925</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="28" t="n">
         <v>2968313.21</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -2709,7 +3226,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -2718,8 +3235,13 @@
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
-      <c r="N10" s="29" t="n"/>
+      <c r="N10" s="30" t="n"/>
       <c r="O10" s="15" t="n"/>
+      <c r="P10" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -2730,18 +3252,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>IF($E11="","",DATE(YEAR($E11),MONTH($E11),1))</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>IF($E11="","",EOMONTH($E11,0))</f>
         <v/>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="27" t="n">
         <v>45930</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2754,7 +3276,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I11" s="28" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2763,8 +3285,13 @@
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="15" t="n"/>
       <c r="M11" s="15" t="n"/>
-      <c r="N11" s="29" t="n"/>
+      <c r="N11" s="30" t="n"/>
       <c r="O11" s="15" t="n"/>
+      <c r="P11" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -2775,18 +3302,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>IF($E12="","",DATE(YEAR($E12),MONTH($E12),1))</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>IF($E12="","",EOMONTH($E12,0))</f>
         <v/>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="27" t="n">
         <v>45931</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="28" t="n">
         <v>4483676.08</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -2799,7 +3326,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -2808,8 +3335,13 @@
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
-      <c r="N12" s="29" t="n"/>
+      <c r="N12" s="30" t="n"/>
       <c r="O12" s="15" t="n"/>
+      <c r="P12" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -2820,18 +3352,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>IF($E13="","",DATE(YEAR($E13),MONTH($E13),1))</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>IF($E13="","",EOMONTH($E13,0))</f>
         <v/>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="27" t="n">
         <v>45933</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="28" t="n">
         <v>3412038.97</v>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -2840,7 +3372,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I13" s="28" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2849,8 +3381,13 @@
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
-      <c r="N13" s="29" t="n"/>
+      <c r="N13" s="30" t="n"/>
       <c r="O13" s="15" t="n"/>
+      <c r="P13" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -2861,18 +3398,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>IF($E14="","",DATE(YEAR($E14),MONTH($E14),1))</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>IF($E14="","",EOMONTH($E14,0))</f>
         <v/>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="27" t="n">
         <v>45943</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="28" t="n">
         <v>3385329.45</v>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
@@ -2881,7 +3418,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2890,8 +3427,13 @@
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
-      <c r="N14" s="29" t="n"/>
+      <c r="N14" s="30" t="n"/>
       <c r="O14" s="15" t="n"/>
+      <c r="P14" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -2902,18 +3444,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>IF($E15="","",DATE(YEAR($E15),MONTH($E15),1))</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>IF($E15="","",EOMONTH($E15,0))</f>
         <v/>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="27" t="n">
         <v>45950</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="28" t="n">
         <v>4898587.92</v>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
@@ -2922,7 +3464,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I15" s="28" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2931,8 +3473,13 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="15" t="n"/>
-      <c r="N15" s="29" t="n"/>
+      <c r="N15" s="30" t="n"/>
       <c r="O15" s="15" t="n"/>
+      <c r="P15" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -2943,18 +3490,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <f>IF($E16="","",DATE(YEAR($E16),MONTH($E16),1))</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <f>IF($E16="","",EOMONTH($E16,0))</f>
         <v/>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="27" t="n">
         <v>45954</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="28" t="n">
         <v>3480924.53</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -2967,7 +3514,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I16" s="28" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>date_stored_as_text; party_whitespace_cleaned</t>
         </is>
@@ -2976,8 +3523,13 @@
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
-      <c r="N16" s="29" t="n"/>
+      <c r="N16" s="30" t="n"/>
       <c r="O16" s="15" t="n"/>
+      <c r="P16" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -2988,18 +3540,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <f>IF($E17="","",DATE(YEAR($E17),MONTH($E17),1))</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <f>IF($E17="","",EOMONTH($E17,0))</f>
         <v/>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <v>45957</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="28" t="n">
         <v>2614260.03</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -3012,7 +3564,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3021,8 +3573,13 @@
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
-      <c r="N17" s="29" t="n"/>
+      <c r="N17" s="30" t="n"/>
       <c r="O17" s="15" t="n"/>
+      <c r="P17" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -3033,18 +3590,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <f>IF($E18="","",DATE(YEAR($E18),MONTH($E18),1))</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>IF($E18="","",EOMONTH($E18,0))</f>
         <v/>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="27" t="n">
         <v>45961</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -3057,7 +3614,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3066,8 +3623,13 @@
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
-      <c r="N18" s="29" t="n"/>
+      <c r="N18" s="30" t="n"/>
       <c r="O18" s="15" t="n"/>
+      <c r="P18" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -3078,18 +3640,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="27">
         <f>IF($E19="","",DATE(YEAR($E19),MONTH($E19),1))</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <f>IF($E19="","",EOMONTH($E19,0))</f>
         <v/>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="27" t="n">
         <v>45961</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="28" t="n">
         <v>3317511.83</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -3102,7 +3664,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3111,8 +3673,13 @@
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
-      <c r="N19" s="29" t="n"/>
+      <c r="N19" s="30" t="n"/>
       <c r="O19" s="15" t="n"/>
+      <c r="P19" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -3123,18 +3690,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>IF($E20="","",DATE(YEAR($E20),MONTH($E20),1))</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>IF($E20="","",EOMONTH($E20,0))</f>
         <v/>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="27" t="n">
         <v>45964</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="28" t="n">
         <v>3724798.28</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -3147,13 +3714,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I20" s="28" t="inlineStr"/>
+      <c r="I20" s="29" t="inlineStr"/>
       <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
-      <c r="N20" s="29" t="n"/>
+      <c r="N20" s="30" t="n"/>
       <c r="O20" s="15" t="n"/>
+      <c r="P20" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
@@ -3164,18 +3736,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>IF($E21="","",DATE(YEAR($E21),MONTH($E21),1))</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>IF($E21="","",EOMONTH($E21,0))</f>
         <v/>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="27" t="n">
         <v>45966</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="28" t="n">
         <v>5044035.13</v>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
@@ -3184,7 +3756,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I21" s="28" t="inlineStr">
+      <c r="I21" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3193,8 +3765,13 @@
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15" t="n"/>
-      <c r="N21" s="29" t="n"/>
+      <c r="N21" s="30" t="n"/>
       <c r="O21" s="15" t="n"/>
+      <c r="P21" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -3205,18 +3782,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>IF($E22="","",DATE(YEAR($E22),MONTH($E22),1))</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>IF($E22="","",EOMONTH($E22,0))</f>
         <v/>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="27" t="n">
         <v>45978</v>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="28" t="n">
         <v>5245536.51</v>
       </c>
       <c r="G22" s="10" t="inlineStr"/>
@@ -3225,7 +3802,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr">
+      <c r="I22" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3234,8 +3811,13 @@
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
-      <c r="N22" s="29" t="n"/>
+      <c r="N22" s="30" t="n"/>
       <c r="O22" s="15" t="n"/>
+      <c r="P22" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -3246,18 +3828,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <f>IF($E23="","",DATE(YEAR($E23),MONTH($E23),1))</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="27">
         <f>IF($E23="","",EOMONTH($E23,0))</f>
         <v/>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="27" t="n">
         <v>45989</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="28" t="n">
         <v>4173936.71</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -3270,7 +3852,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I23" s="28" t="inlineStr">
+      <c r="I23" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3279,8 +3861,13 @@
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
-      <c r="N23" s="29" t="n"/>
+      <c r="N23" s="30" t="n"/>
       <c r="O23" s="15" t="n"/>
+      <c r="P23" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -3291,18 +3878,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <f>IF($E24="","",DATE(YEAR($E24),MONTH($E24),1))</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <f>IF($E24="","",EOMONTH($E24,0))</f>
         <v/>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="27" t="n">
         <v>45989</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -3315,7 +3902,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
+      <c r="I24" s="29" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3324,8 +3911,13 @@
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
-      <c r="N24" s="29" t="n"/>
+      <c r="N24" s="30" t="n"/>
       <c r="O24" s="15" t="n"/>
+      <c r="P24" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -3336,18 +3928,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>IF($E25="","",DATE(YEAR($E25),MONTH($E25),1))</f>
         <v/>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>IF($E25="","",EOMONTH($E25,0))</f>
         <v/>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="27" t="n">
         <v>46020</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="28" t="n">
         <v>2828677.68</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -3360,7 +3952,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I25" s="28" t="inlineStr">
+      <c r="I25" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3369,8 +3961,13 @@
       <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n"/>
       <c r="M25" s="15" t="n"/>
-      <c r="N25" s="29" t="n"/>
+      <c r="N25" s="30" t="n"/>
       <c r="O25" s="15" t="n"/>
+      <c r="P25" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -3381,18 +3978,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <f>IF($E26="","",DATE(YEAR($E26),MONTH($E26),1))</f>
         <v/>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="27">
         <f>IF($E26="","",EOMONTH($E26,0))</f>
         <v/>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="27" t="n">
         <v>46022</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -3405,7 +4002,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I26" s="28" t="inlineStr">
+      <c r="I26" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3414,8 +4011,13 @@
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
-      <c r="N26" s="29" t="n"/>
+      <c r="N26" s="30" t="n"/>
       <c r="O26" s="15" t="n"/>
+      <c r="P26" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -3426,18 +4028,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <f>IF($E27="","",DATE(YEAR($E27),MONTH($E27),1))</f>
         <v/>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="27">
         <f>IF($E27="","",EOMONTH($E27,0))</f>
         <v/>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="27" t="n">
         <v>46022</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="28" t="n">
         <v>2233241.99</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3450,7 +4052,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I27" s="28" t="inlineStr">
+      <c r="I27" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3459,8 +4061,13 @@
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15" t="n"/>
-      <c r="N27" s="29" t="n"/>
+      <c r="N27" s="30" t="n"/>
       <c r="O27" s="15" t="n"/>
+      <c r="P27" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -3471,18 +4078,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <f>IF($E28="","",DATE(YEAR($E28),MONTH($E28),1))</f>
         <v/>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="27">
         <f>IF($E28="","",EOMONTH($E28,0))</f>
         <v/>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="27" t="n">
         <v>46024</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="28" t="n">
         <v>3489077.98</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -3495,7 +4102,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I28" s="28" t="inlineStr">
+      <c r="I28" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -3504,8 +4111,13 @@
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
-      <c r="N28" s="29" t="n"/>
+      <c r="N28" s="30" t="n"/>
       <c r="O28" s="15" t="n"/>
+      <c r="P28" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -3516,18 +4128,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <f>IF($E29="","",DATE(YEAR($E29),MONTH($E29),1))</f>
         <v/>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="27">
         <f>IF($E29="","",EOMONTH($E29,0))</f>
         <v/>
       </c>
-      <c r="E29" s="26" t="n">
+      <c r="E29" s="27" t="n">
         <v>46028</v>
       </c>
-      <c r="F29" s="27" t="n">
+      <c r="F29" s="28" t="n">
         <v>4395299.21</v>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -3536,7 +4148,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I29" s="28" t="inlineStr">
+      <c r="I29" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3545,8 +4157,13 @@
       <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
-      <c r="N29" s="29" t="n"/>
+      <c r="N29" s="30" t="n"/>
       <c r="O29" s="15" t="n"/>
+      <c r="P29" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -3557,18 +4174,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="27">
         <f>IF($E30="","",DATE(YEAR($E30),MONTH($E30),1))</f>
         <v/>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="27">
         <f>IF($E30="","",EOMONTH($E30,0))</f>
         <v/>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="27" t="n">
         <v>46031</v>
       </c>
-      <c r="F30" s="27" t="n">
+      <c r="F30" s="28" t="n">
         <v>8800991.4</v>
       </c>
       <c r="G30" s="10" t="inlineStr"/>
@@ -3577,7 +4194,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I30" s="28" t="inlineStr">
+      <c r="I30" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3586,8 +4203,13 @@
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
       <c r="M30" s="15" t="n"/>
-      <c r="N30" s="29" t="n"/>
+      <c r="N30" s="30" t="n"/>
       <c r="O30" s="15" t="n"/>
+      <c r="P30" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -3598,18 +4220,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="27">
         <f>IF($E31="","",DATE(YEAR($E31),MONTH($E31),1))</f>
         <v/>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="27">
         <f>IF($E31="","",EOMONTH($E31,0))</f>
         <v/>
       </c>
-      <c r="E31" s="26" t="n">
+      <c r="E31" s="27" t="n">
         <v>46038</v>
       </c>
-      <c r="F31" s="27" t="n">
+      <c r="F31" s="28" t="n">
         <v>6502110.67</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3622,7 +4244,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I31" s="29" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3631,8 +4253,13 @@
       <c r="K31" s="15" t="n"/>
       <c r="L31" s="15" t="n"/>
       <c r="M31" s="15" t="n"/>
-      <c r="N31" s="29" t="n"/>
+      <c r="N31" s="30" t="n"/>
       <c r="O31" s="15" t="n"/>
+      <c r="P31" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -3643,18 +4270,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="27">
         <f>IF($E32="","",DATE(YEAR($E32),MONTH($E32),1))</f>
         <v/>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="27">
         <f>IF($E32="","",EOMONTH($E32,0))</f>
         <v/>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="27" t="n">
         <v>46051</v>
       </c>
-      <c r="F32" s="27" t="n">
+      <c r="F32" s="28" t="n">
         <v>3463573.21</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -3667,7 +4294,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I32" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3676,8 +4303,13 @@
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
-      <c r="N32" s="29" t="n"/>
+      <c r="N32" s="30" t="n"/>
       <c r="O32" s="15" t="n"/>
+      <c r="P32" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
@@ -3688,18 +4320,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="27">
         <f>IF($E33="","",DATE(YEAR($E33),MONTH($E33),1))</f>
         <v/>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="27">
         <f>IF($E33="","",EOMONTH($E33,0))</f>
         <v/>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="27" t="n">
         <v>46052</v>
       </c>
-      <c r="F33" s="27" t="n">
+      <c r="F33" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -3712,7 +4344,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
+      <c r="I33" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3721,8 +4353,13 @@
       <c r="K33" s="15" t="n"/>
       <c r="L33" s="15" t="n"/>
       <c r="M33" s="15" t="n"/>
-      <c r="N33" s="29" t="n"/>
+      <c r="N33" s="30" t="n"/>
       <c r="O33" s="15" t="n"/>
+      <c r="P33" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -3733,18 +4370,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <f>IF($E34="","",DATE(YEAR($E34),MONTH($E34),1))</f>
         <v/>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="27">
         <f>IF($E34="","",EOMONTH($E34,0))</f>
         <v/>
       </c>
-      <c r="E34" s="26" t="n">
+      <c r="E34" s="27" t="n">
         <v>46055</v>
       </c>
-      <c r="F34" s="27" t="n">
+      <c r="F34" s="28" t="n">
         <v>3679179.76</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -3757,7 +4394,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
+      <c r="I34" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -3766,8 +4403,13 @@
       <c r="K34" s="15" t="n"/>
       <c r="L34" s="15" t="n"/>
       <c r="M34" s="15" t="n"/>
-      <c r="N34" s="29" t="n"/>
+      <c r="N34" s="30" t="n"/>
       <c r="O34" s="15" t="n"/>
+      <c r="P34" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -3778,18 +4420,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="27">
         <f>IF($E35="","",DATE(YEAR($E35),MONTH($E35),1))</f>
         <v/>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="27">
         <f>IF($E35="","",EOMONTH($E35,0))</f>
         <v/>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="27" t="n">
         <v>46057</v>
       </c>
-      <c r="F35" s="27" t="n">
+      <c r="F35" s="28" t="n">
         <v>3674499.52</v>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
@@ -3798,7 +4440,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I35" s="28" t="inlineStr">
+      <c r="I35" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3807,8 +4449,13 @@
       <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="15" t="n"/>
-      <c r="N35" s="29" t="n"/>
+      <c r="N35" s="30" t="n"/>
       <c r="O35" s="15" t="n"/>
+      <c r="P35" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3819,18 +4466,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="27">
         <f>IF($E36="","",DATE(YEAR($E36),MONTH($E36),1))</f>
         <v/>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="27">
         <f>IF($E36="","",EOMONTH($E36,0))</f>
         <v/>
       </c>
-      <c r="E36" s="26" t="n">
+      <c r="E36" s="27" t="n">
         <v>46080</v>
       </c>
-      <c r="F36" s="27" t="n">
+      <c r="F36" s="28" t="n">
         <v>6558159.12</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -3843,7 +4490,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I36" s="28" t="inlineStr">
+      <c r="I36" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3852,8 +4499,13 @@
       <c r="K36" s="15" t="n"/>
       <c r="L36" s="15" t="n"/>
       <c r="M36" s="15" t="n"/>
-      <c r="N36" s="29" t="n"/>
+      <c r="N36" s="30" t="n"/>
       <c r="O36" s="15" t="n"/>
+      <c r="P36" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -3864,18 +4516,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="27">
         <f>IF($E37="","",DATE(YEAR($E37),MONTH($E37),1))</f>
         <v/>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="27">
         <f>IF($E37="","",EOMONTH($E37,0))</f>
         <v/>
       </c>
-      <c r="E37" s="26" t="n">
+      <c r="E37" s="27" t="n">
         <v>46080</v>
       </c>
-      <c r="F37" s="27" t="n">
+      <c r="F37" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -3888,7 +4540,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I37" s="28" t="inlineStr">
+      <c r="I37" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3897,8 +4549,13 @@
       <c r="K37" s="15" t="n"/>
       <c r="L37" s="15" t="n"/>
       <c r="M37" s="15" t="n"/>
-      <c r="N37" s="29" t="n"/>
+      <c r="N37" s="30" t="n"/>
       <c r="O37" s="15" t="n"/>
+      <c r="P37" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -3909,18 +4566,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="27">
         <f>IF($E38="","",DATE(YEAR($E38),MONTH($E38),1))</f>
         <v/>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="27">
         <f>IF($E38="","",EOMONTH($E38,0))</f>
         <v/>
       </c>
-      <c r="E38" s="26" t="n">
+      <c r="E38" s="27" t="n">
         <v>46083</v>
       </c>
-      <c r="F38" s="27" t="n">
+      <c r="F38" s="28" t="n">
         <v>3562528.89</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3933,7 +4590,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I38" s="28" t="inlineStr">
+      <c r="I38" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3942,8 +4599,13 @@
       <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n"/>
       <c r="M38" s="15" t="n"/>
-      <c r="N38" s="29" t="n"/>
+      <c r="N38" s="30" t="n"/>
       <c r="O38" s="15" t="n"/>
+      <c r="P38" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -3954,18 +4616,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="27">
         <f>IF($E39="","",DATE(YEAR($E39),MONTH($E39),1))</f>
         <v/>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="27">
         <f>IF($E39="","",EOMONTH($E39,0))</f>
         <v/>
       </c>
-      <c r="E39" s="26" t="n">
+      <c r="E39" s="27" t="n">
         <v>46085</v>
       </c>
-      <c r="F39" s="27" t="n">
+      <c r="F39" s="28" t="n">
         <v>8557737.25</v>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
@@ -3974,7 +4636,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I39" s="28" t="inlineStr">
+      <c r="I39" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -3983,8 +4645,13 @@
       <c r="K39" s="15" t="n"/>
       <c r="L39" s="15" t="n"/>
       <c r="M39" s="15" t="n"/>
-      <c r="N39" s="29" t="n"/>
+      <c r="N39" s="30" t="n"/>
       <c r="O39" s="15" t="n"/>
+      <c r="P39" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
@@ -3995,18 +4662,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="27">
         <f>IF($E40="","",DATE(YEAR($E40),MONTH($E40),1))</f>
         <v/>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="27">
         <f>IF($E40="","",EOMONTH($E40,0))</f>
         <v/>
       </c>
-      <c r="E40" s="26" t="n">
+      <c r="E40" s="27" t="n">
         <v>46093</v>
       </c>
-      <c r="F40" s="27" t="n">
+      <c r="F40" s="28" t="n">
         <v>2301959.84</v>
       </c>
       <c r="G40" s="10" t="inlineStr"/>
@@ -4015,7 +4682,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I40" s="28" t="inlineStr">
+      <c r="I40" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4024,8 +4691,13 @@
       <c r="K40" s="15" t="n"/>
       <c r="L40" s="15" t="n"/>
       <c r="M40" s="15" t="n"/>
-      <c r="N40" s="29" t="n"/>
+      <c r="N40" s="30" t="n"/>
       <c r="O40" s="15" t="n"/>
+      <c r="P40" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n">
@@ -4036,18 +4708,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C41" s="26">
+      <c r="C41" s="27">
         <f>IF($E41="","",DATE(YEAR($E41),MONTH($E41),1))</f>
         <v/>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="27">
         <f>IF($E41="","",EOMONTH($E41,0))</f>
         <v/>
       </c>
-      <c r="E41" s="26" t="n">
+      <c r="E41" s="27" t="n">
         <v>46108</v>
       </c>
-      <c r="F41" s="27" t="n">
+      <c r="F41" s="28" t="n">
         <v>5989486.48</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -4060,7 +4732,7 @@
           <t>DS Smith Paper Limited</t>
         </is>
       </c>
-      <c r="I41" s="28" t="inlineStr">
+      <c r="I41" s="29" t="inlineStr">
         <is>
           <t>ref_holds_a_party_name_not_a_transaction_description; party_whitespace_cleaned</t>
         </is>
@@ -4069,8 +4741,13 @@
       <c r="K41" s="15" t="n"/>
       <c r="L41" s="15" t="n"/>
       <c r="M41" s="15" t="n"/>
-      <c r="N41" s="29" t="n"/>
+      <c r="N41" s="30" t="n"/>
       <c r="O41" s="15" t="n"/>
+      <c r="P41" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
@@ -4081,18 +4758,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="27">
         <f>IF($E42="","",DATE(YEAR($E42),MONTH($E42),1))</f>
         <v/>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="27">
         <f>IF($E42="","",EOMONTH($E42,0))</f>
         <v/>
       </c>
-      <c r="E42" s="26" t="n">
+      <c r="E42" s="27" t="n">
         <v>46112</v>
       </c>
-      <c r="F42" s="27" t="n">
+      <c r="F42" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -4105,13 +4782,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I42" s="28" t="inlineStr"/>
+      <c r="I42" s="29" t="inlineStr"/>
       <c r="J42" s="15" t="n"/>
       <c r="K42" s="15" t="n"/>
       <c r="L42" s="15" t="n"/>
       <c r="M42" s="15" t="n"/>
-      <c r="N42" s="29" t="n"/>
+      <c r="N42" s="30" t="n"/>
       <c r="O42" s="15" t="n"/>
+      <c r="P42" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n">
@@ -4122,18 +4804,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="27">
         <f>IF($E43="","",DATE(YEAR($E43),MONTH($E43),1))</f>
         <v/>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="27">
         <f>IF($E43="","",EOMONTH($E43,0))</f>
         <v/>
       </c>
-      <c r="E43" s="26" t="n">
+      <c r="E43" s="27" t="n">
         <v>46113</v>
       </c>
-      <c r="F43" s="27" t="n">
+      <c r="F43" s="28" t="n">
         <v>3316944.84</v>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -4146,13 +4828,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I43" s="28" t="inlineStr"/>
+      <c r="I43" s="29" t="inlineStr"/>
       <c r="J43" s="15" t="n"/>
       <c r="K43" s="15" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15" t="n"/>
-      <c r="N43" s="29" t="n"/>
+      <c r="N43" s="30" t="n"/>
       <c r="O43" s="15" t="n"/>
+      <c r="P43" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -4163,18 +4850,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <f>IF($E44="","",DATE(YEAR($E44),MONTH($E44),1))</f>
         <v/>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="27">
         <f>IF($E44="","",EOMONTH($E44,0))</f>
         <v/>
       </c>
-      <c r="E44" s="26" t="n">
+      <c r="E44" s="27" t="n">
         <v>46128</v>
       </c>
-      <c r="F44" s="27" t="n">
+      <c r="F44" s="28" t="n">
         <v>2611670.69</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -4187,13 +4874,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I44" s="28" t="inlineStr"/>
+      <c r="I44" s="29" t="inlineStr"/>
       <c r="J44" s="15" t="n"/>
       <c r="K44" s="15" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15" t="n"/>
-      <c r="N44" s="29" t="n"/>
+      <c r="N44" s="30" t="n"/>
       <c r="O44" s="15" t="n"/>
+      <c r="P44" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
@@ -4204,18 +4896,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C45" s="26">
+      <c r="C45" s="27">
         <f>IF($E45="","",DATE(YEAR($E45),MONTH($E45),1))</f>
         <v/>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="27">
         <f>IF($E45="","",EOMONTH($E45,0))</f>
         <v/>
       </c>
-      <c r="E45" s="26" t="n">
+      <c r="E45" s="27" t="n">
         <v>46129</v>
       </c>
-      <c r="F45" s="27" t="n">
+      <c r="F45" s="28" t="n">
         <v>4996002.96</v>
       </c>
       <c r="G45" s="10" t="inlineStr"/>
@@ -4224,7 +4916,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I45" s="28" t="inlineStr">
+      <c r="I45" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4233,8 +4925,13 @@
       <c r="K45" s="15" t="n"/>
       <c r="L45" s="15" t="n"/>
       <c r="M45" s="15" t="n"/>
-      <c r="N45" s="29" t="n"/>
+      <c r="N45" s="30" t="n"/>
       <c r="O45" s="15" t="n"/>
+      <c r="P45" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
@@ -4245,18 +4942,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <f>IF($E46="","",DATE(YEAR($E46),MONTH($E46),1))</f>
         <v/>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="27">
         <f>IF($E46="","",EOMONTH($E46,0))</f>
         <v/>
       </c>
-      <c r="E46" s="26" t="n">
+      <c r="E46" s="27" t="n">
         <v>46135</v>
       </c>
-      <c r="F46" s="27" t="n">
+      <c r="F46" s="28" t="n">
         <v>2334786.77</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -4269,7 +4966,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I46" s="28" t="inlineStr">
+      <c r="I46" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4278,8 +4975,13 @@
       <c r="K46" s="15" t="n"/>
       <c r="L46" s="15" t="n"/>
       <c r="M46" s="15" t="n"/>
-      <c r="N46" s="29" t="n"/>
+      <c r="N46" s="30" t="n"/>
       <c r="O46" s="15" t="n"/>
+      <c r="P46" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
@@ -4290,18 +4992,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="27">
         <f>IF($E47="","",DATE(YEAR($E47),MONTH($E47),1))</f>
         <v/>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="27">
         <f>IF($E47="","",EOMONTH($E47,0))</f>
         <v/>
       </c>
-      <c r="E47" s="26" t="n">
+      <c r="E47" s="27" t="n">
         <v>46139</v>
       </c>
-      <c r="F47" s="27" t="n">
+      <c r="F47" s="28" t="n">
         <v>2598639.67</v>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -4314,7 +5016,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I47" s="28" t="inlineStr">
+      <c r="I47" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4323,8 +5025,13 @@
       <c r="K47" s="15" t="n"/>
       <c r="L47" s="15" t="n"/>
       <c r="M47" s="15" t="n"/>
-      <c r="N47" s="29" t="n"/>
+      <c r="N47" s="30" t="n"/>
       <c r="O47" s="15" t="n"/>
+      <c r="P47" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
@@ -4335,18 +5042,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C48" s="26">
+      <c r="C48" s="27">
         <f>IF($E48="","",DATE(YEAR($E48),MONTH($E48),1))</f>
         <v/>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="27">
         <f>IF($E48="","",EOMONTH($E48,0))</f>
         <v/>
       </c>
-      <c r="E48" s="26" t="n">
+      <c r="E48" s="27" t="n">
         <v>46142</v>
       </c>
-      <c r="F48" s="27" t="n">
+      <c r="F48" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -4359,13 +5066,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I48" s="28" t="inlineStr"/>
+      <c r="I48" s="29" t="inlineStr"/>
       <c r="J48" s="15" t="n"/>
       <c r="K48" s="15" t="n"/>
       <c r="L48" s="15" t="n"/>
       <c r="M48" s="15" t="n"/>
-      <c r="N48" s="29" t="n"/>
+      <c r="N48" s="30" t="n"/>
       <c r="O48" s="15" t="n"/>
+      <c r="P48" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
@@ -4376,18 +5088,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C49" s="26">
+      <c r="C49" s="27">
         <f>IF($E49="","",DATE(YEAR($E49),MONTH($E49),1))</f>
         <v/>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="27">
         <f>IF($E49="","",EOMONTH($E49,0))</f>
         <v/>
       </c>
-      <c r="E49" s="26" t="n">
+      <c r="E49" s="27" t="n">
         <v>46142</v>
       </c>
-      <c r="F49" s="27" t="n">
+      <c r="F49" s="28" t="n">
         <v>3232025.51</v>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -4400,7 +5112,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I49" s="28" t="inlineStr">
+      <c r="I49" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4409,8 +5121,13 @@
       <c r="K49" s="15" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15" t="n"/>
-      <c r="N49" s="29" t="n"/>
+      <c r="N49" s="30" t="n"/>
       <c r="O49" s="15" t="n"/>
+      <c r="P49" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
@@ -4421,18 +5138,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C50" s="26">
+      <c r="C50" s="27">
         <f>IF($E50="","",DATE(YEAR($E50),MONTH($E50),1))</f>
         <v/>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="27">
         <f>IF($E50="","",EOMONTH($E50,0))</f>
         <v/>
       </c>
-      <c r="E50" s="26" t="n">
+      <c r="E50" s="27" t="n">
         <v>46147</v>
       </c>
-      <c r="F50" s="27" t="n">
+      <c r="F50" s="28" t="n">
         <v>3723586.74</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -4445,13 +5162,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I50" s="28" t="inlineStr"/>
+      <c r="I50" s="29" t="inlineStr"/>
       <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="n"/>
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15" t="n"/>
-      <c r="N50" s="29" t="n"/>
+      <c r="N50" s="30" t="n"/>
       <c r="O50" s="15" t="n"/>
+      <c r="P50" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
@@ -4462,18 +5184,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C51" s="26">
+      <c r="C51" s="27">
         <f>IF($E51="","",DATE(YEAR($E51),MONTH($E51),1))</f>
         <v/>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="27">
         <f>IF($E51="","",EOMONTH($E51,0))</f>
         <v/>
       </c>
-      <c r="E51" s="26" t="n">
+      <c r="E51" s="27" t="n">
         <v>46150</v>
       </c>
-      <c r="F51" s="27" t="n">
+      <c r="F51" s="28" t="n">
         <v>5009315.83</v>
       </c>
       <c r="G51" s="10" t="inlineStr"/>
@@ -4482,7 +5204,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I51" s="28" t="inlineStr">
+      <c r="I51" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -4491,8 +5213,13 @@
       <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15" t="n"/>
-      <c r="N51" s="29" t="n"/>
+      <c r="N51" s="30" t="n"/>
       <c r="O51" s="15" t="n"/>
+      <c r="P51" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
@@ -4503,18 +5230,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C52" s="26">
+      <c r="C52" s="27">
         <f>IF($E52="","",DATE(YEAR($E52),MONTH($E52),1))</f>
         <v/>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="27">
         <f>IF($E52="","",EOMONTH($E52,0))</f>
         <v/>
       </c>
-      <c r="E52" s="26" t="n">
+      <c r="E52" s="27" t="n">
         <v>46157</v>
       </c>
-      <c r="F52" s="27" t="n">
+      <c r="F52" s="28" t="n">
         <v>4340970.4</v>
       </c>
       <c r="G52" s="10" t="inlineStr"/>
@@ -4523,7 +5250,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I52" s="28" t="inlineStr">
+      <c r="I52" s="29" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -4532,8 +5259,13 @@
       <c r="K52" s="15" t="n"/>
       <c r="L52" s="15" t="n"/>
       <c r="M52" s="15" t="n"/>
-      <c r="N52" s="29" t="n"/>
+      <c r="N52" s="30" t="n"/>
       <c r="O52" s="15" t="n"/>
+      <c r="P52" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
@@ -4544,18 +5276,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C53" s="26">
+      <c r="C53" s="27">
         <f>IF($E53="","",DATE(YEAR($E53),MONTH($E53),1))</f>
         <v/>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="27">
         <f>IF($E53="","",EOMONTH($E53,0))</f>
         <v/>
       </c>
-      <c r="E53" s="26" t="n">
+      <c r="E53" s="27" t="n">
         <v>46170</v>
       </c>
-      <c r="F53" s="27" t="n">
+      <c r="F53" s="28" t="n">
         <v>2400509.91</v>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -4568,7 +5300,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I53" s="28" t="inlineStr">
+      <c r="I53" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4577,8 +5309,13 @@
       <c r="K53" s="15" t="n"/>
       <c r="L53" s="15" t="n"/>
       <c r="M53" s="15" t="n"/>
-      <c r="N53" s="29" t="n"/>
+      <c r="N53" s="30" t="n"/>
       <c r="O53" s="15" t="n"/>
+      <c r="P53" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
@@ -4589,18 +5326,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C54" s="26">
+      <c r="C54" s="27">
         <f>IF($E54="","",DATE(YEAR($E54),MONTH($E54),1))</f>
         <v/>
       </c>
-      <c r="D54" s="26">
+      <c r="D54" s="27">
         <f>IF($E54="","",EOMONTH($E54,0))</f>
         <v/>
       </c>
-      <c r="E54" s="26" t="n">
+      <c r="E54" s="27" t="n">
         <v>46171</v>
       </c>
-      <c r="F54" s="27" t="n">
+      <c r="F54" s="28" t="n">
         <v>3444449.93</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -4613,7 +5350,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I54" s="28" t="inlineStr">
+      <c r="I54" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4622,8 +5359,13 @@
       <c r="K54" s="15" t="n"/>
       <c r="L54" s="15" t="n"/>
       <c r="M54" s="15" t="n"/>
-      <c r="N54" s="29" t="n"/>
+      <c r="N54" s="30" t="n"/>
       <c r="O54" s="15" t="n"/>
+      <c r="P54" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
@@ -4634,18 +5376,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="27">
         <f>IF($E55="","",DATE(YEAR($E55),MONTH($E55),1))</f>
         <v/>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="27">
         <f>IF($E55="","",EOMONTH($E55,0))</f>
         <v/>
       </c>
-      <c r="E55" s="26" t="n">
+      <c r="E55" s="27" t="n">
         <v>46171</v>
       </c>
-      <c r="F55" s="27" t="n">
+      <c r="F55" s="28" t="n">
         <v>2450000</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -4658,13 +5400,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I55" s="28" t="inlineStr"/>
+      <c r="I55" s="29" t="inlineStr"/>
       <c r="J55" s="15" t="n"/>
       <c r="K55" s="15" t="n"/>
       <c r="L55" s="15" t="n"/>
       <c r="M55" s="15" t="n"/>
-      <c r="N55" s="29" t="n"/>
+      <c r="N55" s="30" t="n"/>
       <c r="O55" s="15" t="n"/>
+      <c r="P55" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
@@ -4675,18 +5422,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C56" s="26">
+      <c r="C56" s="27">
         <f>IF($E56="","",DATE(YEAR($E56),MONTH($E56),1))</f>
         <v/>
       </c>
-      <c r="D56" s="26">
+      <c r="D56" s="27">
         <f>IF($E56="","",EOMONTH($E56,0))</f>
         <v/>
       </c>
-      <c r="E56" s="26" t="n">
+      <c r="E56" s="27" t="n">
         <v>46176</v>
       </c>
-      <c r="F56" s="27" t="n">
+      <c r="F56" s="28" t="n">
         <v>5210470.59</v>
       </c>
       <c r="G56" s="10" t="inlineStr"/>
@@ -4695,7 +5442,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I56" s="28" t="inlineStr">
+      <c r="I56" s="29" t="inlineStr">
         <is>
           <t>ref_typo_corrected_from:ACH PYMTS - LCL BULK FNG; no_named_beneficiary</t>
         </is>
@@ -4704,8 +5451,13 @@
       <c r="K56" s="15" t="n"/>
       <c r="L56" s="15" t="n"/>
       <c r="M56" s="15" t="n"/>
-      <c r="N56" s="29" t="n"/>
+      <c r="N56" s="30" t="n"/>
       <c r="O56" s="15" t="n"/>
+      <c r="P56" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
@@ -4716,18 +5468,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C57" s="26">
+      <c r="C57" s="27">
         <f>IF($E57="","",DATE(YEAR($E57),MONTH($E57),1))</f>
         <v/>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="27">
         <f>IF($E57="","",EOMONTH($E57,0))</f>
         <v/>
       </c>
-      <c r="E57" s="26" t="n">
+      <c r="E57" s="27" t="n">
         <v>46177</v>
       </c>
-      <c r="F57" s="27" t="n">
+      <c r="F57" s="28" t="n">
         <v>4006482.03</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -4740,13 +5492,18 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I57" s="28" t="inlineStr"/>
+      <c r="I57" s="29" t="inlineStr"/>
       <c r="J57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
       <c r="L57" s="15" t="n"/>
       <c r="M57" s="15" t="n"/>
-      <c r="N57" s="29" t="n"/>
+      <c r="N57" s="30" t="n"/>
       <c r="O57" s="15" t="n"/>
+      <c r="P57" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
@@ -4757,18 +5514,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C58" s="26">
+      <c r="C58" s="27">
         <f>IF($E58="","",DATE(YEAR($E58),MONTH($E58),1))</f>
         <v/>
       </c>
-      <c r="D58" s="26">
+      <c r="D58" s="27">
         <f>IF($E58="","",EOMONTH($E58,0))</f>
         <v/>
       </c>
-      <c r="E58" s="26" t="n">
+      <c r="E58" s="27" t="n">
         <v>46184</v>
       </c>
-      <c r="F58" s="27" t="n">
+      <c r="F58" s="28" t="n">
         <v>6226088.99</v>
       </c>
       <c r="G58" s="10" t="inlineStr"/>
@@ -4777,7 +5534,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I58" s="28" t="inlineStr">
+      <c r="I58" s="29" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4786,8 +5543,13 @@
       <c r="K58" s="15" t="n"/>
       <c r="L58" s="15" t="n"/>
       <c r="M58" s="15" t="n"/>
-      <c r="N58" s="29" t="n"/>
+      <c r="N58" s="30" t="n"/>
       <c r="O58" s="15" t="n"/>
+      <c r="P58" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -4798,18 +5560,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C59" s="26">
+      <c r="C59" s="27">
         <f>IF($E59="","",DATE(YEAR($E59),MONTH($E59),1))</f>
         <v/>
       </c>
-      <c r="D59" s="26">
+      <c r="D59" s="27">
         <f>IF($E59="","",EOMONTH($E59,0))</f>
         <v/>
       </c>
-      <c r="E59" s="26" t="n">
+      <c r="E59" s="27" t="n">
         <v>46185</v>
       </c>
-      <c r="F59" s="27" t="n">
+      <c r="F59" s="28" t="n">
         <v>2292348.71</v>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -4822,7 +5584,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I59" s="28" t="inlineStr">
+      <c r="I59" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4831,8 +5593,13 @@
       <c r="K59" s="15" t="n"/>
       <c r="L59" s="15" t="n"/>
       <c r="M59" s="15" t="n"/>
-      <c r="N59" s="29" t="n"/>
+      <c r="N59" s="30" t="n"/>
       <c r="O59" s="15" t="n"/>
+      <c r="P59" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
@@ -4843,18 +5610,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C60" s="26">
+      <c r="C60" s="27">
         <f>IF($E60="","",DATE(YEAR($E60),MONTH($E60),1))</f>
         <v/>
       </c>
-      <c r="D60" s="26">
+      <c r="D60" s="27">
         <f>IF($E60="","",EOMONTH($E60,0))</f>
         <v/>
       </c>
-      <c r="E60" s="26" t="n">
+      <c r="E60" s="27" t="n">
         <v>46202</v>
       </c>
-      <c r="F60" s="27" t="n">
+      <c r="F60" s="28" t="n">
         <v>2782960.69</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -4867,7 +5634,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I60" s="28" t="inlineStr">
+      <c r="I60" s="29" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4876,16 +5643,21 @@
       <c r="K60" s="15" t="n"/>
       <c r="L60" s="15" t="n"/>
       <c r="M60" s="15" t="n"/>
-      <c r="N60" s="29" t="n"/>
+      <c r="N60" s="30" t="n"/>
       <c r="O60" s="15" t="n"/>
+      <c r="P60" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="E61" s="30" t="inlineStr">
+      <c r="E61" s="32" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F61" s="31">
+      <c r="F61" s="33">
         <f>SUM(F5:F60)</f>
         <v/>
       </c>
@@ -4896,11 +5668,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O60"/>
+  <autoFilter ref="A4:P60"/>
   <mergeCells count="1">
     <mergeCell ref="A3:I3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="P5:P60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -5064,7 +5842,7 @@
       <c r="C6" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>5, 6, 7, 8, 12, 13, 14, 15, 19, 20, 21, 22, ... (+15 more)</t>
         </is>
@@ -5084,7 +5862,7 @@
       <c r="C7" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 17, 18, ... (+14 more)</t>
         </is>
@@ -5104,7 +5882,7 @@
       <c r="C8" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>1, 3, 4, 9, 10, 11, 17, 18, 25, 26, 31, 35, ... (+6 more)</t>
         </is>
@@ -5124,7 +5902,7 @@
       <c r="C9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>12, 20, 27</t>
         </is>
@@ -5144,7 +5922,7 @@
       <c r="C10" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -5164,7 +5942,7 @@
       <c r="C11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -5183,7 +5961,7 @@
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5195,7 +5973,7 @@
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5207,7 +5985,7 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5219,7 +5997,7 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>*</t>
         </is>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,18 +87,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00BF8F00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C55A11"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -175,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -219,15 +207,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,7 +220,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -637,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D58"/>
+  <dimension ref="B2:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1000,277 +982,329 @@
     <row r="30">
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Invoice list amount column</t>
+          <t>ZP list amount column</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr"/>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+          <t>Caption of the amount column in the exported FBL1N payment list. Leave blank -- the macro tries the caption, then the SAP technical name, then works it out from what the column contains, which is language-independent. Only fill this in if the Log says it picked the wrong one.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Invoice list supplier column</t>
+          <t>ZP list vendor column</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr"/>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Caption of the supplier column in that same file.</t>
+          <t>Caption of the vendor-name column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Invoice list document column</t>
+          <t>ZP list document column</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr"/>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Caption of the invoice-number column in that same file.</t>
+          <t>Caption of the document-number column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>Invoice list amount column</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr"/>
       <c r="D33" s="12" t="inlineStr">
         <is>
+          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Invoice list supplier column</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr"/>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Caption of the supplier column in that same file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Invoice list document column</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr"/>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Caption of the invoice-number column in that same file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Extra popup titles to allow</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr"/>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr"/>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Samples in the sheet</t>
-        </is>
-      </c>
-      <c r="C37" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Included in the next run</t>
-        </is>
-      </c>
-      <c r="C38" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="C39" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>DONE -- invoice downloaded</t>
-        </is>
-      </c>
-      <c r="C40" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
+          <t>Samples in the sheet</t>
         </is>
       </c>
       <c r="C41" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_SCF -- Santander, needs the extra hop</t>
+          <t>Included in the next run</t>
         </is>
       </c>
       <c r="C42" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
+        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C43" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
+        <f>COUNTIF(Samples!P5:P1000,"No")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>PARTIAL -- traced, no invoice file</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C44" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
         </is>
       </c>
       <c r="C45" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>BLOCKED_SCF -- Santander, needs the extra hop</t>
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>PARTIAL -- traced, no invoice file</t>
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C49" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="14" t="inlineStr">
         <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C51" s="15">
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C52" s="15">
+        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Files downloaded</t>
+        </is>
+      </c>
+      <c r="C53" s="15">
+        <f>SUM(Samples!N5:N1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Samples with no named beneficiary in the request</t>
+        </is>
+      </c>
+      <c r="C54" s="15">
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C51" s="15">
+      <c r="C55" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="B55" s="14" t="inlineStr">
+    <row r="59" ht="28" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="B56" s="14" t="inlineStr">
+    <row r="60" ht="28" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C60" s="16" t="inlineStr">
         <is>
           <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="B57" s="14" t="inlineStr">
+    <row r="61" ht="28" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C61" s="16" t="inlineStr">
         <is>
           <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="B58" s="14" t="inlineStr">
+    <row r="62" ht="28" customHeight="1">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1278,10 +1312,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C59:D59"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1303,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F69"/>
+  <dimension ref="A2:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2253,7 +2287,7 @@
     <row r="44">
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Steps 8-9: FBL1N, the ZP payments of the batch (PREDICTED)</t>
+          <t>Steps 8-9: FBL1N, the ZP payments of the batch</t>
         </is>
       </c>
       <c r="C44" s="19" t="n"/>
@@ -2264,17 +2298,17 @@
     <row r="45">
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.CompanyCode</t>
+          <t>Fbl1n.AllItemsRadio</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Company code. PREDICTED from standard RFITEMAP -- no recording reaches FBL1N. Run modProbe.ProbeCurrentScreen on the FBL1N selection screen to check every Fbl1n.* row at once</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>'All items' radio</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E45" s="22" t="inlineStr">
@@ -2284,24 +2318,24 @@
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtDD_BUKRS-LOW</t>
+          <t>wnd[0]/usr/radX_AISEL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.AllItemsRadio</t>
+          <t>Fbl1n.CompanyCode</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>'All items' radio. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Company code. KD_BUKRS, not the DD_BUKRS that was predicted</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E46" s="22" t="inlineStr">
@@ -2311,7 +2345,7 @@
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/radX_AISEL</t>
+          <t>wnd[0]/usr/ctxtKD_BUKRS-LOW</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2357,12 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Posting date, low. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Posting date, low</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
@@ -2350,12 +2384,12 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Posting date, high. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Posting date, high</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
@@ -2372,17 +2406,17 @@
     <row r="49">
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.DocNumberFrom</t>
+          <t>Fbl1n.DynamicSelections</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Document number, single value. NOTE: on standard FBL1N the document number lives in dynamic selections, not the main screen -- if the probe cannot find this, leave the whole Fbl1n block blank and use the fallback described in the README. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Opens the dynamic-selections block. The document number is NOT on the main selection screen -- it lives in dynamic selections, so this has to be pressed before the field below exists</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
@@ -2392,11 +2426,11 @@
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtSO_BELNR-LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
+          <t>wnd[0]/tbar[1]/btn[16]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
       <c r="B50" s="20" t="inlineStr">
         <is>
           <t>Fbl1n.DocNumberMultiSelect</t>
@@ -2404,12 +2438,12 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>The arrow button beside it that opens multiple selection. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Multiple-selection arrow for document number, inside the dynamic-selections subscreen</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E50" s="22" t="inlineStr">
@@ -2419,7 +2453,7 @@
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/btn%_SO_BELNR_%_APP_%-VALU_PUSH</t>
+          <t>wnd[0]/usr/ssub%_SUBSCREEN_%_SUB%_CONTAINER:SAPLSSEL:2001/ssubSUBSCREEN_CONTAINER2:SAPLSSEL:2000/ssubSUBSCREEN_CONTAINER:SAPLSSEL:1106/btn%_%%DYN011_%_APP_%-VALU_PUSH</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2465,12 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>'Upload from clipboard' on the multiple-selection dialog. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>'Upload from clipboard' on the multiple-selection dialog</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E51" s="22" t="inlineStr">
@@ -2458,12 +2492,12 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Copy/Execute on that dialog. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D52" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Copy on that dialog</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E52" s="22" t="inlineStr">
@@ -2485,12 +2519,12 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Execute. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Execute</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
@@ -2507,17 +2541,17 @@
     <row r="54">
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.ResultGrid</t>
+          <t>Fbl1n.ResultAnchor</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>ALV grid of vendor line items. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Confirms the FBL1N result came up. NOTE: FBL1N renders as a CLASSIC LIST here (lbl[x,y]), not an ALV grid, so there is no grid to read -- the list is exported and read back instead. VERIFY</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
@@ -2527,51 +2561,35 @@
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/cntlCONTAINER/shellcont/shell</t>
+          <t>wnd[0]/usr/lbl[164,8]</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>Fbl1n.Col.Amount</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>DC amount column. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
-        </is>
-      </c>
-      <c r="E55" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t>DMSHB</t>
-        </is>
-      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>Step 10: the largest payment's invoices, and the PDF</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.Col.DocNumber</t>
+          <t>Payment.UsageMenu</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Document number column. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Environment &gt; Payment usage from inside the payment document. menu[4] here, not the menu[5] used from the clearing document -- menu indices differ per screen. VERIFY</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E56" s="22" t="inlineStr">
@@ -2581,24 +2599,24 @@
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>BELNR</t>
+          <t>wnd[0]/mbar/menu[4]/menu[3]</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.Col.Vendor</t>
+          <t>Invoice.GosToolbox</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Vendor account column. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D57" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Services-for-object toolbox. shellcont[2], not the plain shellcont that was predicted</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E57" s="22" t="inlineStr">
@@ -2608,24 +2626,24 @@
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>LIFNR</t>
+          <t>wnd[0]/titl/shellcont[2]/shell</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.Col.VendorName</t>
+          <t>Invoice.AttachListGrid</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Vendor name column. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D58" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Attachment-list grid. CONTAINER_0100</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E58" s="22" t="inlineStr">
@@ -2635,35 +2653,51 @@
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>NAME1</t>
+          <t>wnd[1]/usr/cntlCONTAINER_0100/shellcont/shell</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="18" t="inlineStr">
-        <is>
-          <t>Step 10: the invoice PDF (NOT RECORDED)</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="n"/>
-      <c r="D59" s="19" t="n"/>
-      <c r="E59" s="19" t="n"/>
-      <c r="F59" s="19" t="n"/>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.AttachListColumn</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Column used to select the attachment row</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>BITM_DESCR</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Invoice.GosToolbox</t>
+          <t>Invoice.ExportMenuItem</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Services-for-object toolbox on the title bar. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Context-menu entry that saves the attachment. A CONTEXT MENU item, not the toolbar button that was predicted</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E60" s="22" t="inlineStr">
@@ -2673,24 +2707,24 @@
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/titl/shellcont/shell</t>
+          <t>%ATTA_EXPORT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListGrid</t>
+          <t>Invoice.SaveWindow</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Attachment-list grid. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D61" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Window the PDF save dialog opens in. wnd[2], because the attachment list is already wnd[1]</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E61" s="22" t="inlineStr">
@@ -2700,24 +2734,24 @@
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/cntlCONTAINER/shellcont/shell</t>
+          <t>wnd[2]</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Invoice.SaveButton</t>
+          <t>Invoice.CloseAttachList</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Save/export button on the attachment list. PREDICTED</t>
-        </is>
-      </c>
-      <c r="D62" s="25" t="inlineStr">
-        <is>
-          <t>PREDICTED</t>
+          <t>Closes the attachment list afterwards</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E62" s="22" t="inlineStr">
@@ -2727,102 +2761,44 @@
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="18" t="inlineStr">
-        <is>
-          <t>Step 10, Santander SCF only: the extra hop (NOT RECORDED)</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n"/>
-      <c r="F63" s="19" t="n"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="20" t="inlineStr">
-        <is>
-          <t>Scf.OpenInvoices</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>How you get from the SCF payment to the invoices it settled. A menu entry, a button, or a field to focus and F2 -- the macro reads the control type and does the right thing. BLOCKED: no recording covers it</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="E64" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="n"/>
-    </row>
-    <row r="65">
-      <c r="B65" s="20" t="inlineStr">
-        <is>
-          <t>Scf.InvoiceListMenu</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>Menu path that lists those invoices. BLOCKED</t>
-        </is>
-      </c>
-      <c r="D65" s="26" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="E65" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="n"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="B67" s="16" t="inlineStr">
+          <t>wnd[1]/tbar[0]/btn[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="B68" s="16" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="B69" s="16" t="inlineStr">
+    <row r="66" ht="30" customHeight="1">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>The recording entered dates as 8 digits with no separators (01092025). The Control sheet's 'SAP date format' is set to DDMMYYYY to match. Do not change it to DMY unless you have checked that this system accepts 01.09.2025 as well.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B64:F64"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B59:F59"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B66:F66"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
@@ -2964,18 +2940,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="25">
         <f>IF($E5="","",DATE(YEAR($E5),MONTH($E5),1))</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="25">
         <f>IF($E5="","",EOMONTH($E5,0))</f>
         <v/>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="25" t="n">
         <v>45903</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="26" t="n">
         <v>8072447.42</v>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
@@ -2984,7 +2960,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -2993,9 +2969,9 @@
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
-      <c r="N5" s="30" t="n"/>
+      <c r="N5" s="28" t="n"/>
       <c r="O5" s="15" t="n"/>
-      <c r="P5" s="31" t="inlineStr">
+      <c r="P5" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3010,18 +2986,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="25">
         <f>IF($E6="","",DATE(YEAR($E6),MONTH($E6),1))</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="25">
         <f>IF($E6="","",EOMONTH($E6,0))</f>
         <v/>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="25" t="n">
         <v>45912</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="26" t="n">
         <v>2161788.23</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -3034,7 +3010,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -3043,9 +3019,9 @@
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
-      <c r="N6" s="30" t="n"/>
+      <c r="N6" s="28" t="n"/>
       <c r="O6" s="15" t="n"/>
-      <c r="P6" s="31" t="inlineStr">
+      <c r="P6" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3060,18 +3036,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="25">
         <f>IF($E7="","",DATE(YEAR($E7),MONTH($E7),1))</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="25">
         <f>IF($E7="","",EOMONTH($E7,0))</f>
         <v/>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="25" t="n">
         <v>45915</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="26" t="n">
         <v>5988033.6</v>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -3080,7 +3056,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3089,9 +3065,9 @@
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15" t="n"/>
-      <c r="N7" s="30" t="n"/>
+      <c r="N7" s="28" t="n"/>
       <c r="O7" s="15" t="n"/>
-      <c r="P7" s="31" t="inlineStr">
+      <c r="P7" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3106,18 +3082,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="25">
         <f>IF($E8="","",DATE(YEAR($E8),MONTH($E8),1))</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="25">
         <f>IF($E8="","",EOMONTH($E8,0))</f>
         <v/>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="25" t="n">
         <v>45922</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="26" t="n">
         <v>2942842.52</v>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
@@ -3126,7 +3102,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3135,9 +3111,9 @@
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
-      <c r="N8" s="30" t="n"/>
+      <c r="N8" s="28" t="n"/>
       <c r="O8" s="15" t="n"/>
-      <c r="P8" s="31" t="inlineStr">
+      <c r="P8" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3152,18 +3128,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="25">
         <f>IF($E9="","",DATE(YEAR($E9),MONTH($E9),1))</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="25">
         <f>IF($E9="","",EOMONTH($E9,0))</f>
         <v/>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="25" t="n">
         <v>45924</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="26" t="n">
         <v>8617262.93</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -3176,7 +3152,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3185,9 +3161,9 @@
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
-      <c r="N9" s="30" t="n"/>
+      <c r="N9" s="28" t="n"/>
       <c r="O9" s="15" t="n"/>
-      <c r="P9" s="31" t="inlineStr">
+      <c r="P9" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3202,18 +3178,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="25">
         <f>IF($E10="","",DATE(YEAR($E10),MONTH($E10),1))</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="25">
         <f>IF($E10="","",EOMONTH($E10,0))</f>
         <v/>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="25" t="n">
         <v>45925</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="26" t="n">
         <v>2968313.21</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -3226,7 +3202,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3235,9 +3211,9 @@
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
-      <c r="N10" s="30" t="n"/>
+      <c r="N10" s="28" t="n"/>
       <c r="O10" s="15" t="n"/>
-      <c r="P10" s="31" t="inlineStr">
+      <c r="P10" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3252,18 +3228,18 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="25">
         <f>IF($E11="","",DATE(YEAR($E11),MONTH($E11),1))</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="25">
         <f>IF($E11="","",EOMONTH($E11,0))</f>
         <v/>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="25" t="n">
         <v>45930</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -3276,7 +3252,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3285,9 +3261,9 @@
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="15" t="n"/>
       <c r="M11" s="15" t="n"/>
-      <c r="N11" s="30" t="n"/>
+      <c r="N11" s="28" t="n"/>
       <c r="O11" s="15" t="n"/>
-      <c r="P11" s="31" t="inlineStr">
+      <c r="P11" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3302,18 +3278,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="25">
         <f>IF($E12="","",DATE(YEAR($E12),MONTH($E12),1))</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="25">
         <f>IF($E12="","",EOMONTH($E12,0))</f>
         <v/>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="25" t="n">
         <v>45931</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="26" t="n">
         <v>4483676.08</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -3326,7 +3302,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3335,9 +3311,9 @@
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
-      <c r="N12" s="30" t="n"/>
+      <c r="N12" s="28" t="n"/>
       <c r="O12" s="15" t="n"/>
-      <c r="P12" s="31" t="inlineStr">
+      <c r="P12" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3352,18 +3328,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="25">
         <f>IF($E13="","",DATE(YEAR($E13),MONTH($E13),1))</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="25">
         <f>IF($E13="","",EOMONTH($E13,0))</f>
         <v/>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="25" t="n">
         <v>45933</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="26" t="n">
         <v>3412038.97</v>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -3372,7 +3348,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3381,9 +3357,9 @@
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
-      <c r="N13" s="30" t="n"/>
+      <c r="N13" s="28" t="n"/>
       <c r="O13" s="15" t="n"/>
-      <c r="P13" s="31" t="inlineStr">
+      <c r="P13" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3398,18 +3374,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="25">
         <f>IF($E14="","",DATE(YEAR($E14),MONTH($E14),1))</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="25">
         <f>IF($E14="","",EOMONTH($E14,0))</f>
         <v/>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="25" t="n">
         <v>45943</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="26" t="n">
         <v>3385329.45</v>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
@@ -3418,7 +3394,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3427,9 +3403,9 @@
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
-      <c r="N14" s="30" t="n"/>
+      <c r="N14" s="28" t="n"/>
       <c r="O14" s="15" t="n"/>
-      <c r="P14" s="31" t="inlineStr">
+      <c r="P14" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3444,18 +3420,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="25">
         <f>IF($E15="","",DATE(YEAR($E15),MONTH($E15),1))</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="25">
         <f>IF($E15="","",EOMONTH($E15,0))</f>
         <v/>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="25" t="n">
         <v>45950</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="26" t="n">
         <v>4898587.92</v>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
@@ -3464,7 +3440,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3473,9 +3449,9 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="15" t="n"/>
-      <c r="N15" s="30" t="n"/>
+      <c r="N15" s="28" t="n"/>
       <c r="O15" s="15" t="n"/>
-      <c r="P15" s="31" t="inlineStr">
+      <c r="P15" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3490,18 +3466,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="25">
         <f>IF($E16="","",DATE(YEAR($E16),MONTH($E16),1))</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="25">
         <f>IF($E16="","",EOMONTH($E16,0))</f>
         <v/>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="25" t="n">
         <v>45954</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="26" t="n">
         <v>3480924.53</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -3514,7 +3490,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I16" s="29" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>date_stored_as_text; party_whitespace_cleaned</t>
         </is>
@@ -3523,9 +3499,9 @@
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
-      <c r="N16" s="30" t="n"/>
+      <c r="N16" s="28" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="31" t="inlineStr">
+      <c r="P16" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3540,18 +3516,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="25">
         <f>IF($E17="","",DATE(YEAR($E17),MONTH($E17),1))</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="25">
         <f>IF($E17="","",EOMONTH($E17,0))</f>
         <v/>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="25" t="n">
         <v>45957</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="26" t="n">
         <v>2614260.03</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -3564,7 +3540,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I17" s="29" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3573,9 +3549,9 @@
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
-      <c r="N17" s="30" t="n"/>
+      <c r="N17" s="28" t="n"/>
       <c r="O17" s="15" t="n"/>
-      <c r="P17" s="31" t="inlineStr">
+      <c r="P17" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3590,18 +3566,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="25">
         <f>IF($E18="","",DATE(YEAR($E18),MONTH($E18),1))</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="25">
         <f>IF($E18="","",EOMONTH($E18,0))</f>
         <v/>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="25" t="n">
         <v>45961</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -3614,7 +3590,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I18" s="29" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3623,9 +3599,9 @@
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
-      <c r="N18" s="30" t="n"/>
+      <c r="N18" s="28" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="31" t="inlineStr">
+      <c r="P18" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3640,18 +3616,18 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="25">
         <f>IF($E19="","",DATE(YEAR($E19),MONTH($E19),1))</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="25">
         <f>IF($E19="","",EOMONTH($E19,0))</f>
         <v/>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="25" t="n">
         <v>45961</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="26" t="n">
         <v>3317511.83</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -3664,7 +3640,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I19" s="29" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3673,9 +3649,9 @@
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
-      <c r="N19" s="30" t="n"/>
+      <c r="N19" s="28" t="n"/>
       <c r="O19" s="15" t="n"/>
-      <c r="P19" s="31" t="inlineStr">
+      <c r="P19" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3690,18 +3666,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="25">
         <f>IF($E20="","",DATE(YEAR($E20),MONTH($E20),1))</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="25">
         <f>IF($E20="","",EOMONTH($E20,0))</f>
         <v/>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="25" t="n">
         <v>45964</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="26" t="n">
         <v>3724798.28</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -3714,14 +3690,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I20" s="29" t="inlineStr"/>
+      <c r="I20" s="27" t="inlineStr"/>
       <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
-      <c r="N20" s="30" t="n"/>
+      <c r="N20" s="28" t="n"/>
       <c r="O20" s="15" t="n"/>
-      <c r="P20" s="31" t="inlineStr">
+      <c r="P20" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3736,18 +3712,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="25">
         <f>IF($E21="","",DATE(YEAR($E21),MONTH($E21),1))</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="25">
         <f>IF($E21="","",EOMONTH($E21,0))</f>
         <v/>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="25" t="n">
         <v>45966</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="26" t="n">
         <v>5044035.13</v>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
@@ -3756,7 +3732,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3765,9 +3741,9 @@
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15" t="n"/>
-      <c r="N21" s="30" t="n"/>
+      <c r="N21" s="28" t="n"/>
       <c r="O21" s="15" t="n"/>
-      <c r="P21" s="31" t="inlineStr">
+      <c r="P21" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3782,18 +3758,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="25">
         <f>IF($E22="","",DATE(YEAR($E22),MONTH($E22),1))</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="25">
         <f>IF($E22="","",EOMONTH($E22,0))</f>
         <v/>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="25" t="n">
         <v>45978</v>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="26" t="n">
         <v>5245536.51</v>
       </c>
       <c r="G22" s="10" t="inlineStr"/>
@@ -3802,7 +3778,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I22" s="29" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -3811,9 +3787,9 @@
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
-      <c r="N22" s="30" t="n"/>
+      <c r="N22" s="28" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="31" t="inlineStr">
+      <c r="P22" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3828,18 +3804,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="25">
         <f>IF($E23="","",DATE(YEAR($E23),MONTH($E23),1))</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="25">
         <f>IF($E23="","",EOMONTH($E23,0))</f>
         <v/>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="25" t="n">
         <v>45989</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="26" t="n">
         <v>4173936.71</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -3852,7 +3828,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I23" s="29" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3861,9 +3837,9 @@
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
-      <c r="N23" s="30" t="n"/>
+      <c r="N23" s="28" t="n"/>
       <c r="O23" s="15" t="n"/>
-      <c r="P23" s="31" t="inlineStr">
+      <c r="P23" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3878,18 +3854,18 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="25">
         <f>IF($E24="","",DATE(YEAR($E24),MONTH($E24),1))</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="25">
         <f>IF($E24="","",EOMONTH($E24,0))</f>
         <v/>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="25" t="n">
         <v>45989</v>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="F24" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -3902,7 +3878,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I24" s="29" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -3911,9 +3887,9 @@
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
-      <c r="N24" s="30" t="n"/>
+      <c r="N24" s="28" t="n"/>
       <c r="O24" s="15" t="n"/>
-      <c r="P24" s="31" t="inlineStr">
+      <c r="P24" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3928,18 +3904,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="25">
         <f>IF($E25="","",DATE(YEAR($E25),MONTH($E25),1))</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="25">
         <f>IF($E25="","",EOMONTH($E25,0))</f>
         <v/>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="25" t="n">
         <v>46020</v>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="26" t="n">
         <v>2828677.68</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -3952,7 +3928,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I25" s="29" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -3961,9 +3937,9 @@
       <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n"/>
       <c r="M25" s="15" t="n"/>
-      <c r="N25" s="30" t="n"/>
+      <c r="N25" s="28" t="n"/>
       <c r="O25" s="15" t="n"/>
-      <c r="P25" s="31" t="inlineStr">
+      <c r="P25" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3978,18 +3954,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="25">
         <f>IF($E26="","",DATE(YEAR($E26),MONTH($E26),1))</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="25">
         <f>IF($E26="","",EOMONTH($E26,0))</f>
         <v/>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="25" t="n">
         <v>46022</v>
       </c>
-      <c r="F26" s="28" t="n">
+      <c r="F26" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -4002,7 +3978,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I26" s="29" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -4011,9 +3987,9 @@
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
-      <c r="N26" s="30" t="n"/>
+      <c r="N26" s="28" t="n"/>
       <c r="O26" s="15" t="n"/>
-      <c r="P26" s="31" t="inlineStr">
+      <c r="P26" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4028,18 +4004,18 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="25">
         <f>IF($E27="","",DATE(YEAR($E27),MONTH($E27),1))</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="25">
         <f>IF($E27="","",EOMONTH($E27,0))</f>
         <v/>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="25" t="n">
         <v>46022</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F27" s="26" t="n">
         <v>2233241.99</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -4052,7 +4028,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I27" s="29" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4061,9 +4037,9 @@
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15" t="n"/>
-      <c r="N27" s="30" t="n"/>
+      <c r="N27" s="28" t="n"/>
       <c r="O27" s="15" t="n"/>
-      <c r="P27" s="31" t="inlineStr">
+      <c r="P27" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4078,18 +4054,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="25">
         <f>IF($E28="","",DATE(YEAR($E28),MONTH($E28),1))</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="25">
         <f>IF($E28="","",EOMONTH($E28,0))</f>
         <v/>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="25" t="n">
         <v>46024</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="26" t="n">
         <v>3489077.98</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -4102,7 +4078,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I28" s="29" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -4111,9 +4087,9 @@
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
-      <c r="N28" s="30" t="n"/>
+      <c r="N28" s="28" t="n"/>
       <c r="O28" s="15" t="n"/>
-      <c r="P28" s="31" t="inlineStr">
+      <c r="P28" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4128,18 +4104,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="25">
         <f>IF($E29="","",DATE(YEAR($E29),MONTH($E29),1))</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="25">
         <f>IF($E29="","",EOMONTH($E29,0))</f>
         <v/>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="25" t="n">
         <v>46028</v>
       </c>
-      <c r="F29" s="28" t="n">
+      <c r="F29" s="26" t="n">
         <v>4395299.21</v>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -4148,7 +4124,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I29" s="29" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -4157,9 +4133,9 @@
       <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
-      <c r="N29" s="30" t="n"/>
+      <c r="N29" s="28" t="n"/>
       <c r="O29" s="15" t="n"/>
-      <c r="P29" s="31" t="inlineStr">
+      <c r="P29" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4174,18 +4150,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="25">
         <f>IF($E30="","",DATE(YEAR($E30),MONTH($E30),1))</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="25">
         <f>IF($E30="","",EOMONTH($E30,0))</f>
         <v/>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="25" t="n">
         <v>46031</v>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="F30" s="26" t="n">
         <v>8800991.4</v>
       </c>
       <c r="G30" s="10" t="inlineStr"/>
@@ -4194,7 +4170,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I30" s="29" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -4203,9 +4179,9 @@
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
       <c r="M30" s="15" t="n"/>
-      <c r="N30" s="30" t="n"/>
+      <c r="N30" s="28" t="n"/>
       <c r="O30" s="15" t="n"/>
-      <c r="P30" s="31" t="inlineStr">
+      <c r="P30" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4220,18 +4196,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="25">
         <f>IF($E31="","",DATE(YEAR($E31),MONTH($E31),1))</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="25">
         <f>IF($E31="","",EOMONTH($E31,0))</f>
         <v/>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E31" s="25" t="n">
         <v>46038</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F31" s="26" t="n">
         <v>6502110.67</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -4244,7 +4220,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I31" s="29" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>date_stored_as_text; ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -4253,9 +4229,9 @@
       <c r="K31" s="15" t="n"/>
       <c r="L31" s="15" t="n"/>
       <c r="M31" s="15" t="n"/>
-      <c r="N31" s="30" t="n"/>
+      <c r="N31" s="28" t="n"/>
       <c r="O31" s="15" t="n"/>
-      <c r="P31" s="31" t="inlineStr">
+      <c r="P31" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4270,18 +4246,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="25">
         <f>IF($E32="","",DATE(YEAR($E32),MONTH($E32),1))</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="25">
         <f>IF($E32="","",EOMONTH($E32,0))</f>
         <v/>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="25" t="n">
         <v>46051</v>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="F32" s="26" t="n">
         <v>3463573.21</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -4294,7 +4270,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I32" s="29" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -4303,9 +4279,9 @@
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
-      <c r="N32" s="30" t="n"/>
+      <c r="N32" s="28" t="n"/>
       <c r="O32" s="15" t="n"/>
-      <c r="P32" s="31" t="inlineStr">
+      <c r="P32" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4320,18 +4296,18 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="25">
         <f>IF($E33="","",DATE(YEAR($E33),MONTH($E33),1))</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="25">
         <f>IF($E33="","",EOMONTH($E33,0))</f>
         <v/>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="25" t="n">
         <v>46052</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -4344,7 +4320,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I33" s="29" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -4353,9 +4329,9 @@
       <c r="K33" s="15" t="n"/>
       <c r="L33" s="15" t="n"/>
       <c r="M33" s="15" t="n"/>
-      <c r="N33" s="30" t="n"/>
+      <c r="N33" s="28" t="n"/>
       <c r="O33" s="15" t="n"/>
-      <c r="P33" s="31" t="inlineStr">
+      <c r="P33" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4370,18 +4346,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="25">
         <f>IF($E34="","",DATE(YEAR($E34),MONTH($E34),1))</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="25">
         <f>IF($E34="","",EOMONTH($E34,0))</f>
         <v/>
       </c>
-      <c r="E34" s="27" t="n">
+      <c r="E34" s="25" t="n">
         <v>46055</v>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="F34" s="26" t="n">
         <v>3679179.76</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -4394,7 +4370,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I34" s="29" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned</t>
         </is>
@@ -4403,9 +4379,9 @@
       <c r="K34" s="15" t="n"/>
       <c r="L34" s="15" t="n"/>
       <c r="M34" s="15" t="n"/>
-      <c r="N34" s="30" t="n"/>
+      <c r="N34" s="28" t="n"/>
       <c r="O34" s="15" t="n"/>
-      <c r="P34" s="31" t="inlineStr">
+      <c r="P34" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4420,18 +4396,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="25">
         <f>IF($E35="","",DATE(YEAR($E35),MONTH($E35),1))</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="25">
         <f>IF($E35="","",EOMONTH($E35,0))</f>
         <v/>
       </c>
-      <c r="E35" s="27" t="n">
+      <c r="E35" s="25" t="n">
         <v>46057</v>
       </c>
-      <c r="F35" s="28" t="n">
+      <c r="F35" s="26" t="n">
         <v>3674499.52</v>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
@@ -4440,7 +4416,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I35" s="29" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -4449,9 +4425,9 @@
       <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="15" t="n"/>
-      <c r="N35" s="30" t="n"/>
+      <c r="N35" s="28" t="n"/>
       <c r="O35" s="15" t="n"/>
-      <c r="P35" s="31" t="inlineStr">
+      <c r="P35" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4466,18 +4442,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="25">
         <f>IF($E36="","",DATE(YEAR($E36),MONTH($E36),1))</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="25">
         <f>IF($E36="","",EOMONTH($E36,0))</f>
         <v/>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="25" t="n">
         <v>46080</v>
       </c>
-      <c r="F36" s="28" t="n">
+      <c r="F36" s="26" t="n">
         <v>6558159.12</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -4490,7 +4466,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I36" s="29" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4499,9 +4475,9 @@
       <c r="K36" s="15" t="n"/>
       <c r="L36" s="15" t="n"/>
       <c r="M36" s="15" t="n"/>
-      <c r="N36" s="30" t="n"/>
+      <c r="N36" s="28" t="n"/>
       <c r="O36" s="15" t="n"/>
-      <c r="P36" s="31" t="inlineStr">
+      <c r="P36" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4516,18 +4492,18 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="25">
         <f>IF($E37="","",DATE(YEAR($E37),MONTH($E37),1))</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="25">
         <f>IF($E37="","",EOMONTH($E37,0))</f>
         <v/>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="25" t="n">
         <v>46080</v>
       </c>
-      <c r="F37" s="28" t="n">
+      <c r="F37" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -4540,7 +4516,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I37" s="29" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -4549,9 +4525,9 @@
       <c r="K37" s="15" t="n"/>
       <c r="L37" s="15" t="n"/>
       <c r="M37" s="15" t="n"/>
-      <c r="N37" s="30" t="n"/>
+      <c r="N37" s="28" t="n"/>
       <c r="O37" s="15" t="n"/>
-      <c r="P37" s="31" t="inlineStr">
+      <c r="P37" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4566,18 +4542,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="25">
         <f>IF($E38="","",DATE(YEAR($E38),MONTH($E38),1))</f>
         <v/>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="25">
         <f>IF($E38="","",EOMONTH($E38,0))</f>
         <v/>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E38" s="25" t="n">
         <v>46083</v>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F38" s="26" t="n">
         <v>3562528.89</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -4590,7 +4566,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I38" s="29" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; party_whitespace_cleaned</t>
         </is>
@@ -4599,9 +4575,9 @@
       <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n"/>
       <c r="M38" s="15" t="n"/>
-      <c r="N38" s="30" t="n"/>
+      <c r="N38" s="28" t="n"/>
       <c r="O38" s="15" t="n"/>
-      <c r="P38" s="31" t="inlineStr">
+      <c r="P38" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4616,18 +4592,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="25">
         <f>IF($E39="","",DATE(YEAR($E39),MONTH($E39),1))</f>
         <v/>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="25">
         <f>IF($E39="","",EOMONTH($E39,0))</f>
         <v/>
       </c>
-      <c r="E39" s="27" t="n">
+      <c r="E39" s="25" t="n">
         <v>46085</v>
       </c>
-      <c r="F39" s="28" t="n">
+      <c r="F39" s="26" t="n">
         <v>8557737.25</v>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
@@ -4636,7 +4612,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I39" s="29" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4645,9 +4621,9 @@
       <c r="K39" s="15" t="n"/>
       <c r="L39" s="15" t="n"/>
       <c r="M39" s="15" t="n"/>
-      <c r="N39" s="30" t="n"/>
+      <c r="N39" s="28" t="n"/>
       <c r="O39" s="15" t="n"/>
-      <c r="P39" s="31" t="inlineStr">
+      <c r="P39" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4662,18 +4638,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="25">
         <f>IF($E40="","",DATE(YEAR($E40),MONTH($E40),1))</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="25">
         <f>IF($E40="","",EOMONTH($E40,0))</f>
         <v/>
       </c>
-      <c r="E40" s="27" t="n">
+      <c r="E40" s="25" t="n">
         <v>46093</v>
       </c>
-      <c r="F40" s="28" t="n">
+      <c r="F40" s="26" t="n">
         <v>2301959.84</v>
       </c>
       <c r="G40" s="10" t="inlineStr"/>
@@ -4682,7 +4658,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I40" s="29" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4691,9 +4667,9 @@
       <c r="K40" s="15" t="n"/>
       <c r="L40" s="15" t="n"/>
       <c r="M40" s="15" t="n"/>
-      <c r="N40" s="30" t="n"/>
+      <c r="N40" s="28" t="n"/>
       <c r="O40" s="15" t="n"/>
-      <c r="P40" s="31" t="inlineStr">
+      <c r="P40" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4708,18 +4684,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="25">
         <f>IF($E41="","",DATE(YEAR($E41),MONTH($E41),1))</f>
         <v/>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="25">
         <f>IF($E41="","",EOMONTH($E41,0))</f>
         <v/>
       </c>
-      <c r="E41" s="27" t="n">
+      <c r="E41" s="25" t="n">
         <v>46108</v>
       </c>
-      <c r="F41" s="28" t="n">
+      <c r="F41" s="26" t="n">
         <v>5989486.48</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -4732,7 +4708,7 @@
           <t>DS Smith Paper Limited</t>
         </is>
       </c>
-      <c r="I41" s="29" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>ref_holds_a_party_name_not_a_transaction_description; party_whitespace_cleaned</t>
         </is>
@@ -4741,9 +4717,9 @@
       <c r="K41" s="15" t="n"/>
       <c r="L41" s="15" t="n"/>
       <c r="M41" s="15" t="n"/>
-      <c r="N41" s="30" t="n"/>
+      <c r="N41" s="28" t="n"/>
       <c r="O41" s="15" t="n"/>
-      <c r="P41" s="31" t="inlineStr">
+      <c r="P41" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4758,18 +4734,18 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="25">
         <f>IF($E42="","",DATE(YEAR($E42),MONTH($E42),1))</f>
         <v/>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="25">
         <f>IF($E42="","",EOMONTH($E42,0))</f>
         <v/>
       </c>
-      <c r="E42" s="27" t="n">
+      <c r="E42" s="25" t="n">
         <v>46112</v>
       </c>
-      <c r="F42" s="28" t="n">
+      <c r="F42" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -4782,14 +4758,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I42" s="29" t="inlineStr"/>
+      <c r="I42" s="27" t="inlineStr"/>
       <c r="J42" s="15" t="n"/>
       <c r="K42" s="15" t="n"/>
       <c r="L42" s="15" t="n"/>
       <c r="M42" s="15" t="n"/>
-      <c r="N42" s="30" t="n"/>
+      <c r="N42" s="28" t="n"/>
       <c r="O42" s="15" t="n"/>
-      <c r="P42" s="31" t="inlineStr">
+      <c r="P42" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4804,18 +4780,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="25">
         <f>IF($E43="","",DATE(YEAR($E43),MONTH($E43),1))</f>
         <v/>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="25">
         <f>IF($E43="","",EOMONTH($E43,0))</f>
         <v/>
       </c>
-      <c r="E43" s="27" t="n">
+      <c r="E43" s="25" t="n">
         <v>46113</v>
       </c>
-      <c r="F43" s="28" t="n">
+      <c r="F43" s="26" t="n">
         <v>3316944.84</v>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -4828,14 +4804,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I43" s="29" t="inlineStr"/>
+      <c r="I43" s="27" t="inlineStr"/>
       <c r="J43" s="15" t="n"/>
       <c r="K43" s="15" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15" t="n"/>
-      <c r="N43" s="30" t="n"/>
+      <c r="N43" s="28" t="n"/>
       <c r="O43" s="15" t="n"/>
-      <c r="P43" s="31" t="inlineStr">
+      <c r="P43" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4850,18 +4826,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="25">
         <f>IF($E44="","",DATE(YEAR($E44),MONTH($E44),1))</f>
         <v/>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="25">
         <f>IF($E44="","",EOMONTH($E44,0))</f>
         <v/>
       </c>
-      <c r="E44" s="27" t="n">
+      <c r="E44" s="25" t="n">
         <v>46128</v>
       </c>
-      <c r="F44" s="28" t="n">
+      <c r="F44" s="26" t="n">
         <v>2611670.69</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -4874,14 +4850,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I44" s="29" t="inlineStr"/>
+      <c r="I44" s="27" t="inlineStr"/>
       <c r="J44" s="15" t="n"/>
       <c r="K44" s="15" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15" t="n"/>
-      <c r="N44" s="30" t="n"/>
+      <c r="N44" s="28" t="n"/>
       <c r="O44" s="15" t="n"/>
-      <c r="P44" s="31" t="inlineStr">
+      <c r="P44" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4896,18 +4872,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="25">
         <f>IF($E45="","",DATE(YEAR($E45),MONTH($E45),1))</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="25">
         <f>IF($E45="","",EOMONTH($E45,0))</f>
         <v/>
       </c>
-      <c r="E45" s="27" t="n">
+      <c r="E45" s="25" t="n">
         <v>46129</v>
       </c>
-      <c r="F45" s="28" t="n">
+      <c r="F45" s="26" t="n">
         <v>4996002.96</v>
       </c>
       <c r="G45" s="10" t="inlineStr"/>
@@ -4916,7 +4892,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I45" s="29" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -4925,9 +4901,9 @@
       <c r="K45" s="15" t="n"/>
       <c r="L45" s="15" t="n"/>
       <c r="M45" s="15" t="n"/>
-      <c r="N45" s="30" t="n"/>
+      <c r="N45" s="28" t="n"/>
       <c r="O45" s="15" t="n"/>
-      <c r="P45" s="31" t="inlineStr">
+      <c r="P45" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4942,18 +4918,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="25">
         <f>IF($E46="","",DATE(YEAR($E46),MONTH($E46),1))</f>
         <v/>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="25">
         <f>IF($E46="","",EOMONTH($E46,0))</f>
         <v/>
       </c>
-      <c r="E46" s="27" t="n">
+      <c r="E46" s="25" t="n">
         <v>46135</v>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="F46" s="26" t="n">
         <v>2334786.77</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -4966,7 +4942,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I46" s="29" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -4975,9 +4951,9 @@
       <c r="K46" s="15" t="n"/>
       <c r="L46" s="15" t="n"/>
       <c r="M46" s="15" t="n"/>
-      <c r="N46" s="30" t="n"/>
+      <c r="N46" s="28" t="n"/>
       <c r="O46" s="15" t="n"/>
-      <c r="P46" s="31" t="inlineStr">
+      <c r="P46" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4992,18 +4968,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="25">
         <f>IF($E47="","",DATE(YEAR($E47),MONTH($E47),1))</f>
         <v/>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="25">
         <f>IF($E47="","",EOMONTH($E47,0))</f>
         <v/>
       </c>
-      <c r="E47" s="27" t="n">
+      <c r="E47" s="25" t="n">
         <v>46139</v>
       </c>
-      <c r="F47" s="28" t="n">
+      <c r="F47" s="26" t="n">
         <v>2598639.67</v>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -5016,7 +4992,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I47" s="29" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -5025,9 +5001,9 @@
       <c r="K47" s="15" t="n"/>
       <c r="L47" s="15" t="n"/>
       <c r="M47" s="15" t="n"/>
-      <c r="N47" s="30" t="n"/>
+      <c r="N47" s="28" t="n"/>
       <c r="O47" s="15" t="n"/>
-      <c r="P47" s="31" t="inlineStr">
+      <c r="P47" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5042,18 +5018,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="25">
         <f>IF($E48="","",DATE(YEAR($E48),MONTH($E48),1))</f>
         <v/>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="25">
         <f>IF($E48="","",EOMONTH($E48,0))</f>
         <v/>
       </c>
-      <c r="E48" s="27" t="n">
+      <c r="E48" s="25" t="n">
         <v>46142</v>
       </c>
-      <c r="F48" s="28" t="n">
+      <c r="F48" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -5066,14 +5042,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I48" s="29" t="inlineStr"/>
+      <c r="I48" s="27" t="inlineStr"/>
       <c r="J48" s="15" t="n"/>
       <c r="K48" s="15" t="n"/>
       <c r="L48" s="15" t="n"/>
       <c r="M48" s="15" t="n"/>
-      <c r="N48" s="30" t="n"/>
+      <c r="N48" s="28" t="n"/>
       <c r="O48" s="15" t="n"/>
-      <c r="P48" s="31" t="inlineStr">
+      <c r="P48" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5088,18 +5064,18 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="25">
         <f>IF($E49="","",DATE(YEAR($E49),MONTH($E49),1))</f>
         <v/>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="25">
         <f>IF($E49="","",EOMONTH($E49,0))</f>
         <v/>
       </c>
-      <c r="E49" s="27" t="n">
+      <c r="E49" s="25" t="n">
         <v>46142</v>
       </c>
-      <c r="F49" s="28" t="n">
+      <c r="F49" s="26" t="n">
         <v>3232025.51</v>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -5112,7 +5088,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I49" s="29" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -5121,9 +5097,9 @@
       <c r="K49" s="15" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15" t="n"/>
-      <c r="N49" s="30" t="n"/>
+      <c r="N49" s="28" t="n"/>
       <c r="O49" s="15" t="n"/>
-      <c r="P49" s="31" t="inlineStr">
+      <c r="P49" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5138,18 +5114,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="25">
         <f>IF($E50="","",DATE(YEAR($E50),MONTH($E50),1))</f>
         <v/>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="25">
         <f>IF($E50="","",EOMONTH($E50,0))</f>
         <v/>
       </c>
-      <c r="E50" s="27" t="n">
+      <c r="E50" s="25" t="n">
         <v>46147</v>
       </c>
-      <c r="F50" s="28" t="n">
+      <c r="F50" s="26" t="n">
         <v>3723586.74</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -5162,14 +5138,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I50" s="29" t="inlineStr"/>
+      <c r="I50" s="27" t="inlineStr"/>
       <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="n"/>
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15" t="n"/>
-      <c r="N50" s="30" t="n"/>
+      <c r="N50" s="28" t="n"/>
       <c r="O50" s="15" t="n"/>
-      <c r="P50" s="31" t="inlineStr">
+      <c r="P50" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5184,18 +5160,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="25">
         <f>IF($E51="","",DATE(YEAR($E51),MONTH($E51),1))</f>
         <v/>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="25">
         <f>IF($E51="","",EOMONTH($E51,0))</f>
         <v/>
       </c>
-      <c r="E51" s="27" t="n">
+      <c r="E51" s="25" t="n">
         <v>46150</v>
       </c>
-      <c r="F51" s="28" t="n">
+      <c r="F51" s="26" t="n">
         <v>5009315.83</v>
       </c>
       <c r="G51" s="10" t="inlineStr"/>
@@ -5204,7 +5180,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I51" s="29" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -5213,9 +5189,9 @@
       <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15" t="n"/>
-      <c r="N51" s="30" t="n"/>
+      <c r="N51" s="28" t="n"/>
       <c r="O51" s="15" t="n"/>
-      <c r="P51" s="31" t="inlineStr">
+      <c r="P51" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5230,18 +5206,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="25">
         <f>IF($E52="","",DATE(YEAR($E52),MONTH($E52),1))</f>
         <v/>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="25">
         <f>IF($E52="","",EOMONTH($E52,0))</f>
         <v/>
       </c>
-      <c r="E52" s="27" t="n">
+      <c r="E52" s="25" t="n">
         <v>46157</v>
       </c>
-      <c r="F52" s="28" t="n">
+      <c r="F52" s="26" t="n">
         <v>4340970.4</v>
       </c>
       <c r="G52" s="10" t="inlineStr"/>
@@ -5250,7 +5226,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I52" s="29" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>ref_whitespace_cleaned; no_named_beneficiary</t>
         </is>
@@ -5259,9 +5235,9 @@
       <c r="K52" s="15" t="n"/>
       <c r="L52" s="15" t="n"/>
       <c r="M52" s="15" t="n"/>
-      <c r="N52" s="30" t="n"/>
+      <c r="N52" s="28" t="n"/>
       <c r="O52" s="15" t="n"/>
-      <c r="P52" s="31" t="inlineStr">
+      <c r="P52" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5276,18 +5252,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="25">
         <f>IF($E53="","",DATE(YEAR($E53),MONTH($E53),1))</f>
         <v/>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="25">
         <f>IF($E53="","",EOMONTH($E53,0))</f>
         <v/>
       </c>
-      <c r="E53" s="27" t="n">
+      <c r="E53" s="25" t="n">
         <v>46170</v>
       </c>
-      <c r="F53" s="28" t="n">
+      <c r="F53" s="26" t="n">
         <v>2400509.91</v>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -5300,7 +5276,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I53" s="29" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -5309,9 +5285,9 @@
       <c r="K53" s="15" t="n"/>
       <c r="L53" s="15" t="n"/>
       <c r="M53" s="15" t="n"/>
-      <c r="N53" s="30" t="n"/>
+      <c r="N53" s="28" t="n"/>
       <c r="O53" s="15" t="n"/>
-      <c r="P53" s="31" t="inlineStr">
+      <c r="P53" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5326,18 +5302,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="25">
         <f>IF($E54="","",DATE(YEAR($E54),MONTH($E54),1))</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="25">
         <f>IF($E54="","",EOMONTH($E54,0))</f>
         <v/>
       </c>
-      <c r="E54" s="27" t="n">
+      <c r="E54" s="25" t="n">
         <v>46171</v>
       </c>
-      <c r="F54" s="28" t="n">
+      <c r="F54" s="26" t="n">
         <v>3444449.93</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -5350,7 +5326,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I54" s="29" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -5359,9 +5335,9 @@
       <c r="K54" s="15" t="n"/>
       <c r="L54" s="15" t="n"/>
       <c r="M54" s="15" t="n"/>
-      <c r="N54" s="30" t="n"/>
+      <c r="N54" s="28" t="n"/>
       <c r="O54" s="15" t="n"/>
-      <c r="P54" s="31" t="inlineStr">
+      <c r="P54" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5376,18 +5352,18 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="25">
         <f>IF($E55="","",DATE(YEAR($E55),MONTH($E55),1))</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="25">
         <f>IF($E55="","",EOMONTH($E55,0))</f>
         <v/>
       </c>
-      <c r="E55" s="27" t="n">
+      <c r="E55" s="25" t="n">
         <v>46171</v>
       </c>
-      <c r="F55" s="28" t="n">
+      <c r="F55" s="26" t="n">
         <v>2450000</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -5400,14 +5376,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I55" s="29" t="inlineStr"/>
+      <c r="I55" s="27" t="inlineStr"/>
       <c r="J55" s="15" t="n"/>
       <c r="K55" s="15" t="n"/>
       <c r="L55" s="15" t="n"/>
       <c r="M55" s="15" t="n"/>
-      <c r="N55" s="30" t="n"/>
+      <c r="N55" s="28" t="n"/>
       <c r="O55" s="15" t="n"/>
-      <c r="P55" s="31" t="inlineStr">
+      <c r="P55" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5422,18 +5398,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="25">
         <f>IF($E56="","",DATE(YEAR($E56),MONTH($E56),1))</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="25">
         <f>IF($E56="","",EOMONTH($E56,0))</f>
         <v/>
       </c>
-      <c r="E56" s="27" t="n">
+      <c r="E56" s="25" t="n">
         <v>46176</v>
       </c>
-      <c r="F56" s="28" t="n">
+      <c r="F56" s="26" t="n">
         <v>5210470.59</v>
       </c>
       <c r="G56" s="10" t="inlineStr"/>
@@ -5442,7 +5418,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I56" s="29" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>ref_typo_corrected_from:ACH PYMTS - LCL BULK FNG; no_named_beneficiary</t>
         </is>
@@ -5451,9 +5427,9 @@
       <c r="K56" s="15" t="n"/>
       <c r="L56" s="15" t="n"/>
       <c r="M56" s="15" t="n"/>
-      <c r="N56" s="30" t="n"/>
+      <c r="N56" s="28" t="n"/>
       <c r="O56" s="15" t="n"/>
-      <c r="P56" s="31" t="inlineStr">
+      <c r="P56" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5468,18 +5444,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="25">
         <f>IF($E57="","",DATE(YEAR($E57),MONTH($E57),1))</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="25">
         <f>IF($E57="","",EOMONTH($E57,0))</f>
         <v/>
       </c>
-      <c r="E57" s="27" t="n">
+      <c r="E57" s="25" t="n">
         <v>46177</v>
       </c>
-      <c r="F57" s="28" t="n">
+      <c r="F57" s="26" t="n">
         <v>4006482.03</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -5492,14 +5468,14 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I57" s="29" t="inlineStr"/>
+      <c r="I57" s="27" t="inlineStr"/>
       <c r="J57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
       <c r="L57" s="15" t="n"/>
       <c r="M57" s="15" t="n"/>
-      <c r="N57" s="30" t="n"/>
+      <c r="N57" s="28" t="n"/>
       <c r="O57" s="15" t="n"/>
-      <c r="P57" s="31" t="inlineStr">
+      <c r="P57" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5514,18 +5490,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="25">
         <f>IF($E58="","",DATE(YEAR($E58),MONTH($E58),1))</f>
         <v/>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="25">
         <f>IF($E58="","",EOMONTH($E58,0))</f>
         <v/>
       </c>
-      <c r="E58" s="27" t="n">
+      <c r="E58" s="25" t="n">
         <v>46184</v>
       </c>
-      <c r="F58" s="28" t="n">
+      <c r="F58" s="26" t="n">
         <v>6226088.99</v>
       </c>
       <c r="G58" s="10" t="inlineStr"/>
@@ -5534,7 +5510,7 @@
           <t>ACH PYMTS - LCL BULK FNDG</t>
         </is>
       </c>
-      <c r="I58" s="29" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>no_named_beneficiary</t>
         </is>
@@ -5543,9 +5519,9 @@
       <c r="K58" s="15" t="n"/>
       <c r="L58" s="15" t="n"/>
       <c r="M58" s="15" t="n"/>
-      <c r="N58" s="30" t="n"/>
+      <c r="N58" s="28" t="n"/>
       <c r="O58" s="15" t="n"/>
-      <c r="P58" s="31" t="inlineStr">
+      <c r="P58" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5560,18 +5536,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="25">
         <f>IF($E59="","",DATE(YEAR($E59),MONTH($E59),1))</f>
         <v/>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="25">
         <f>IF($E59="","",EOMONTH($E59,0))</f>
         <v/>
       </c>
-      <c r="E59" s="27" t="n">
+      <c r="E59" s="25" t="n">
         <v>46185</v>
       </c>
-      <c r="F59" s="28" t="n">
+      <c r="F59" s="26" t="n">
         <v>2292348.71</v>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -5584,7 +5560,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I59" s="29" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -5593,9 +5569,9 @@
       <c r="K59" s="15" t="n"/>
       <c r="L59" s="15" t="n"/>
       <c r="M59" s="15" t="n"/>
-      <c r="N59" s="30" t="n"/>
+      <c r="N59" s="28" t="n"/>
       <c r="O59" s="15" t="n"/>
-      <c r="P59" s="31" t="inlineStr">
+      <c r="P59" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5610,18 +5586,18 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="25">
         <f>IF($E60="","",DATE(YEAR($E60),MONTH($E60),1))</f>
         <v/>
       </c>
-      <c r="D60" s="27">
+      <c r="D60" s="25">
         <f>IF($E60="","",EOMONTH($E60,0))</f>
         <v/>
       </c>
-      <c r="E60" s="27" t="n">
+      <c r="E60" s="25" t="n">
         <v>46202</v>
       </c>
-      <c r="F60" s="28" t="n">
+      <c r="F60" s="26" t="n">
         <v>2782960.69</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -5634,7 +5610,7 @@
           <t>ISSUE CHAPS PAYMENT</t>
         </is>
       </c>
-      <c r="I60" s="29" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>party_whitespace_cleaned</t>
         </is>
@@ -5643,21 +5619,21 @@
       <c r="K60" s="15" t="n"/>
       <c r="L60" s="15" t="n"/>
       <c r="M60" s="15" t="n"/>
-      <c r="N60" s="30" t="n"/>
+      <c r="N60" s="28" t="n"/>
       <c r="O60" s="15" t="n"/>
-      <c r="P60" s="31" t="inlineStr">
+      <c r="P60" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="E61" s="32" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F61" s="33">
+      <c r="F61" s="31">
         <f>SUM(F5:F60)</f>
         <v/>
       </c>
@@ -5842,7 +5818,7 @@
       <c r="C6" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>5, 6, 7, 8, 12, 13, 14, 15, 19, 20, 21, 22, ... (+15 more)</t>
         </is>
@@ -5862,7 +5838,7 @@
       <c r="C7" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 17, 18, ... (+14 more)</t>
         </is>
@@ -5882,7 +5858,7 @@
       <c r="C8" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>1, 3, 4, 9, 10, 11, 17, 18, 25, 26, 31, 35, ... (+6 more)</t>
         </is>
@@ -5902,7 +5878,7 @@
       <c r="C9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>12, 20, 27</t>
         </is>
@@ -5922,7 +5898,7 @@
       <c r="C10" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -5942,7 +5918,7 @@
       <c r="C11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -5961,7 +5937,7 @@
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5973,7 +5949,7 @@
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5985,7 +5961,7 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -5997,7 +5973,7 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>*</t>
         </is>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D62"/>
+  <dimension ref="B2:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1021,138 +1021,144 @@
     <row r="33">
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Invoice list amount column</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr"/>
+          <t>Invoice document type</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+          <t>The PDF is taken from the invoice, which is the KR document and carries a NEGATIVE amount. The list it is picked from holds several types at once -- ZP payments, KR invoices, SB statement documents -- so without this filter the largest row is usually a payment, not an invoice. Comparisons are on magnitude, so the negative sign does not matter.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Invoice list supplier column</t>
+          <t>Invoice list amount column</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Caption of the supplier column in that same file.</t>
+          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Invoice list document column</t>
+          <t>Invoice list supplier column</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Caption of the invoice-number column in that same file.</t>
+          <t>Caption of the supplier column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Extra popup titles to allow</t>
+          <t>Invoice list document column</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+          <t>Caption of the invoice-number column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>Extra popup titles to allow</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
+          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr"/>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>Samples in the sheet</t>
-        </is>
-      </c>
-      <c r="C41" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Included in the next run</t>
+          <t>Samples in the sheet</t>
         </is>
       </c>
       <c r="C42" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Included in the next run</t>
         </is>
       </c>
       <c r="C43" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"No")</f>
+        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>DONE -- invoice downloaded</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C44" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
+        <f>COUNTIF(Samples!P5:P1000,"No")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C45" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_SCF -- Santander, needs the extra hop</t>
+          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_SCF")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
         <v/>
       </c>
     </row>
@@ -1247,64 +1253,75 @@
     <row r="55">
       <c r="B55" s="14" t="inlineStr">
         <is>
+          <t>Reached a confirming (Santander SCF) payment</t>
+        </is>
+      </c>
+      <c r="C55" s="15">
+        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C55" s="15">
+      <c r="C56" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="3" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
+          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="14" t="inlineStr">
         <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="B63" s="14" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C62" s="16" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1313,9 +1330,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C63:D63"/>
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C59:D59"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1337,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F66"/>
+  <dimension ref="A2:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2433,66 +2450,66 @@
     <row r="50" ht="30" customHeight="1">
       <c r="B50" s="20" t="inlineStr">
         <is>
+          <t>Fbl1n.DocNumberField</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>The document-number field itself, inside dynamic selections. Used when the batch holds a single document, so the multiple-selection dialog is not needed</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/ssub%_SUBSCREEN_%_SUB%_CONTAINER:SAPLSSEL:2001/ssubSUBSCREEN_CONTAINER2:SAPLSSEL:2000/ssubSUBSCREEN_CONTAINER:SAPLSSEL:1106/txt%%DYN011-LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="20" t="inlineStr">
+        <is>
           <t>Fbl1n.DocNumberMultiSelect</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>Multiple-selection arrow for document number, inside the dynamic-selections subscreen</t>
         </is>
       </c>
-      <c r="D50" s="21" t="inlineStr">
+      <c r="D51" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/ssub%_SUBSCREEN_%_SUB%_CONTAINER:SAPLSSEL:2001/ssubSUBSCREEN_CONTAINER2:SAPLSSEL:2000/ssubSUBSCREEN_CONTAINER:SAPLSSEL:1106/btn%_%%DYN011_%_APP_%-VALU_PUSH</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>MultiSel.PasteFromClipboard</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>'Upload from clipboard' on the multiple-selection dialog</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E51" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>wnd[1]/tbar[0]/btn[24]</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>MultiSel.Confirm</t>
+          <t>MultiSel.PasteFromClipboard</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Copy on that dialog</t>
+          <t>'Upload from clipboard' on the multiple-selection dialog</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -2507,19 +2524,19 @@
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[8]</t>
+          <t>wnd[1]/tbar[0]/btn[24]</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.ExecuteButton</t>
+          <t>MultiSel.Confirm</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Execute</t>
+          <t>Copy on that dialog</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
@@ -2534,89 +2551,89 @@
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/tbar[1]/btn[8]</t>
+          <t>wnd[1]/tbar[0]/btn[8]</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="20" t="inlineStr">
         <is>
+          <t>Fbl1n.ExecuteButton</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Execute</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/tbar[1]/btn[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="20" t="inlineStr">
+        <is>
           <t>Fbl1n.ResultAnchor</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>Confirms the FBL1N result came up. NOTE: FBL1N renders as a CLASSIC LIST here (lbl[x,y]), not an ALV grid, so there is no grid to read -- the list is exported and read back instead. VERIFY</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="E54" s="22" t="inlineStr">
+      <c r="E55" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/lbl[164,8]</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="18" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>Step 10: the largest payment's invoices, and the PDF</t>
         </is>
       </c>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="19" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="20" t="inlineStr">
-        <is>
-          <t>Payment.UsageMenu</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>Environment &gt; Payment usage from inside the payment document. menu[4] here, not the menu[5] used from the clearing document -- menu indices differ per screen. VERIFY</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E56" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/mbar/menu[4]/menu[3]</t>
-        </is>
-      </c>
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>Invoice.GosToolbox</t>
+          <t>Payment.UsageMenu</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Services-for-object toolbox. shellcont[2], not the plain shellcont that was predicted</t>
-        </is>
-      </c>
-      <c r="D57" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Environment &gt; Payment usage from inside the payment document. menu[4] here, not the menu[5] used from the clearing document -- menu indices differ per screen. VERIFY</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E57" s="22" t="inlineStr">
@@ -2626,19 +2643,19 @@
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/titl/shellcont[2]/shell</t>
+          <t>wnd[0]/mbar/menu[4]/menu[3]</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListGrid</t>
+          <t>Invoice.GosToolbox</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Attachment-list grid. CONTAINER_0100</t>
+          <t>Services-for-object toolbox. The container index is NOT stable -- N1.vbs found it at shellcont[2] and B2.vbs at shellcont[1] on the same system, because it depends on what else the title bar carries. The macro tries this value first and then probes the neighbours, so it is a hint, not a hard ID</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -2653,19 +2670,19 @@
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/cntlCONTAINER_0100/shellcont/shell</t>
+          <t>wnd[0]/titl/shellcont[1]/shell</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListColumn</t>
+          <t>Invoice.AttachListGrid</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Column used to select the attachment row</t>
+          <t>Attachment-list grid. CONTAINER_0100</t>
         </is>
       </c>
       <c r="D59" s="21" t="inlineStr">
@@ -2680,19 +2697,19 @@
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>BITM_DESCR</t>
+          <t>wnd[1]/usr/cntlCONTAINER_0100/shellcont/shell</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Invoice.ExportMenuItem</t>
+          <t>Invoice.AttachListColumn</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Context-menu entry that saves the attachment. A CONTEXT MENU item, not the toolbar button that was predicted</t>
+          <t>Column used to select the attachment row</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -2707,19 +2724,19 @@
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>%ATTA_EXPORT</t>
+          <t>BITM_DESCR</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Invoice.SaveWindow</t>
+          <t>Invoice.ExportMenuItem</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Window the PDF save dialog opens in. wnd[2], because the attachment list is already wnd[1]</t>
+          <t>Context-menu entry that saves the attachment. A CONTEXT MENU item, not the toolbar button that was predicted</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr">
@@ -2734,53 +2751,80 @@
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>wnd[2]</t>
+          <t>%ATTA_EXPORT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="20" t="inlineStr">
         <is>
+          <t>Invoice.SaveWindow</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Window the PDF save dialog opens in. wnd[2], because the attachment list is already wnd[1]</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>wnd[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="20" t="inlineStr">
+        <is>
           <t>Invoice.CloseAttachList</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>Closes the attachment list afterwards</t>
         </is>
       </c>
-      <c r="D62" s="21" t="inlineStr">
+      <c r="D63" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E62" s="22" t="inlineStr">
+      <c r="E63" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F62" s="23" t="inlineStr">
+      <c r="F63" s="23" t="inlineStr">
         <is>
           <t>wnd[1]/tbar[0]/btn[0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
+          <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>The recording entered dates as 8 digits with no separators (01092025). The Control sheet's 'SAP date format' is set to DDMMYYYY to match. Do not change it to DMY unless you have checked that this system accepts 01.09.2025 as well.</t>
         </is>
@@ -2790,18 +2834,18 @@
   <mergeCells count="14">
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B64:F64"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B56:F56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F67"/>
+  <dimension ref="A2:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Posting status column. VERIFY</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Update-status column. The grid dump on PP2 shows no ESTAT -- VB1OK 'Update 1 OK' and VB2OK '2nd update OK' are what this release carries</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>ESTAT</t>
+          <t>VB1OK</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Bank reference / note-to-payee, logged as context. VERIFY</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Note-to-payee, logged beside each match as context. The grid dump shows no SGTXT; VWEZW is 'Payment Notes' and VGREF is 'Bank reference'</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>SGTXT</t>
+          <t>VWEZW</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
     <row r="56">
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>Step 10: the largest payment's invoices, and the PDF</t>
+          <t>Opening a document by number (FB03)</t>
         </is>
       </c>
       <c r="C56" s="19" t="n"/>
@@ -2623,12 +2623,12 @@
     <row r="57">
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>Payment.UsageMenu</t>
+          <t>FB03.DocNumber</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Environment &gt; Payment usage from inside the payment document. menu[4] here, not the menu[5] used from the clearing document -- menu indices differ per screen. VERIFY</t>
+          <t>Document number field on the FB03 entry screen. This is how the largest payment is opened -- by number, not by clicking a row. Standard SAP; run modProbe.ProbeCurrentScreen on FB03 to confirm. VERIFY</t>
         </is>
       </c>
       <c r="D57" s="24" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/mbar/menu[4]/menu[3]</t>
+          <t>wnd[0]/usr/txtRF05L-BELNR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Invoice.GosToolbox</t>
+          <t>FB03.CompanyCode</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Services-for-object toolbox. The container index is NOT stable -- N1.vbs found it at shellcont[2] and B2.vbs at shellcont[1] on the same system, because it depends on what else the title bar carries. The macro tries this value first and then probes the neighbours, so it is a hint, not a hard ID</t>
-        </is>
-      </c>
-      <c r="D58" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Company code field on that screen. VERIFY</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E58" s="22" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/titl/shellcont[1]/shell</t>
+          <t>wnd[0]/usr/ctxtRF05L-BUKRS</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListGrid</t>
+          <t>FB03.FiscalYear</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Attachment-list grid. CONTAINER_0100</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Fiscal year field on that screen. VERIFY</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E59" s="22" t="inlineStr">
@@ -2697,51 +2697,35 @@
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/cntlCONTAINER_0100/shellcont/shell</t>
+          <t>wnd[0]/usr/txtRF05L-GJAHR</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>Invoice.AttachListColumn</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Column used to select the attachment row</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E60" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>BITM_DESCR</t>
-        </is>
-      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Step 10: the largest payment's invoices, and the PDF</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Invoice.ExportMenuItem</t>
+          <t>Payment.UsageMenu</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Context-menu entry that saves the attachment. A CONTEXT MENU item, not the toolbar button that was predicted</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Environment &gt; Payment usage from inside the payment document. menu[4] here, not the menu[5] used from the clearing document -- menu indices differ per screen. VERIFY</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E61" s="22" t="inlineStr">
@@ -2751,19 +2735,19 @@
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>%ATTA_EXPORT</t>
+          <t>wnd[0]/mbar/menu[4]/menu[3]</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Invoice.SaveWindow</t>
+          <t>Invoice.GosToolbox</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Window the PDF save dialog opens in. wnd[2], because the attachment list is already wnd[1]</t>
+          <t>Services-for-object toolbox. The container index is NOT stable -- N1.vbs found it at shellcont[2] and B2.vbs at shellcont[1] on the same system, because it depends on what else the title bar carries. The macro tries this value first and then probes the neighbours, so it is a hint, not a hard ID</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -2778,74 +2762,183 @@
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>wnd[2]</t>
+          <t>wnd[0]/titl/shellcont[1]/shell</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="20" t="inlineStr">
         <is>
+          <t>Invoice.AttachListGrid</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Attachment-list grid. CONTAINER_0100</t>
+        </is>
+      </c>
+      <c r="D63" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/cntlCONTAINER_0100/shellcont/shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.AttachListColumn</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Column used to select the attachment row</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>BITM_DESCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.ExportMenuItem</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Context-menu entry that saves the attachment. A CONTEXT MENU item, not the toolbar button that was predicted</t>
+        </is>
+      </c>
+      <c r="D65" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>%ATTA_EXPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Invoice.SaveWindow</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>Window the PDF save dialog opens in. wnd[2], because the attachment list is already wnd[1]</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>wnd[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="20" t="inlineStr">
+        <is>
           <t>Invoice.CloseAttachList</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr">
         <is>
           <t>Closes the attachment list afterwards</t>
         </is>
       </c>
-      <c r="D63" s="21" t="inlineStr">
+      <c r="D67" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E63" s="22" t="inlineStr">
+      <c r="E67" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F63" s="23" t="inlineStr">
+      <c r="F67" s="23" t="inlineStr">
         <is>
           <t>wnd[1]/tbar[0]/btn[0]</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="B65" s="16" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="B66" s="16" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="B67" s="16" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>The recording entered dates as 8 digits with no separators (01092025). The Control sheet's 'SAP date format' is set to DDMMYYYY to match. Do not change it to DMY unless you have checked that this system accepts 01.09.2025 as well.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B69:F69"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B71:F71"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B70:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -2612,7 +2612,7 @@
     <row r="56">
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>Opening a document by number (FB03)</t>
+          <t>FB03: fallback only, not the normal path</t>
         </is>
       </c>
       <c r="C56" s="19" t="n"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Document number field on the FB03 entry screen. This is how the largest payment is opened -- by number, not by clicking a row. Standard SAP; run modProbe.ProbeCurrentScreen on FB03 to confirm. VERIFY</t>
+          <t>The largest payment is normally opened from the FBL1N list itself, by finding the label whose text is its document number -- the same F2 drill the recordings use, aimed by content instead of by screen position. FB03 is only used if that number is not on screen, e.g. a long list that has scrolled. Leave these blank to disable the fallback entirely. VERIFY</t>
         </is>
       </c>
       <c r="D57" s="24" t="inlineStr">

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>DRY RUN walks every screen and logs what it would export, without exporting. EXTRACT performs the exports. Always complete one clean DRY RUN first.</t>
+          <t>Both modes run the WHOLE chain and write the same files -- the exports are read-only on the SAP side, and the chain reads them back, so it cannot run without them. The only difference is where they land: DRY RUN puts everything under a '_dry run' subfolder of the download root, so a rehearsal is never mistaken for the evidence pack. Do one clean DRY RUN, read the Log, then switch.</t>
         </is>
       </c>
     </row>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -932,7 +932,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Only documents of this type are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document.</t>
+          <t>Only documents of these types are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document. Takes a comma-separated list -- 'ZP, ZV, KZ' -- for batches paid outside the normal payment run. When nothing matches, the Log names the types the file actually held.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F71"/>
+  <dimension ref="A2:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2064,117 +2064,117 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Doc.OverviewButton</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Document-overview button. F2 on the FBL1N list lands on the LINE ITEM, and Environment &gt; Payment usage lives on the document -- this is the hop between them, pressed in N1.vbs. Only used when the usage menu is missing, so clearing it just skips the attempt</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/tbar[1]/btn[9]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Step 6: Environment &gt; Payment Usage</t>
         </is>
       </c>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="19" t="n"/>
-      <c r="F34" s="19" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>PaymentUsage.Menu</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Menu path to the batch's payment documents. Confirmed in all four recordings</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/mbar/menu[5]/menu[3]</t>
-        </is>
-      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="20" t="inlineStr">
         <is>
+          <t>PaymentUsage.Menu</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Menu path to the batch's payment documents. Confirmed in all four recordings</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/mbar/menu[5]/menu[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="20" t="inlineStr">
+        <is>
           <t>PaymentUsage.ListAnchor</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>An element that exists on that list, used only to confirm the menu landed. Clear it to skip the check</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/chk[1,6]</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="18" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Step 7: classic list export (List &gt; Save/Send &gt; File)</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Export.ListMenu</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Menu path that opens the save-list dialog</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/mbar/menu[0]/menu[3]/menu[1]</t>
-        </is>
-      </c>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Export.FormatOkButton</t>
+          <t>Export.ListMenu</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Confirm the file-format popup</t>
+          <t>Menu path that opens the save-list dialog</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -2189,19 +2189,19 @@
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[0]</t>
+          <t>wnd[0]/mbar/menu[0]/menu[3]/menu[1]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Save.Path</t>
+          <t>Export.FormatOkButton</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Directory field</t>
+          <t>Confirm the file-format popup</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -2216,19 +2216,19 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_PATH</t>
+          <t>wnd[1]/tbar[0]/btn[0]</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Save.FileName</t>
+          <t>Save.Path</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>File name field. Confirmed in Audit2.vbs and Audit5.vbs</t>
+          <t>Directory field</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -2243,111 +2243,111 @@
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
+          <t>wnd[1]/usr/ctxtDY_PATH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Save.Encoding</t>
+          <t>Save.FileName</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Encoding field, where present. VERIFY</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>File name field. Confirmed in Audit2.vbs and Audit5.vbs</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
         </is>
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
+          <t>wnd[1]/usr/ctxtDY_FILENAME</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="20" t="inlineStr">
         <is>
+          <t>Save.Encoding</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Encoding field, where present. VERIFY</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>wnd[1]/usr/ctxtDY_FILE_ENCODING</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="20" t="inlineStr">
+        <is>
           <t>Save.GenerateButton</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>Confirm the save. btn[0], not btn[11]</t>
         </is>
       </c>
-      <c r="D43" s="21" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E43" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>wnd[1]/tbar[0]/btn[0]</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="18" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>Steps 8-9: FBL1N, the ZP payments of the batch</t>
         </is>
       </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Fbl1n.AllItemsRadio</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>'All items' radio</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/usr/radX_AISEL</t>
-        </is>
-      </c>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.CompanyCode</t>
+          <t>Fbl1n.AllItemsRadio</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Company code. KD_BUKRS, not the DD_BUKRS that was predicted</t>
+          <t>'All items' radio</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -2362,19 +2362,19 @@
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtKD_BUKRS-LOW</t>
+          <t>wnd[0]/usr/radX_AISEL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.PostingDateFrom</t>
+          <t>Fbl1n.CompanyCode</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Posting date, low</t>
+          <t>Company code. KD_BUKRS, not the DD_BUKRS that was predicted</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
@@ -2389,19 +2389,19 @@
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtSO_BUDAT-LOW</t>
+          <t>wnd[0]/usr/ctxtKD_BUKRS-LOW</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.PostingDateTo</t>
+          <t>Fbl1n.PostingDateFrom</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Posting date, high</t>
+          <t>Posting date, low</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -2416,127 +2416,127 @@
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtSO_BUDAT-HIGH</t>
+          <t>wnd[0]/usr/ctxtSO_BUDAT-LOW</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="20" t="inlineStr">
         <is>
+          <t>Fbl1n.PostingDateTo</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Posting date, high</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/ctxtSO_BUDAT-HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="20" t="inlineStr">
+        <is>
           <t>Fbl1n.DynamicSelections</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Opens the dynamic-selections block. The document number is NOT on the main selection screen -- it lives in dynamic selections, so this has to be pressed before the field below exists</t>
         </is>
       </c>
-      <c r="D49" s="21" t="inlineStr">
+      <c r="D50" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E49" s="22" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/tbar[1]/btn[16]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t>Fbl1n.DocNumberField</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>The document-number field itself, inside dynamic selections. Used when the batch holds a single document, so the multiple-selection dialog is not needed</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E50" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/usr/ssub%_SUBSCREEN_%_SUB%_CONTAINER:SAPLSSEL:2001/ssubSUBSCREEN_CONTAINER2:SAPLSSEL:2000/ssubSUBSCREEN_CONTAINER:SAPLSSEL:1106/txt%%DYN011-LOW</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="B51" s="20" t="inlineStr">
         <is>
+          <t>Fbl1n.DocNumberField</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>The document-number field itself, inside dynamic selections. Used when the batch holds a single document, so the multiple-selection dialog is not needed</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/ssub%_SUBSCREEN_%_SUB%_CONTAINER:SAPLSSEL:2001/ssubSUBSCREEN_CONTAINER2:SAPLSSEL:2000/ssubSUBSCREEN_CONTAINER:SAPLSSEL:1106/txt%%DYN011-LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="20" t="inlineStr">
+        <is>
           <t>Fbl1n.DocNumberMultiSelect</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>Multiple-selection arrow for document number, inside the dynamic-selections subscreen</t>
         </is>
       </c>
-      <c r="D51" s="21" t="inlineStr">
+      <c r="D52" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E51" s="22" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/ssub%_SUBSCREEN_%_SUB%_CONTAINER:SAPLSSEL:2001/ssubSUBSCREEN_CONTAINER2:SAPLSSEL:2000/ssubSUBSCREEN_CONTAINER:SAPLSSEL:1106/btn%_%%DYN011_%_APP_%-VALU_PUSH</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="20" t="inlineStr">
-        <is>
-          <t>MultiSel.PasteFromClipboard</t>
-        </is>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>'Upload from clipboard' on the multiple-selection dialog</t>
-        </is>
-      </c>
-      <c r="D52" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
-        </is>
-      </c>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>wnd[1]/tbar[0]/btn[24]</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>MultiSel.Confirm</t>
+          <t>MultiSel.PasteFromClipboard</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Copy on that dialog</t>
+          <t>'Upload from clipboard' on the multiple-selection dialog</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
@@ -2551,19 +2551,19 @@
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/tbar[0]/btn[8]</t>
+          <t>wnd[1]/tbar[0]/btn[24]</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Fbl1n.ExecuteButton</t>
+          <t>MultiSel.Confirm</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Execute</t>
+          <t>Copy on that dialog</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -2578,84 +2578,84 @@
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/tbar[1]/btn[8]</t>
+          <t>wnd[1]/tbar[0]/btn[8]</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="20" t="inlineStr">
         <is>
+          <t>Fbl1n.ExecuteButton</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Execute</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/tbar[1]/btn[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="20" t="inlineStr">
+        <is>
           <t>Fbl1n.ResultAnchor</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>Confirms the FBL1N result came up. NOTE: FBL1N renders as a CLASSIC LIST here (lbl[x,y]), not an ALV grid, so there is no grid to read -- the list is exported and read back instead. VERIFY</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D56" s="24" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="E55" s="22" t="inlineStr">
+      <c r="E56" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F55" s="23" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/lbl[164,8]</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="18" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="18" t="inlineStr">
         <is>
           <t>FB03: fallback only, not the normal path</t>
         </is>
       </c>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
-      <c r="E56" s="19" t="n"/>
-      <c r="F56" s="19" t="n"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>FB03.DocNumber</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>The largest payment is normally opened from the FBL1N list itself, by finding the label whose text is its document number -- the same F2 drill the recordings use, aimed by content instead of by screen position. FB03 is only used if that number is not on screen, e.g. a long list that has scrolled. Leave these blank to disable the fallback entirely. VERIFY</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E57" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/usr/txtRF05L-BELNR</t>
-        </is>
-      </c>
+      <c r="C57" s="19" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="19" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>FB03.CompanyCode</t>
+          <t>FB03.DocNumber</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Company code field on that screen. VERIFY</t>
+          <t>The largest payment is normally opened from the FBL1N list itself, by finding the label whose text is its document number -- the same F2 drill the recordings use, aimed by content instead of by screen position. FB03 is only used if that number is not on screen, e.g. a long list that has scrolled. Leave these blank to disable the fallback entirely. VERIFY</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr">
@@ -2670,89 +2670,89 @@
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/usr/ctxtRF05L-BUKRS</t>
+          <t>wnd[0]/usr/txtRF05L-BELNR</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="20" t="inlineStr">
         <is>
+          <t>FB03.CompanyCode</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Company code field on that screen. VERIFY</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>wnd[0]/usr/ctxtRF05L-BUKRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="20" t="inlineStr">
+        <is>
           <t>FB03.FiscalYear</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>Fiscal year field on that screen. VERIFY</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D60" s="24" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E60" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F59" s="23" t="inlineStr">
+      <c r="F60" s="23" t="inlineStr">
         <is>
           <t>wnd[0]/usr/txtRF05L-GJAHR</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="18" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="18" t="inlineStr">
         <is>
           <t>Step 10: the largest payment's invoices, and the PDF</t>
         </is>
       </c>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>Payment.UsageMenu</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>Environment &gt; Payment usage from inside the payment document. menu[4] here, not the menu[5] used from the clearing document -- menu indices differ per screen. VERIFY</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E61" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F61" s="23" t="inlineStr">
-        <is>
-          <t>wnd[0]/mbar/menu[4]/menu[3]</t>
-        </is>
-      </c>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Invoice.GosToolbox</t>
+          <t>Payment.UsageMenu</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Services-for-object toolbox. The container index is NOT stable -- N1.vbs found it at shellcont[2] and B2.vbs at shellcont[1] on the same system, because it depends on what else the title bar carries. The macro tries this value first and then probes the neighbours, so it is a hint, not a hard ID</t>
-        </is>
-      </c>
-      <c r="D62" s="21" t="inlineStr">
-        <is>
-          <t>recorded</t>
+          <t>Environment &gt; Payment usage from inside the payment document. menu[4] here, not the menu[5] used from the clearing document -- menu indices differ per screen. VERIFY</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="E62" s="22" t="inlineStr">
@@ -2762,19 +2762,19 @@
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>wnd[0]/titl/shellcont[1]/shell</t>
+          <t>wnd[0]/mbar/menu[4]/menu[3]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListGrid</t>
+          <t>Invoice.GosToolbox</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Attachment-list grid. CONTAINER_0100</t>
+          <t>Services-for-object toolbox. The container index is NOT stable -- N1.vbs found it at shellcont[2] and B2.vbs at shellcont[1] on the same system, because it depends on what else the title bar carries. The macro tries this value first and then probes the neighbours, so it is a hint, not a hard ID</t>
         </is>
       </c>
       <c r="D63" s="21" t="inlineStr">
@@ -2789,19 +2789,19 @@
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>wnd[1]/usr/cntlCONTAINER_0100/shellcont/shell</t>
+          <t>wnd[0]/titl/shellcont[1]/shell</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Invoice.AttachListColumn</t>
+          <t>Invoice.AttachListGrid</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Column used to select the attachment row</t>
+          <t>Attachment-list grid. CONTAINER_0100</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -2816,19 +2816,19 @@
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>BITM_DESCR</t>
+          <t>wnd[1]/usr/cntlCONTAINER_0100/shellcont/shell</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>Invoice.ExportMenuItem</t>
+          <t>Invoice.AttachListColumn</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Context-menu entry that saves the attachment. A CONTEXT MENU item, not the toolbar button that was predicted</t>
+          <t>Column used to select the attachment row</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
@@ -2843,19 +2843,19 @@
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>%ATTA_EXPORT</t>
+          <t>BITM_DESCR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Invoice.SaveWindow</t>
+          <t>Invoice.ExportMenuItem</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Window the PDF save dialog opens in. wnd[2], because the attachment list is already wnd[1]</t>
+          <t>Context-menu entry that saves the attachment. A CONTEXT MENU item, not the toolbar button that was predicted</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -2870,75 +2870,102 @@
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>wnd[2]</t>
+          <t>%ATTA_EXPORT</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="20" t="inlineStr">
         <is>
+          <t>Invoice.SaveWindow</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Window the PDF save dialog opens in. wnd[2], because the attachment list is already wnd[1]</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>wnd[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="20" t="inlineStr">
+        <is>
           <t>Invoice.CloseAttachList</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>Closes the attachment list afterwards</t>
         </is>
       </c>
-      <c r="D67" s="21" t="inlineStr">
+      <c r="D68" s="21" t="inlineStr">
         <is>
           <t>recorded</t>
         </is>
       </c>
-      <c r="E67" s="22" t="inlineStr">
+      <c r="E68" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F67" s="23" t="inlineStr">
+      <c r="F68" s="23" t="inlineStr">
         <is>
           <t>wnd[1]/tbar[0]/btn[0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
+          <t>The macro reads column F only. A blank 'Required = Yes' row aborts the run with a message naming the missing key, rather than guessing at an ID.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="B71" s="16" t="inlineStr">
         <is>
+          <t>FEBAN's selection screen is a modal popup on this system (wnd[1]), not a full screen. That is why FEBAN.SelectionWindow exists -- the macro has to know which window to press Execute in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="B72" s="16" t="inlineStr">
+        <is>
           <t>The recording entered dates as 8 digits with no separators (01092025). The Control sheet's 'SAP date format' is set to DDMMYYYY to match. Do not change it to DMY unless you have checked that this system accepts 01.09.2025 as well.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B72:F72"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B61:F61"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -1026,12 +1026,12 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KR, RN</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>The PDF is taken from the invoice, which is the KR document and carries a NEGATIVE amount. The list it is picked from holds several types at once -- ZP payments, KR invoices, SB statement documents -- so without this filter the largest row is usually a payment, not an invoice. Comparisons are on magnitude, so the negative sign does not matter.</t>
+          <t>The PDF is taken from the invoice, which carries a NEGATIVE amount. The list it is picked from holds several types at once -- ZP payments, invoices, SB statement documents -- so without this filter the largest row is usually a payment, not an invoice. Comparisons are on magnitude, so the negative sign does not matter. Takes a comma-separated list: KR is the SAP standard, and the first invoice exported from this system came back as RN, so both are here. When nothing matches, the Log names the types the file actually held.</t>
         </is>
       </c>
     </row>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>The PDF is taken from the invoice, which carries a NEGATIVE amount. The list it is picked from holds several types at once -- ZP payments, invoices, SB statement documents -- so without this filter the largest row is usually a payment, not an invoice. Comparisons are on magnitude, so the negative sign does not matter. Takes a comma-separated list: KR is the SAP standard, and the first invoice exported from this system came back as RN, so both are here. When nothing matches, the Log names the types the file actually held.</t>
+          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
         </is>
       </c>
     </row>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D63"/>
+  <dimension ref="B2:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1187,141 +1187,152 @@
     <row r="49">
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>NO CLEARING -- internal transfer, line items exported</t>
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="C53" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTBLANK(Samples!J5:J60)</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>Files downloaded</t>
         </is>
       </c>
       <c r="C54" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>SUM(Samples!N5:N1000)</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Reached a confirming (Santander SCF) payment</t>
+          <t>Samples with no named beneficiary in the request</t>
         </is>
       </c>
       <c r="C55" s="15">
-        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="14" t="inlineStr">
         <is>
+          <t>Reached a confirming (Santander SCF) payment</t>
+        </is>
+      </c>
+      <c r="C56" s="15">
+        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C56" s="15">
+      <c r="C57" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="3" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
+          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="14" t="inlineStr">
         <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="B64" s="14" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C63" s="16" t="inlineStr">
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1329,8 +1340,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C60:D60"/>
     <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="C62:D62"/>
   </mergeCells>

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D64"/>
+  <dimension ref="B2:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1021,318 +1021,335 @@
     <row r="33">
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Invoice document type</t>
+          <t>Invoice attachment title contains</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>KR, RN</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
+          <t>An invoice document carries more than one attachment -- on this system the workflow notes sit above the document itself -- so the row whose text contains this word is the one downloaded. The titles come from the archiving system rather than from SAP, so they do not follow the SAP logon language. Nothing matching takes the last row and says so in the Log, naming every attachment it saw.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Invoice list amount column</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr"/>
+          <t>Invoice document type</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>KR, RN</t>
+        </is>
+      </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Invoice list supplier column</t>
+          <t>Invoice list amount column</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Caption of the supplier column in that same file.</t>
+          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Invoice list document column</t>
+          <t>Invoice list supplier column</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Caption of the invoice-number column in that same file.</t>
+          <t>Caption of the supplier column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Extra popup titles to allow</t>
+          <t>Invoice list document column</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+          <t>Caption of the invoice-number column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>Extra popup titles to allow</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr"/>
       <c r="D38" s="12" t="inlineStr">
         <is>
+          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr"/>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>Samples in the sheet</t>
-        </is>
-      </c>
-      <c r="C42" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Included in the next run</t>
+          <t>Samples in the sheet</t>
         </is>
       </c>
       <c r="C43" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Included in the next run</t>
         </is>
       </c>
       <c r="C44" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"No")</f>
+        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>DONE -- invoice downloaded</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C45" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
+        <f>COUNTIF(Samples!P5:P1000,"No")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
+          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>PARTIAL -- traced, no invoice file</t>
+          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>NO CLEARING -- internal transfer, line items exported</t>
+          <t>PARTIAL -- traced, no invoice file</t>
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>NO CLEARING -- internal transfer, line items exported</t>
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="C54" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTBLANK(Samples!J5:J60)</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>Files downloaded</t>
         </is>
       </c>
       <c r="C55" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>SUM(Samples!N5:N1000)</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Reached a confirming (Santander SCF) payment</t>
+          <t>Samples with no named beneficiary in the request</t>
         </is>
       </c>
       <c r="C56" s="15">
-        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="14" t="inlineStr">
         <is>
+          <t>Reached a confirming (Santander SCF) payment</t>
+        </is>
+      </c>
+      <c r="C57" s="15">
+        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C57" s="15">
+      <c r="C58" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="3" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
+          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="14" t="inlineStr">
         <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="B65" s="14" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C65" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1340,9 +1357,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C64:D64"/>
     <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C61:D61"/>
     <mergeCell ref="C62:D62"/>
   </mergeCells>
   <dataValidations count="2">

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -3006,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P61"/>
+  <dimension ref="A2:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3025,6 +3025,9 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="46" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -3037,7 +3040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Extracted from the auditor's 'Paper Samples' sheet by scripts/extract_samples.py. Columns C and D are formulas, so correcting a payment date in column E re-derives the FEBAN statement-date range automatically.</t>
+          <t>Use 'Import request' to add an auditor's sample file -- it finds the header wherever it is and asks which company code the request belongs to. Columns C and D are formulas, so correcting a payment date in column E re-derives the FEBAN statement-date range automatically.</t>
         </is>
       </c>
     </row>
@@ -3120,6 +3123,21 @@
       <c r="P4" s="17" t="inlineStr">
         <is>
           <t>Include?</t>
+        </is>
+      </c>
+      <c r="Q4" s="17" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="R4" s="17" t="inlineStr">
+        <is>
+          <t>Company code</t>
+        </is>
+      </c>
+      <c r="S4" s="17" t="inlineStr">
+        <is>
+          <t>Auditor's comment</t>
         </is>
       </c>
     </row>
@@ -3168,6 +3186,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -3218,6 +3247,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -3264,6 +3304,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -3310,6 +3361,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -3360,6 +3422,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -3410,6 +3483,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -3460,6 +3544,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -3510,6 +3605,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -3556,6 +3662,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -3602,6 +3719,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -3648,6 +3776,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -3698,6 +3837,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -3748,6 +3898,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -3798,6 +3959,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -3848,6 +4020,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -3894,6 +4077,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
@@ -3940,6 +4134,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -3986,6 +4191,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -4036,6 +4252,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -4086,6 +4313,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -4136,6 +4374,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -4186,6 +4435,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -4236,6 +4496,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -4286,6 +4557,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -4332,6 +4614,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -4378,6 +4671,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q30" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -4428,6 +4732,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -4478,6 +4793,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
@@ -4528,6 +4854,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -4578,6 +4915,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -4624,6 +4972,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -4674,6 +5033,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q36" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R36" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -4724,6 +5094,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -4774,6 +5155,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -4820,6 +5212,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
@@ -4866,6 +5269,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n">
@@ -4916,6 +5330,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
@@ -4962,6 +5387,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R42" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n">
@@ -5008,6 +5444,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -5054,6 +5501,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R44" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
@@ -5100,6 +5558,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R45" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
@@ -5150,6 +5619,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R46" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
@@ -5200,6 +5680,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R47" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
@@ -5246,6 +5737,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q48" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R48" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
@@ -5296,6 +5798,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q49" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R49" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
@@ -5342,6 +5855,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q50" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R50" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
@@ -5388,6 +5912,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q51" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
@@ -5434,6 +5969,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q52" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R52" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
@@ -5484,6 +6030,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q53" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
@@ -5534,6 +6091,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q54" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R54" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
@@ -5580,6 +6148,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q55" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R55" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
@@ -5626,6 +6205,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q56" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R56" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
@@ -5672,6 +6262,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q57" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R57" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
@@ -5718,6 +6319,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q58" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R58" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -5768,6 +6380,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q59" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R59" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
@@ -5818,6 +6441,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q60" s="10" t="inlineStr">
+        <is>
+          <t>Paper Samples</t>
+        </is>
+      </c>
+      <c r="R60" s="10" t="inlineStr">
+        <is>
+          <t>GBKM</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="E61" s="30" t="inlineStr">

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D65"/>
+  <dimension ref="B2:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1215,141 +1215,152 @@
     <row r="51">
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>NO VENDOR PAYMENTS -- treasury/FX settlement</t>
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO VENDOR PAYMENTS")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C54" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="C55" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTBLANK(Samples!J5:J60)</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>Files downloaded</t>
         </is>
       </c>
       <c r="C56" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>SUM(Samples!N5:N1000)</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Reached a confirming (Santander SCF) payment</t>
+          <t>Samples with no named beneficiary in the request</t>
         </is>
       </c>
       <c r="C57" s="15">
-        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="14" t="inlineStr">
         <is>
+          <t>Reached a confirming (Santander SCF) payment</t>
+        </is>
+      </c>
+      <c r="C58" s="15">
+        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C58" s="15">
+      <c r="C59" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="3" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
+          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="14" t="inlineStr">
         <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="B66" s="14" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C66" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1360,7 +1371,7 @@
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="C64:D64"/>
     <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C66:D66"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -3017,7 +3017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:S61"/>
+  <dimension ref="A2:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3039,6 +3039,8 @@
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="46" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -3149,6 +3151,16 @@
       <c r="S4" s="17" t="inlineStr">
         <is>
           <t>Auditor's comment</t>
+        </is>
+      </c>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t>Start document</t>
+        </is>
+      </c>
+      <c r="U4" s="17" t="inlineStr">
+        <is>
+          <t>Start at</t>
         </is>
       </c>
     </row>
@@ -3208,6 +3220,8 @@
         </is>
       </c>
       <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -3269,6 +3283,8 @@
         </is>
       </c>
       <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -3326,6 +3342,8 @@
         </is>
       </c>
       <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -3383,6 +3401,8 @@
         </is>
       </c>
       <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -3444,6 +3464,8 @@
         </is>
       </c>
       <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -3505,6 +3527,8 @@
         </is>
       </c>
       <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -3566,6 +3590,8 @@
         </is>
       </c>
       <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -3627,6 +3653,8 @@
         </is>
       </c>
       <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -3684,6 +3712,8 @@
         </is>
       </c>
       <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -3741,6 +3771,8 @@
         </is>
       </c>
       <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -3798,6 +3830,8 @@
         </is>
       </c>
       <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -3859,6 +3893,8 @@
         </is>
       </c>
       <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -3920,6 +3956,8 @@
         </is>
       </c>
       <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -3981,6 +4019,8 @@
         </is>
       </c>
       <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -4042,6 +4082,8 @@
         </is>
       </c>
       <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -4099,6 +4141,8 @@
         </is>
       </c>
       <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
@@ -4156,6 +4200,8 @@
         </is>
       </c>
       <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -4213,6 +4259,8 @@
         </is>
       </c>
       <c r="S22" s="10" t="n"/>
+      <c r="T22" s="10" t="n"/>
+      <c r="U22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -4274,6 +4322,8 @@
         </is>
       </c>
       <c r="S23" s="10" t="n"/>
+      <c r="T23" s="10" t="n"/>
+      <c r="U23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -4335,6 +4385,8 @@
         </is>
       </c>
       <c r="S24" s="10" t="n"/>
+      <c r="T24" s="10" t="n"/>
+      <c r="U24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -4396,6 +4448,8 @@
         </is>
       </c>
       <c r="S25" s="10" t="n"/>
+      <c r="T25" s="10" t="n"/>
+      <c r="U25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -4457,6 +4511,8 @@
         </is>
       </c>
       <c r="S26" s="10" t="n"/>
+      <c r="T26" s="10" t="n"/>
+      <c r="U26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -4518,6 +4574,8 @@
         </is>
       </c>
       <c r="S27" s="10" t="n"/>
+      <c r="T27" s="10" t="n"/>
+      <c r="U27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -4579,6 +4637,8 @@
         </is>
       </c>
       <c r="S28" s="10" t="n"/>
+      <c r="T28" s="10" t="n"/>
+      <c r="U28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -4636,6 +4696,8 @@
         </is>
       </c>
       <c r="S29" s="10" t="n"/>
+      <c r="T29" s="10" t="n"/>
+      <c r="U29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -4693,6 +4755,8 @@
         </is>
       </c>
       <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
+      <c r="U30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -4754,6 +4818,8 @@
         </is>
       </c>
       <c r="S31" s="10" t="n"/>
+      <c r="T31" s="10" t="n"/>
+      <c r="U31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -4815,6 +4881,8 @@
         </is>
       </c>
       <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
@@ -4876,6 +4944,8 @@
         </is>
       </c>
       <c r="S33" s="10" t="n"/>
+      <c r="T33" s="10" t="n"/>
+      <c r="U33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -4937,6 +5007,8 @@
         </is>
       </c>
       <c r="S34" s="10" t="n"/>
+      <c r="T34" s="10" t="n"/>
+      <c r="U34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -4994,6 +5066,8 @@
         </is>
       </c>
       <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -5055,6 +5129,8 @@
         </is>
       </c>
       <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
+      <c r="U36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -5116,6 +5192,8 @@
         </is>
       </c>
       <c r="S37" s="10" t="n"/>
+      <c r="T37" s="10" t="n"/>
+      <c r="U37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -5177,6 +5255,8 @@
         </is>
       </c>
       <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -5234,6 +5314,8 @@
         </is>
       </c>
       <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
@@ -5291,6 +5373,8 @@
         </is>
       </c>
       <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n">
@@ -5352,6 +5436,8 @@
         </is>
       </c>
       <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
@@ -5409,6 +5495,8 @@
         </is>
       </c>
       <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
+      <c r="U42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n">
@@ -5466,6 +5554,8 @@
         </is>
       </c>
       <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="n"/>
+      <c r="U43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -5523,6 +5613,8 @@
         </is>
       </c>
       <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
@@ -5580,6 +5672,8 @@
         </is>
       </c>
       <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
@@ -5641,6 +5735,8 @@
         </is>
       </c>
       <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
@@ -5702,6 +5798,8 @@
         </is>
       </c>
       <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
@@ -5759,6 +5857,8 @@
         </is>
       </c>
       <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
@@ -5820,6 +5920,8 @@
         </is>
       </c>
       <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
@@ -5877,6 +5979,8 @@
         </is>
       </c>
       <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
@@ -5934,6 +6038,8 @@
         </is>
       </c>
       <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
@@ -5991,6 +6097,8 @@
         </is>
       </c>
       <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
@@ -6052,6 +6160,8 @@
         </is>
       </c>
       <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
@@ -6113,6 +6223,8 @@
         </is>
       </c>
       <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
@@ -6170,6 +6282,8 @@
         </is>
       </c>
       <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
@@ -6227,6 +6341,8 @@
         </is>
       </c>
       <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
@@ -6284,6 +6400,8 @@
         </is>
       </c>
       <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
@@ -6341,6 +6459,8 @@
         </is>
       </c>
       <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -6402,6 +6522,8 @@
         </is>
       </c>
       <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
@@ -6463,6 +6585,8 @@
         </is>
       </c>
       <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="E61" s="30" t="inlineStr">

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D66"/>
+  <dimension ref="B2:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -905,462 +905,477 @@
     <row r="25">
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>SAP date format</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>DDMMYYYY</t>
-        </is>
+          <t>Max rows for a settlement</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>How dates are typed into SAP. DDMMYYYY = 01092025, which is what recordings/Audit.vbs used and therefore what is known to work here. Also supported: DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
+          <t>A clearing document with no vendor payments and no more than this many bookkeeping rows is a treasury, tax or FX settlement -- there is no invoice behind it. Above it, the run assumes the document-type column was misread. A real payment run here has held between 34 and 656 payments, never a handful.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Payment document type</t>
+          <t>SAP date format</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>ZP</t>
+          <t>DDMMYYYY</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Only documents of these types are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document. Takes a comma-separated list -- 'ZP, ZV, KZ' -- for batches paid outside the normal payment run. When nothing matches, the Log names the types the file actually held.</t>
+          <t>How dates are typed into SAP. DDMMYYYY = 01092025, which is what recordings/Audit.vbs used and therefore what is known to work here. Also supported: DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Clearing line posting key</t>
+          <t>Payment document type</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>ZP</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Step 4 opens the first line-item row with this posting key that also carries a clearing document. Blank means 'any row with a clearing document'.</t>
+          <t>Only documents of these types are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document. Takes a comma-separated list -- 'ZP, ZV, KZ' -- for batches paid outside the normal payment run. When nothing matches, the Log names the types the file actually held.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Payment usage document column</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr"/>
+          <t>Clearing line posting key</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-number column in the exported Payment Usage list, if the macro cannot find it. Open the first exported file and copy the heading exactly.</t>
+          <t>Step 4 opens the first line-item row with this posting key that also carries a clearing document. Blank means 'any row with a clearing document'.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Payment usage type column</t>
+          <t>Payment usage document column</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr"/>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-type column in that same file. Without it every document is taken rather than only the ZP ones, and the Log says so.</t>
+          <t>Caption of the document-number column in the exported Payment Usage list, if the macro cannot find it. Open the first exported file and copy the heading exactly.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>ZP list amount column</t>
+          <t>Payment usage type column</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr"/>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Caption of the amount column in the exported FBL1N payment list. Leave blank -- the macro tries the caption, then the SAP technical name, then works it out from what the column contains, which is language-independent. Only fill this in if the Log says it picked the wrong one.</t>
+          <t>Caption of the document-type column in that same file. Without it every document is taken rather than only the ZP ones, and the Log says so.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>ZP list vendor column</t>
+          <t>ZP list amount column</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr"/>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Caption of the vendor-name column in that same file. Same rules.</t>
+          <t>Caption of the amount column in the exported FBL1N payment list. Leave blank -- the macro tries the caption, then the SAP technical name, then works it out from what the column contains, which is language-independent. Only fill this in if the Log says it picked the wrong one.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>ZP list document column</t>
+          <t>ZP list vendor column</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr"/>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-number column in that same file. Same rules.</t>
+          <t>Caption of the vendor-name column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Invoice attachment title contains</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
+          <t>ZP list document column</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr"/>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>An invoice document carries more than one attachment -- on this system the workflow notes sit above the document itself -- so the row whose text contains this word is the one downloaded. The titles come from the archiving system rather than from SAP, so they do not follow the SAP logon language. Nothing matching takes the last row and says so in the Log, naming every attachment it saw.</t>
+          <t>Caption of the document-number column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Invoice document type</t>
+          <t>Invoice attachment title contains</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>KR, RN</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
+          <t>An invoice document carries more than one attachment -- on this system the workflow notes sit above the document itself -- so the row whose text contains this word is the one downloaded. The titles come from the archiving system rather than from SAP, so they do not follow the SAP logon language. Nothing matching takes the last row and says so in the Log, naming every attachment it saw.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Invoice list amount column</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr"/>
+          <t>Invoice document type</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>KR, RN</t>
+        </is>
+      </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Invoice list supplier column</t>
+          <t>Invoice list amount column</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Caption of the supplier column in that same file.</t>
+          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Invoice list document column</t>
+          <t>Invoice list supplier column</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Caption of the invoice-number column in that same file.</t>
+          <t>Caption of the supplier column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Extra popup titles to allow</t>
+          <t>Invoice list document column</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr"/>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+          <t>Caption of the invoice-number column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>Extra popup titles to allow</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr"/>
       <c r="D39" s="12" t="inlineStr">
         <is>
+          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr"/>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>Samples in the sheet</t>
-        </is>
-      </c>
-      <c r="C43" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Included in the next run</t>
+          <t>Samples in the sheet</t>
         </is>
       </c>
       <c r="C44" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Included in the next run</t>
         </is>
       </c>
       <c r="C45" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"No")</f>
+        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>DONE -- invoice downloaded</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
+        <f>COUNTIF(Samples!P5:P1000,"No")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
+          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>PARTIAL -- traced, no invoice file</t>
+          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>NO CLEARING -- internal transfer, line items exported</t>
+          <t>PARTIAL -- traced, no invoice file</t>
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>NO VENDOR PAYMENTS -- treasury/FX settlement</t>
+          <t>NO CLEARING -- internal transfer, line items exported</t>
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NO VENDOR PAYMENTS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>NO VENDOR PAYMENTS -- treasury/FX settlement</t>
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO VENDOR PAYMENTS")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C54" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C55" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="C56" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTBLANK(Samples!J5:J60)</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>Files downloaded</t>
         </is>
       </c>
       <c r="C57" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>SUM(Samples!N5:N1000)</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Reached a confirming (Santander SCF) payment</t>
+          <t>Samples with no named beneficiary in the request</t>
         </is>
       </c>
       <c r="C58" s="15">
-        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="14" t="inlineStr">
         <is>
+          <t>Reached a confirming (Santander SCF) payment</t>
+        </is>
+      </c>
+      <c r="C59" s="15">
+        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C59" s="15">
+      <c r="C60" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="3" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
+          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="14" t="inlineStr">
         <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="B67" s="14" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="C67" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1368,10 +1383,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C64:D64"/>
     <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3017,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:U61"/>
+  <dimension ref="A2:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3041,6 +3056,7 @@
     <col width="46" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -3161,6 +3177,11 @@
       <c r="U4" s="17" t="inlineStr">
         <is>
           <t>Start at</t>
+        </is>
+      </c>
+      <c r="V4" s="17" t="inlineStr">
+        <is>
+          <t>Auditor's ZP</t>
         </is>
       </c>
     </row>
@@ -3222,6 +3243,7 @@
       <c r="S5" s="10" t="n"/>
       <c r="T5" s="10" t="n"/>
       <c r="U5" s="10" t="n"/>
+      <c r="V5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -3285,6 +3307,7 @@
       <c r="S6" s="10" t="n"/>
       <c r="T6" s="10" t="n"/>
       <c r="U6" s="10" t="n"/>
+      <c r="V6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -3344,6 +3367,7 @@
       <c r="S7" s="10" t="n"/>
       <c r="T7" s="10" t="n"/>
       <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -3403,6 +3427,7 @@
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="10" t="n"/>
       <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -3466,6 +3491,7 @@
       <c r="S9" s="10" t="n"/>
       <c r="T9" s="10" t="n"/>
       <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -3529,6 +3555,7 @@
       <c r="S10" s="10" t="n"/>
       <c r="T10" s="10" t="n"/>
       <c r="U10" s="10" t="n"/>
+      <c r="V10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -3592,6 +3619,7 @@
       <c r="S11" s="10" t="n"/>
       <c r="T11" s="10" t="n"/>
       <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -3655,6 +3683,7 @@
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="10" t="n"/>
       <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -3714,6 +3743,7 @@
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
       <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -3773,6 +3803,7 @@
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="10" t="n"/>
       <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -3832,6 +3863,7 @@
       <c r="S15" s="10" t="n"/>
       <c r="T15" s="10" t="n"/>
       <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -3895,6 +3927,7 @@
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="10" t="n"/>
       <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -3958,6 +3991,7 @@
       <c r="S17" s="10" t="n"/>
       <c r="T17" s="10" t="n"/>
       <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -4021,6 +4055,7 @@
       <c r="S18" s="10" t="n"/>
       <c r="T18" s="10" t="n"/>
       <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -4084,6 +4119,7 @@
       <c r="S19" s="10" t="n"/>
       <c r="T19" s="10" t="n"/>
       <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -4143,6 +4179,7 @@
       <c r="S20" s="10" t="n"/>
       <c r="T20" s="10" t="n"/>
       <c r="U20" s="10" t="n"/>
+      <c r="V20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
@@ -4202,6 +4239,7 @@
       <c r="S21" s="10" t="n"/>
       <c r="T21" s="10" t="n"/>
       <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -4261,6 +4299,7 @@
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="10" t="n"/>
       <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -4324,6 +4363,7 @@
       <c r="S23" s="10" t="n"/>
       <c r="T23" s="10" t="n"/>
       <c r="U23" s="10" t="n"/>
+      <c r="V23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -4387,6 +4427,7 @@
       <c r="S24" s="10" t="n"/>
       <c r="T24" s="10" t="n"/>
       <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -4450,6 +4491,7 @@
       <c r="S25" s="10" t="n"/>
       <c r="T25" s="10" t="n"/>
       <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -4513,6 +4555,7 @@
       <c r="S26" s="10" t="n"/>
       <c r="T26" s="10" t="n"/>
       <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -4576,6 +4619,7 @@
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
+      <c r="V27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -4639,6 +4683,7 @@
       <c r="S28" s="10" t="n"/>
       <c r="T28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
+      <c r="V28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -4698,6 +4743,7 @@
       <c r="S29" s="10" t="n"/>
       <c r="T29" s="10" t="n"/>
       <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -4757,6 +4803,7 @@
       <c r="S30" s="10" t="n"/>
       <c r="T30" s="10" t="n"/>
       <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -4820,6 +4867,7 @@
       <c r="S31" s="10" t="n"/>
       <c r="T31" s="10" t="n"/>
       <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -4883,6 +4931,7 @@
       <c r="S32" s="10" t="n"/>
       <c r="T32" s="10" t="n"/>
       <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
@@ -4946,6 +4995,7 @@
       <c r="S33" s="10" t="n"/>
       <c r="T33" s="10" t="n"/>
       <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -5009,6 +5059,7 @@
       <c r="S34" s="10" t="n"/>
       <c r="T34" s="10" t="n"/>
       <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -5068,6 +5119,7 @@
       <c r="S35" s="10" t="n"/>
       <c r="T35" s="10" t="n"/>
       <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -5131,6 +5183,7 @@
       <c r="S36" s="10" t="n"/>
       <c r="T36" s="10" t="n"/>
       <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -5194,6 +5247,7 @@
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
       <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -5257,6 +5311,7 @@
       <c r="S38" s="10" t="n"/>
       <c r="T38" s="10" t="n"/>
       <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -5316,6 +5371,7 @@
       <c r="S39" s="10" t="n"/>
       <c r="T39" s="10" t="n"/>
       <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
@@ -5375,6 +5431,7 @@
       <c r="S40" s="10" t="n"/>
       <c r="T40" s="10" t="n"/>
       <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n">
@@ -5438,6 +5495,7 @@
       <c r="S41" s="10" t="n"/>
       <c r="T41" s="10" t="n"/>
       <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
@@ -5497,6 +5555,7 @@
       <c r="S42" s="10" t="n"/>
       <c r="T42" s="10" t="n"/>
       <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n">
@@ -5556,6 +5615,7 @@
       <c r="S43" s="10" t="n"/>
       <c r="T43" s="10" t="n"/>
       <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -5615,6 +5675,7 @@
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
       <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
@@ -5674,6 +5735,7 @@
       <c r="S45" s="10" t="n"/>
       <c r="T45" s="10" t="n"/>
       <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
@@ -5737,6 +5799,7 @@
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="n"/>
       <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
@@ -5800,6 +5863,7 @@
       <c r="S47" s="10" t="n"/>
       <c r="T47" s="10" t="n"/>
       <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
@@ -5859,6 +5923,7 @@
       <c r="S48" s="10" t="n"/>
       <c r="T48" s="10" t="n"/>
       <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
@@ -5922,6 +5987,7 @@
       <c r="S49" s="10" t="n"/>
       <c r="T49" s="10" t="n"/>
       <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
@@ -5981,6 +6047,7 @@
       <c r="S50" s="10" t="n"/>
       <c r="T50" s="10" t="n"/>
       <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
@@ -6040,6 +6107,7 @@
       <c r="S51" s="10" t="n"/>
       <c r="T51" s="10" t="n"/>
       <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
@@ -6099,6 +6167,7 @@
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
@@ -6162,6 +6231,7 @@
       <c r="S53" s="10" t="n"/>
       <c r="T53" s="10" t="n"/>
       <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
@@ -6225,6 +6295,7 @@
       <c r="S54" s="10" t="n"/>
       <c r="T54" s="10" t="n"/>
       <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
@@ -6284,6 +6355,7 @@
       <c r="S55" s="10" t="n"/>
       <c r="T55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
@@ -6343,6 +6415,7 @@
       <c r="S56" s="10" t="n"/>
       <c r="T56" s="10" t="n"/>
       <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
@@ -6402,6 +6475,7 @@
       <c r="S57" s="10" t="n"/>
       <c r="T57" s="10" t="n"/>
       <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
@@ -6461,6 +6535,7 @@
       <c r="S58" s="10" t="n"/>
       <c r="T58" s="10" t="n"/>
       <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -6524,6 +6599,7 @@
       <c r="S59" s="10" t="n"/>
       <c r="T59" s="10" t="n"/>
       <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
@@ -6587,6 +6663,7 @@
       <c r="S60" s="10" t="n"/>
       <c r="T60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="E61" s="30" t="inlineStr">

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D67"/>
+  <dimension ref="B2:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -905,477 +905,494 @@
     <row r="25">
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Max rows for a settlement</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>8</v>
+          <t>Payment usage menu text</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Payment usage</t>
+        </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>A clearing document with no vendor payments and no more than this many bookkeeping rows is a treasury, tax or FX settlement -- there is no invoice behind it. Above it, the run assumes the document-type column was misread. A real payment run here has held between 34 and 656 payments, never a handful.</t>
+          <t>What Environment &gt; Payment Usage is CALLED on your system. The macro finds the command by this name and only falls back to the recorded menu position when the name is not on the menu bar -- a position that exists on the wrong screen is not the right command, and selecting one blind sent a run into FS03. Translate it if your SAP is not in English.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>SAP date format</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>DDMMYYYY</t>
-        </is>
+          <t>Max rows for a settlement</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>How dates are typed into SAP. DDMMYYYY = 01092025, which is what recordings/Audit.vbs used and therefore what is known to work here. Also supported: DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
+          <t>A clearing document with no vendor payments and no more than this many bookkeeping rows is a treasury, tax or FX settlement -- there is no invoice behind it. Above it, the run assumes the document-type column was misread. A real payment run here has held between 34 and 656 payments, never a handful.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Payment document type</t>
+          <t>SAP date format</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>ZP</t>
+          <t>DDMMYYYY</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Only documents of these types are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document. Takes a comma-separated list -- 'ZP, ZV, KZ' -- for batches paid outside the normal payment run. When nothing matches, the Log names the types the file actually held.</t>
+          <t>How dates are typed into SAP. DDMMYYYY = 01092025, which is what recordings/Audit.vbs used and therefore what is known to work here. Also supported: DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Clearing line posting key</t>
+          <t>Payment document type</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>ZP</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Step 4 opens the first line-item row with this posting key that also carries a clearing document. Blank means 'any row with a clearing document'.</t>
+          <t>Only documents of these types are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document. Takes a comma-separated list -- 'ZP, ZV, KZ' -- for batches paid outside the normal payment run. When nothing matches, the Log names the types the file actually held.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Payment usage document column</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr"/>
+          <t>Clearing line posting key</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-number column in the exported Payment Usage list, if the macro cannot find it. Open the first exported file and copy the heading exactly.</t>
+          <t>Step 4 opens the first line-item row with this posting key that also carries a clearing document. Blank means 'any row with a clearing document'.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Payment usage type column</t>
+          <t>Payment usage document column</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr"/>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-type column in that same file. Without it every document is taken rather than only the ZP ones, and the Log says so.</t>
+          <t>Caption of the document-number column in the exported Payment Usage list, if the macro cannot find it. Open the first exported file and copy the heading exactly.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>ZP list amount column</t>
+          <t>Payment usage type column</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr"/>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Caption of the amount column in the exported FBL1N payment list. Leave blank -- the macro tries the caption, then the SAP technical name, then works it out from what the column contains, which is language-independent. Only fill this in if the Log says it picked the wrong one.</t>
+          <t>Caption of the document-type column in that same file. Without it every document is taken rather than only the ZP ones, and the Log says so.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>ZP list vendor column</t>
+          <t>ZP list amount column</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr"/>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Caption of the vendor-name column in that same file. Same rules.</t>
+          <t>Caption of the amount column in the exported FBL1N payment list. Leave blank -- the macro tries the caption, then the SAP technical name, then works it out from what the column contains, which is language-independent. Only fill this in if the Log says it picked the wrong one.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>ZP list document column</t>
+          <t>ZP list vendor column</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr"/>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-number column in that same file. Same rules.</t>
+          <t>Caption of the vendor-name column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Invoice attachment title contains</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
+          <t>ZP list document column</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>An invoice document carries more than one attachment -- on this system the workflow notes sit above the document itself -- so the row whose text contains this word is the one downloaded. The titles come from the archiving system rather than from SAP, so they do not follow the SAP logon language. Nothing matching takes the last row and says so in the Log, naming every attachment it saw.</t>
+          <t>Caption of the document-number column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Invoice document type</t>
+          <t>Invoice attachment title contains</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>KR, RN</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
+          <t>An invoice document carries more than one attachment -- on this system the workflow notes sit above the document itself -- so the row whose text contains this word is the one downloaded. The titles come from the archiving system rather than from SAP, so they do not follow the SAP logon language. Nothing matching takes the last row and says so in the Log, naming every attachment it saw.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Invoice list amount column</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr"/>
+          <t>Invoice document type</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>KR, RN</t>
+        </is>
+      </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Invoice list supplier column</t>
+          <t>Invoice list amount column</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Caption of the supplier column in that same file.</t>
+          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Invoice list document column</t>
+          <t>Invoice list supplier column</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr"/>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Caption of the invoice-number column in that same file.</t>
+          <t>Caption of the supplier column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Extra popup titles to allow</t>
+          <t>Invoice list document column</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr"/>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+          <t>Caption of the invoice-number column in that same file.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>Extra popup titles to allow</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr"/>
       <c r="D40" s="12" t="inlineStr">
         <is>
+          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr"/>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>Samples in the sheet</t>
-        </is>
-      </c>
-      <c r="C44" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Included in the next run</t>
+          <t>Samples in the sheet</t>
         </is>
       </c>
       <c r="C45" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Included in the next run</t>
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"No")</f>
+        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>DONE -- invoice downloaded</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
+        <f>COUNTIF(Samples!P5:P1000,"No")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
+          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>PARTIAL -- traced, no invoice file</t>
+          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>NO CLEARING -- internal transfer, line items exported</t>
+          <t>PARTIAL -- traced, no invoice file</t>
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>NO VENDOR PAYMENTS -- treasury/FX settlement</t>
+          <t>NO CLEARING -- internal transfer, line items exported</t>
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NO VENDOR PAYMENTS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>NO VENDOR PAYMENTS -- treasury/FX settlement</t>
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO VENDOR PAYMENTS")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C54" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C55" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C56" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="C57" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTBLANK(Samples!J5:J60)</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>Files downloaded</t>
         </is>
       </c>
       <c r="C58" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>SUM(Samples!N5:N1000)</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Reached a confirming (Santander SCF) payment</t>
+          <t>Samples with no named beneficiary in the request</t>
         </is>
       </c>
       <c r="C59" s="15">
-        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="14" t="inlineStr">
         <is>
+          <t>Reached a confirming (Santander SCF) payment</t>
+        </is>
+      </c>
+      <c r="C60" s="15">
+        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C60" s="15">
+      <c r="C61" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="3" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
+          <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+          <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="14" t="inlineStr">
         <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="B68" s="14" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C67" s="16" t="inlineStr">
+      <c r="C68" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1383,10 +1400,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C67:D67"/>
     <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C64:D64"/>
     <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/sap-audit-macro/FEBAN_Audit_Control.xlsx
+++ b/sap-audit-macro/FEBAN_Audit_Control.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D68"/>
+  <dimension ref="B2:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -905,494 +905,562 @@
     <row r="25">
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Payment usage menu text</t>
+          <t>Confirming document type</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Payment usage</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>What Environment &gt; Payment Usage is CALLED on your system. The macro finds the command by this name and only falls back to the recorded menu position when the name is not on the menu bar -- a position that exists on the wrong screen is not the right command, and selecting one blind sent a run into FS03. Translate it if your SAP is not in English.</t>
+          <t>Document type the finance provider's side of a confirming batch is posted under. When a Payment Usage list holds these and no payment documents, the run follows their Reference to the real suppliers instead of calling it a treasury settlement.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Max rows for a settlement</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>8</v>
+          <t>Confirming reference column</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>A clearing document with no vendor payments and no more than this many bookkeeping rows is a treasury, tax or FX settlement -- there is no invoice behind it. Above it, the run assumes the document-type column was misread. A real payment run here has held between 34 and 656 payments, never a handful.</t>
+          <t>Heading of the column in the Payment Usage export carrying that reference. Leading zeros are kept -- it is a character field, and 0000243422 is not 243422.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>SAP date format</t>
+          <t>Confirming reference caption</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>DDMMYYYY</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>How dates are typed into SAP. DDMMYYYY = 01092025, which is what recordings/Audit.vbs used and therefore what is known to work here. Also supported: DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
+          <t>What the Reference field is LABELLED in FBL1N's dynamic selections. The run reads the field's technical name off that label, because the %%DYNnnn number depends on which dynamic selections are active and is not a property of the field. Translate if needed.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Payment document type</t>
+          <t>Confirming company code pattern</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>ZP</t>
+          <t>GB*</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Only documents of these types are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document. Takes a comma-separated list -- 'ZP, ZV, KZ' -- for batches paid outside the normal payment run. When nothing matches, the Log names the types the file actually held.</t>
+          <t>Company codes to search for the supplier invoices. NOT the code that made the payment: a confirming batch is paid by one company and the invoices sit in the operating ones. A pattern, so one search covers them all.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Clearing line posting key</t>
+          <t>Payment usage menu text</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Payment usage</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Step 4 opens the first line-item row with this posting key that also carries a clearing document. Blank means 'any row with a clearing document'.</t>
+          <t>What Environment &gt; Payment Usage is CALLED on your system. The macro finds the command by this name and only falls back to the recorded menu position when the name is not on the menu bar -- a position that exists on the wrong screen is not the right command, and selecting one blind sent a run into FS03. Translate it if your SAP is not in English.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Payment usage document column</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr"/>
+          <t>Max rows for a settlement</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-number column in the exported Payment Usage list, if the macro cannot find it. Open the first exported file and copy the heading exactly.</t>
+          <t>A clearing document with no vendor payments and no more than this many bookkeeping rows is a treasury, tax or FX settlement -- there is no invoice behind it. Above it, the run assumes the document-type column was misread. A real payment run here has held between 34 and 656 payments, never a handful.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Payment usage type column</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr"/>
+          <t>SAP date format</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>DDMMYYYY</t>
+        </is>
+      </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-type column in that same file. Without it every document is taken rather than only the ZP ones, and the Log says so.</t>
+          <t>How dates are typed into SAP. DDMMYYYY = 01092025, which is what recordings/Audit.vbs used and therefore what is known to work here. Also supported: DMY = 31.12.2025, DMY/ = 31/12/2025, MDY = 12/31/2025, YMD = 2025-12-31. Get this wrong and FEBAN silently searches the wrong period.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>ZP list amount column</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr"/>
+          <t>Payment document type</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Caption of the amount column in the exported FBL1N payment list. Leave blank -- the macro tries the caption, then the SAP technical name, then works it out from what the column contains, which is language-independent. Only fill this in if the Log says it picked the wrong one.</t>
+          <t>Only documents of these types are taken from the Payment Usage list and fed to FBL1N. ZP is the SAP standard for a payment document. Takes a comma-separated list -- 'ZP, ZV, KZ' -- for batches paid outside the normal payment run. When nothing matches, the Log names the types the file actually held.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>ZP list vendor column</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr"/>
+          <t>Clearing line posting key</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Caption of the vendor-name column in that same file. Same rules.</t>
+          <t>Step 4 opens the first line-item row with this posting key that also carries a clearing document. Blank means 'any row with a clearing document'.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>ZP list document column</t>
+          <t>Payment usage document column</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Caption of the document-number column in that same file. Same rules.</t>
+          <t>Caption of the document-number column in the exported Payment Usage list, if the macro cannot find it. Open the first exported file and copy the heading exactly.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Invoice attachment title contains</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
+          <t>Payment usage type column</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>An invoice document carries more than one attachment -- on this system the workflow notes sit above the document itself -- so the row whose text contains this word is the one downloaded. The titles come from the archiving system rather than from SAP, so they do not follow the SAP logon language. Nothing matching takes the last row and says so in the Log, naming every attachment it saw.</t>
+          <t>Caption of the document-type column in that same file. Without it every document is taken rather than only the ZP ones, and the Log says so.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Invoice document type</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>KR, RN</t>
-        </is>
-      </c>
+          <t>ZP list amount column</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
+          <t>Caption of the amount column in the exported FBL1N payment list. Leave blank -- the macro tries the caption, then the SAP technical name, then works it out from what the column contains, which is language-independent. Only fill this in if the Log says it picked the wrong one.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Invoice list amount column</t>
+          <t>ZP list vendor column</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+          <t>Caption of the vendor-name column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Invoice list supplier column</t>
+          <t>ZP list document column</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr"/>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Caption of the supplier column in that same file.</t>
+          <t>Caption of the document-number column in that same file. Same rules.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Invoice list document column</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr"/>
+          <t>Invoice attachment title contains</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Caption of the invoice-number column in that same file.</t>
+          <t>An invoice document carries more than one attachment -- on this system the workflow notes sit above the document itself -- so the row whose text contains this word is the one downloaded. The titles come from the archiving system rather than from SAP, so they do not follow the SAP logon language. Nothing matching takes the last row and says so in the Log, naming every attachment it saw.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Extra popup titles to allow</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr"/>
+          <t>Invoice document type</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>KR, RN</t>
+        </is>
+      </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+          <t>CROSS-CHECK ONLY -- this no longer decides anything. The invoice is picked by SIGN: in a vendor line-item list the payment is a debit and the invoice it settles is a credit, so the invoice is the negative row and the biggest invoice is the most negative one. That holds whatever the type is called in this company code, which matters because it is RN here and KR on the SAP standard. If the row picked is not one of the types listed, the Log says so and takes it anyway. Blank to switch the cross-check off.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Operator name</t>
+          <t>Invoice list amount column</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
+          <t>Santander SCF route only. Caption of the amount column in the exported list of invoices behind an SCF payment. Blank falls back to a built-in list of captions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Invoice list supplier column</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Caption of the supplier column in that same file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Invoice list document column</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Caption of the invoice-number column in that same file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Extra popup titles to allow</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Pipe-separated. The run stops on any modal popup it does not recognise rather than pressing Enter through it. The save dialog and the attachment list are identified by their contents, so language does not matter for those -- add a title here only if your system shows a popup the run does not expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Operator name</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr"/>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
           <t>Written into the log for the audit trail.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="3" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Progress (formulas over the Samples sheet)</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>Samples in the sheet</t>
-        </is>
-      </c>
-      <c r="C45" s="15">
-        <f>COUNTA(Samples!A5:A1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>Included in the next run</t>
-        </is>
-      </c>
-      <c r="C46" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="C47" s="15">
-        <f>COUNTIF(Samples!P5:P1000,"No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>DONE -- invoice downloaded</t>
-        </is>
-      </c>
-      <c r="C48" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
-        <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
+          <t>Samples in the sheet</t>
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
+        <f>COUNTA(Samples!A5:A1000)</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
+          <t>Included in the next run</t>
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
+        <f>COUNTIF(Samples!P5:P1000,"Yes")+COUNTBLANK(Samples!P5:P60)</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>PARTIAL -- traced, no invoice file</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
+        <f>COUNTIF(Samples!P5:P1000,"No")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>NO CLEARING -- internal transfer, line items exported</t>
+          <t>DONE -- invoice downloaded</t>
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
+        <f>COUNTIF(Samples!J5:J1000,"DONE")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>NO VENDOR PAYMENTS -- treasury/FX settlement</t>
+          <t>BLOCKED_FBL1N -- steps 8-9 not mapped yet</t>
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NO VENDOR PAYMENTS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_FBL1N")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>NOT FOUND -- no matching statement line</t>
+          <t>BLOCKED_INVOICE -- reached the payment, no PDF</t>
         </is>
       </c>
       <c r="C54" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
+        <f>COUNTIF(Samples!J5:J1000,"BLOCKED_INVOICE")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>AMBIGUOUS -- more than one line matched</t>
+          <t>PARTIAL -- traced, no invoice file</t>
         </is>
       </c>
       <c r="C55" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
+        <f>COUNTIF(Samples!J5:J1000,"PARTIAL")</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>NO CLEARING -- internal transfer, line items exported</t>
         </is>
       </c>
       <c r="C56" s="15">
-        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO CLEARING")</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>NO VENDOR PAYMENTS -- treasury/FX settlement</t>
         </is>
       </c>
       <c r="C57" s="15">
-        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <f>COUNTIF(Samples!J5:J1000,"NO VENDOR PAYMENTS")</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Files downloaded</t>
+          <t>NOT FOUND -- no matching statement line</t>
         </is>
       </c>
       <c r="C58" s="15">
-        <f>SUM(Samples!N5:N1000)</f>
+        <f>COUNTIF(Samples!J5:J1000,"NOT FOUND")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Samples with no named beneficiary in the request</t>
+          <t>AMBIGUOUS -- more than one line matched</t>
         </is>
       </c>
       <c r="C59" s="15">
-        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <f>COUNTIF(Samples!J5:J1000,"AMBIGUOUS")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Reached a confirming (Santander SCF) payment</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C60" s="15">
-        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <f>COUNTIF(Samples!J5:J1000,"ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="14" t="inlineStr">
         <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C61" s="15">
+        <f>COUNTBLANK(Samples!J5:J60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Files downloaded</t>
+        </is>
+      </c>
+      <c r="C62" s="15">
+        <f>SUM(Samples!N5:N1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Samples with no named beneficiary in the request</t>
+        </is>
+      </c>
+      <c r="C63" s="15">
+        <f>COUNTIF(Samples!I5:I1000,"*no_named_beneficiary*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Reached a confirming (Santander SCF) payment</t>
+        </is>
+      </c>
+      <c r="C64" s="15">
+        <f>COUNTIF(Samples!O5:O1000,"*confirming party*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="14" t="inlineStr">
+        <is>
           <t>Samples the request already names as SANTANDER SCF</t>
         </is>
       </c>
-      <c r="C61" s="15">
+      <c r="C65" s="15">
         <f>COUNTIF(Samples!G5:G1000,"*SANTANDER*")</f>
         <v/>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="3" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Assumptions baked into this workbook</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="B65" s="14" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C69" s="16" t="inlineStr">
         <is>
           <t>Company code GBKM and the FEBAN transaction are taken from the requester's instruction, not from the auditor's workbook, which names neither.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="B66" s="14" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>The FEBAN statement-date range for each sample is the first to the last calendar day of the month containing that sample's payment date (column C and D formulas on 'Samples').</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="14" t="inlineStr">
+    <row r="71" ht="28" customHeight="1">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="C67" s="16" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>Sample amounts are stored as positive numbers. The auditor's workbook shows them unsigned even where the bank statement shows a debit.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="B68" s="14" t="inlineStr">
+    <row r="72" ht="28" customHeight="1">
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>Source of the sample list: 'Paper Samples' sheet, rows 5-60, of Samples_Paper_SURL260716_152455.962.xlsx as supplied by the auditor.</t>
         </is>
@@ -1400,10 +1468,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C70:D70"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
